--- a/ADS.xlsx
+++ b/ADS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63E54E6-43D1-4AE1-9084-B6FA833FC0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7899ACCD-F853-45ED-BD15-20652B3144EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D5339D34-B55C-48EB-B7CE-B183008CCAE6}</author>
+  </authors>
+  <commentList>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{D5339D34-B55C-48EB-B7CE-B183008CCAE6}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed reporting </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="81">
   <si>
     <t>Adidas</t>
   </si>
@@ -269,6 +287,18 @@
   <si>
     <t>SG&amp;A</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Latin America</t>
+  </si>
+  <si>
+    <t>Japan / South Korea</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
 </sst>
 </file>
 
@@ -279,13 +309,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -335,6 +371,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -355,31 +397,35 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -397,6 +443,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{E127EF10-7E7D-4F52-83D9-C61A06BE341D}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -714,6 +766,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C11" dT="2026-03-04T17:31:47.92" personId="{E127EF10-7E7D-4F52-83D9-C61A06BE341D}" id="{D5339D34-B55C-48EB-B7CE-B183008CCAE6}">
+    <text xml:space="preserve">Changed reporting </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010FB125-5721-48E0-B2EE-531517EC3DD6}">
   <dimension ref="A1:BA29"/>
@@ -731,525 +791,525 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="15">
-        <v>157.55000000000001</v>
-      </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
+      <c r="I2" s="14">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="4">
-        <v>178.54908399999999</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
+      <c r="I3" s="2">
+        <v>178.55922000000001</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
+      <c r="A4" s="14"/>
       <c r="B4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="15">
         <f>I2*I3</f>
-        <v>28130.408184200001</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
+        <v>25319.697396000003</v>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="16">
-        <v>1030</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
+      <c r="I5" s="15">
+        <v>1617</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="16">
-        <f>1802+17+656</f>
-        <v>2475</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
+      <c r="I6" s="15">
+        <f>1996+645</f>
+        <v>2641</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <f>I4-I5+I6</f>
-        <v>29575.408184200001</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
+        <v>26343.697396000003</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1260,8 +1320,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8AFDA6-8DF7-49F6-9902-DB49A0E15CEA}">
-  <dimension ref="A1:AC267"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8AFDA6-8DF7-49F6-9902-DB49A0E15CEA}">
+  <dimension ref="A1:AC269"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1333,6 +1393,9 @@
       <c r="V2" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="W2" s="16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1371,7 +1434,9 @@
       <c r="M3" s="7">
         <v>866</v>
       </c>
-      <c r="N3" s="7"/>
+      <c r="N3" s="7">
+        <v>886</v>
+      </c>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -1384,7 +1449,9 @@
       <c r="V3" s="7">
         <v>838</v>
       </c>
-      <c r="W3" s="7"/>
+      <c r="W3" s="7">
+        <v>886</v>
+      </c>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
@@ -1427,7 +1494,9 @@
       <c r="M4" s="7">
         <v>1115</v>
       </c>
-      <c r="N4" s="7"/>
+      <c r="N4" s="7">
+        <v>1136</v>
+      </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
@@ -1440,7 +1509,9 @@
       <c r="V4" s="7">
         <v>1095</v>
       </c>
-      <c r="W4" s="7"/>
+      <c r="W4" s="7">
+        <v>1136</v>
+      </c>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
@@ -1496,11 +1567,11 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="8">
-        <f t="shared" ref="P5:V5" si="2">+P3+P4</f>
+        <f t="shared" ref="P5:W5" si="2">+P3+P4</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8">
@@ -1527,7 +1598,10 @@
         <f t="shared" si="2"/>
         <v>1933</v>
       </c>
-      <c r="W5" s="7"/>
+      <c r="W5" s="8">
+        <f t="shared" si="2"/>
+        <v>2022</v>
+      </c>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
@@ -1599,7 +1673,10 @@
       <c r="M7" s="7">
         <v>2328</v>
       </c>
-      <c r="N7" s="7"/>
+      <c r="N7" s="7">
+        <f>+W7-SUM(K7:M7)</f>
+        <v>1825</v>
+      </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -1612,7 +1689,9 @@
       <c r="V7" s="7">
         <v>7551</v>
       </c>
-      <c r="W7" s="7"/>
+      <c r="W7" s="7">
+        <v>8136</v>
+      </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
@@ -1657,7 +1736,10 @@
       <c r="M8" s="7">
         <v>1298</v>
       </c>
-      <c r="N8" s="7"/>
+      <c r="N8" s="7">
+        <f t="shared" ref="N8:N33" si="3">+W8-SUM(K8:M8)</f>
+        <v>1266</v>
+      </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
@@ -1670,7 +1752,9 @@
       <c r="V8" s="7">
         <v>5128</v>
       </c>
-      <c r="W8" s="7"/>
+      <c r="W8" s="7">
+        <v>5087</v>
+      </c>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
@@ -1715,7 +1799,10 @@
       <c r="M9" s="7">
         <v>947</v>
       </c>
-      <c r="N9" s="7"/>
+      <c r="N9" s="7">
+        <f t="shared" si="3"/>
+        <v>849</v>
+      </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
@@ -1728,7 +1815,9 @@
       <c r="V9" s="7">
         <v>3459</v>
       </c>
-      <c r="W9" s="7"/>
+      <c r="W9" s="7">
+        <v>3623</v>
+      </c>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
@@ -1765,16 +1854,17 @@
         <v>940</v>
       </c>
       <c r="K10" s="7">
-        <v>1954</v>
+        <v>870</v>
       </c>
       <c r="L10" s="7">
-        <v>1818</v>
+        <v>762</v>
       </c>
       <c r="M10" s="7">
-        <f>935+720+358</f>
-        <v>2013</v>
-      </c>
-      <c r="N10" s="7"/>
+        <v>935</v>
+      </c>
+      <c r="N10" s="7">
+        <v>943</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -1787,7 +1877,9 @@
       <c r="V10" s="7">
         <v>3310</v>
       </c>
-      <c r="W10" s="7"/>
+      <c r="W10" s="7">
+        <v>3510</v>
+      </c>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
@@ -1796,56 +1888,70 @@
       <c r="AC10" s="7"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3023</v>
-      </c>
-      <c r="D11" s="7">
-        <v>3102</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3421</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2538</v>
+      <c r="B11" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="G11" s="7">
-        <v>3239</v>
+        <v>615</v>
       </c>
       <c r="H11" s="7">
-        <v>3573</v>
+        <v>673</v>
       </c>
       <c r="I11" s="7">
-        <v>3773</v>
+        <v>677</v>
       </c>
       <c r="J11" s="7">
-        <v>3390</v>
+        <v>807</v>
       </c>
       <c r="K11" s="7">
-        <v>3760</v>
+        <v>698</v>
       </c>
       <c r="L11" s="7">
-        <v>2476</v>
+        <v>673</v>
       </c>
       <c r="M11" s="7">
-        <v>3750</v>
-      </c>
-      <c r="N11" s="7"/>
+        <v>720</v>
+      </c>
+      <c r="N11" s="7">
+        <v>835</v>
+      </c>
       <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7">
-        <v>12083</v>
+      <c r="P11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="S11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="V11" s="7">
-        <v>13975</v>
-      </c>
-      <c r="W11" s="7"/>
+        <v>2772</v>
+      </c>
+      <c r="W11" s="7">
+        <v>2926</v>
+      </c>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
@@ -1854,56 +1960,70 @@
       <c r="AC11" s="7"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1911</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1836</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2188</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1992</v>
+      <c r="B12" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="G12" s="7">
-        <v>1885</v>
+        <v>339</v>
       </c>
       <c r="H12" s="7">
-        <v>1892</v>
+        <v>321</v>
       </c>
       <c r="I12" s="7">
-        <v>2245</v>
+        <v>361</v>
       </c>
       <c r="J12" s="7">
-        <v>2194</v>
+        <v>318</v>
       </c>
       <c r="K12" s="7">
-        <v>1968</v>
+        <v>374</v>
       </c>
       <c r="L12" s="7">
-        <v>2029</v>
+        <v>355</v>
       </c>
       <c r="M12" s="7">
-        <v>2383</v>
-      </c>
-      <c r="N12" s="7"/>
+        <v>358</v>
+      </c>
+      <c r="N12" s="7">
+        <v>319</v>
+      </c>
       <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7">
-        <v>7856</v>
+      <c r="P12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="S12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="T12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="U12" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="V12" s="7">
-        <v>8216</v>
-      </c>
-      <c r="W12" s="7"/>
+        <v>1339</v>
+      </c>
+      <c r="W12" s="7">
+        <v>1406</v>
+      </c>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
@@ -1913,42 +2033,45 @@
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="7">
-        <v>340</v>
+        <v>3023</v>
       </c>
       <c r="D13" s="7">
-        <v>405</v>
+        <v>3102</v>
       </c>
       <c r="E13" s="7">
-        <v>390</v>
+        <v>3421</v>
       </c>
       <c r="F13" s="7">
-        <v>352</v>
+        <v>2538</v>
       </c>
       <c r="G13" s="7">
-        <v>328</v>
+        <v>3239</v>
       </c>
       <c r="H13" s="7">
-        <v>370</v>
+        <v>3573</v>
       </c>
       <c r="I13" s="7">
-        <v>421</v>
+        <v>3773</v>
       </c>
       <c r="J13" s="7">
-        <v>380</v>
+        <v>3390</v>
       </c>
       <c r="K13" s="7">
-        <v>424</v>
+        <v>3760</v>
       </c>
       <c r="L13" s="7">
-        <v>447</v>
+        <v>2476</v>
       </c>
       <c r="M13" s="7">
-        <v>496</v>
-      </c>
-      <c r="N13" s="7"/>
+        <v>3750</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="3"/>
+        <v>4246</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -1956,12 +2079,14 @@
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7">
-        <v>1488</v>
+        <v>12083</v>
       </c>
       <c r="V13" s="7">
-        <v>1499</v>
-      </c>
-      <c r="W13" s="7"/>
+        <v>13975</v>
+      </c>
+      <c r="W13" s="7">
+        <v>14232</v>
+      </c>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
@@ -1970,218 +2095,197 @@
       <c r="AC13" s="7"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="8">
-        <v>5274</v>
-      </c>
-      <c r="D14" s="8">
-        <v>5343</v>
-      </c>
-      <c r="E14" s="8">
-        <v>5999</v>
-      </c>
-      <c r="F14" s="8">
-        <v>4812</v>
-      </c>
-      <c r="G14" s="8">
-        <v>5458</v>
-      </c>
-      <c r="H14" s="8">
-        <v>5822</v>
-      </c>
-      <c r="I14" s="8">
-        <v>6438</v>
-      </c>
-      <c r="J14" s="8">
-        <v>5965</v>
-      </c>
-      <c r="K14" s="8">
-        <v>6153</v>
-      </c>
-      <c r="L14" s="8">
-        <v>5952</v>
-      </c>
-      <c r="M14" s="8">
-        <v>6630</v>
-      </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8">
-        <v>21915</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>23640</v>
-      </c>
-      <c r="R14" s="8">
-        <v>18435</v>
-      </c>
-      <c r="S14" s="8">
-        <v>21234</v>
-      </c>
-      <c r="T14" s="8">
-        <v>22511</v>
-      </c>
-      <c r="U14" s="8">
-        <v>21427</v>
-      </c>
-      <c r="V14" s="8">
-        <v>23683</v>
-      </c>
-      <c r="W14" s="7"/>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1911</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1836</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2188</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1992</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1885</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1892</v>
+      </c>
+      <c r="I14" s="7">
+        <v>2245</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2194</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1968</v>
+      </c>
+      <c r="L14" s="7">
+        <v>2029</v>
+      </c>
+      <c r="M14" s="7">
+        <v>2383</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="3"/>
+        <v>2384</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7">
+        <v>7856</v>
+      </c>
+      <c r="V14" s="7">
+        <v>8216</v>
+      </c>
+      <c r="W14" s="7">
+        <v>8764</v>
+      </c>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>24</v>
+      <c r="B15" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="C15" s="7">
-        <v>2911</v>
+        <v>340</v>
       </c>
       <c r="D15" s="7">
-        <v>2625</v>
+        <v>405</v>
       </c>
       <c r="E15" s="7">
-        <v>3044</v>
+        <v>390</v>
       </c>
       <c r="F15" s="7">
-        <v>2664</v>
+        <v>352</v>
       </c>
       <c r="G15" s="7">
-        <v>2662</v>
+        <v>328</v>
       </c>
       <c r="H15" s="7">
-        <v>2863</v>
+        <v>370</v>
       </c>
       <c r="I15" s="7">
-        <v>3137</v>
+        <v>421</v>
       </c>
       <c r="J15" s="7">
-        <v>2995</v>
+        <v>380</v>
       </c>
       <c r="K15" s="7">
-        <v>2948</v>
+        <v>424</v>
       </c>
       <c r="L15" s="7">
-        <v>2875</v>
+        <v>447</v>
       </c>
       <c r="M15" s="7">
-        <v>3195</v>
-      </c>
-      <c r="N15" s="7"/>
+        <v>496</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="3"/>
+        <v>448</v>
+      </c>
       <c r="O15" s="7"/>
-      <c r="P15" s="7">
-        <v>10552</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>11347</v>
-      </c>
-      <c r="R15" s="7">
-        <v>9213</v>
-      </c>
-      <c r="S15" s="7">
-        <v>10469</v>
-      </c>
-      <c r="T15" s="7">
-        <v>11867</v>
-      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
       <c r="U15" s="7">
-        <v>11244</v>
+        <v>1488</v>
       </c>
       <c r="V15" s="7">
-        <v>11658</v>
-      </c>
-      <c r="W15" s="7"/>
+        <v>1499</v>
+      </c>
+      <c r="W15" s="7">
+        <v>1815</v>
+      </c>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="7">
-        <f t="shared" ref="C16" si="3">C14-C15</f>
-        <v>2363</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" ref="D16" si="4">D14-D15</f>
-        <v>2718</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" ref="E16" si="5">E14-E15</f>
-        <v>2955</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" ref="F16" si="6">F14-F15</f>
-        <v>2148</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" ref="G16" si="7">G14-G15</f>
-        <v>2796</v>
-      </c>
-      <c r="H16" s="7">
-        <f t="shared" ref="H16" si="8">H14-H15</f>
-        <v>2959</v>
-      </c>
-      <c r="I16" s="7">
-        <f t="shared" ref="I16" si="9">I14-I15</f>
-        <v>3301</v>
-      </c>
-      <c r="J16" s="7">
-        <f t="shared" ref="J16:M16" si="10">J14-J15</f>
-        <v>2970</v>
-      </c>
-      <c r="K16" s="7">
-        <f t="shared" si="10"/>
-        <v>3205</v>
-      </c>
-      <c r="L16" s="7">
-        <f t="shared" si="10"/>
-        <v>3077</v>
-      </c>
-      <c r="M16" s="7">
-        <f t="shared" si="10"/>
-        <v>3435</v>
-      </c>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7">
-        <f t="shared" ref="P16:T16" si="11">P14-P15</f>
-        <v>11363</v>
-      </c>
-      <c r="Q16" s="7">
-        <f t="shared" si="11"/>
-        <v>12293</v>
-      </c>
-      <c r="R16" s="7">
-        <f t="shared" si="11"/>
-        <v>9222</v>
-      </c>
-      <c r="S16" s="7">
-        <f t="shared" si="11"/>
-        <v>10765</v>
-      </c>
-      <c r="T16" s="7">
-        <f t="shared" si="11"/>
-        <v>10644</v>
-      </c>
-      <c r="U16" s="7">
-        <f>U14-U15</f>
-        <v>10183</v>
-      </c>
-      <c r="V16" s="7">
-        <f>V14-V15</f>
-        <v>12025</v>
-      </c>
-      <c r="W16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5274</v>
+      </c>
+      <c r="D16" s="8">
+        <v>5343</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5999</v>
+      </c>
+      <c r="F16" s="8">
+        <v>4812</v>
+      </c>
+      <c r="G16" s="8">
+        <v>5458</v>
+      </c>
+      <c r="H16" s="8">
+        <v>5822</v>
+      </c>
+      <c r="I16" s="8">
+        <v>6438</v>
+      </c>
+      <c r="J16" s="8">
+        <v>5965</v>
+      </c>
+      <c r="K16" s="8">
+        <v>6153</v>
+      </c>
+      <c r="L16" s="8">
+        <v>5952</v>
+      </c>
+      <c r="M16" s="8">
+        <v>6630</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="3"/>
+        <v>6076</v>
+      </c>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8">
+        <v>21915</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>23640</v>
+      </c>
+      <c r="R16" s="8">
+        <v>18435</v>
+      </c>
+      <c r="S16" s="8">
+        <v>21234</v>
+      </c>
+      <c r="T16" s="8">
+        <v>22511</v>
+      </c>
+      <c r="U16" s="8">
+        <v>21427</v>
+      </c>
+      <c r="V16" s="8">
+        <v>23683</v>
+      </c>
+      <c r="W16" s="8">
+        <v>24811</v>
+      </c>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
@@ -2190,65 +2294,70 @@
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="7">
-        <v>25</v>
+        <v>2911</v>
       </c>
       <c r="D17" s="7">
-        <v>21</v>
+        <v>2625</v>
       </c>
       <c r="E17" s="7">
-        <v>20</v>
+        <v>3044</v>
       </c>
       <c r="F17" s="7">
-        <v>17</v>
+        <v>2664</v>
       </c>
       <c r="G17" s="7">
-        <v>17</v>
+        <v>2662</v>
       </c>
       <c r="H17" s="7">
-        <v>19</v>
+        <v>2863</v>
       </c>
       <c r="I17" s="7">
-        <v>20</v>
+        <v>3137</v>
       </c>
       <c r="J17" s="7">
-        <v>26</v>
+        <v>2995</v>
       </c>
       <c r="K17" s="7">
-        <v>19</v>
+        <v>2948</v>
       </c>
       <c r="L17" s="7">
-        <v>18</v>
+        <v>2875</v>
       </c>
       <c r="M17" s="7">
-        <v>24</v>
-      </c>
-      <c r="N17" s="7"/>
+        <v>3195</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="3"/>
+        <v>2988</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7">
-        <v>129</v>
+        <v>10552</v>
       </c>
       <c r="Q17" s="7">
-        <v>154</v>
+        <v>11347</v>
       </c>
       <c r="R17" s="7">
-        <v>61</v>
+        <v>9213</v>
       </c>
       <c r="S17" s="7">
-        <v>86</v>
+        <v>10469</v>
       </c>
       <c r="T17" s="7">
-        <v>112</v>
+        <v>11867</v>
       </c>
       <c r="U17" s="7">
-        <v>83</v>
+        <v>11244</v>
       </c>
       <c r="V17" s="7">
-        <v>81</v>
-      </c>
-      <c r="W17" s="7"/>
+        <v>11658</v>
+      </c>
+      <c r="W17" s="7">
+        <v>12006</v>
+      </c>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
@@ -2257,65 +2366,89 @@
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7">
-        <v>39</v>
+        <f t="shared" ref="C18" si="4">C16-C17</f>
+        <v>2363</v>
       </c>
       <c r="D18" s="7">
-        <v>18</v>
+        <f t="shared" ref="D18" si="5">D16-D17</f>
+        <v>2718</v>
       </c>
       <c r="E18" s="7">
-        <v>5</v>
+        <f t="shared" ref="E18" si="6">E16-E17</f>
+        <v>2955</v>
       </c>
       <c r="F18" s="7">
-        <v>10</v>
+        <f t="shared" ref="F18" si="7">F16-F17</f>
+        <v>2148</v>
       </c>
       <c r="G18" s="7">
-        <v>2</v>
+        <f t="shared" ref="G18" si="8">G16-G17</f>
+        <v>2796</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <f t="shared" ref="H18" si="9">H16-H17</f>
+        <v>2959</v>
       </c>
       <c r="I18" s="7">
-        <v>113</v>
+        <f t="shared" ref="I18" si="10">I16-I17</f>
+        <v>3301</v>
       </c>
       <c r="J18" s="7">
-        <v>53</v>
+        <f t="shared" ref="J18:N18" si="11">J16-J17</f>
+        <v>2970</v>
       </c>
       <c r="K18" s="7">
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>3205</v>
       </c>
       <c r="L18" s="7">
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>3077</v>
       </c>
       <c r="M18" s="7">
-        <v>18</v>
-      </c>
-      <c r="N18" s="7"/>
+        <f t="shared" si="11"/>
+        <v>3435</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="11"/>
+        <v>3088</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7">
-        <v>48</v>
+        <f t="shared" ref="P18:T18" si="12">P16-P17</f>
+        <v>11363</v>
       </c>
       <c r="Q18" s="7">
-        <v>56</v>
+        <f t="shared" si="12"/>
+        <v>12293</v>
       </c>
       <c r="R18" s="7">
-        <v>42</v>
+        <f t="shared" si="12"/>
+        <v>9222</v>
       </c>
       <c r="S18" s="7">
-        <v>28</v>
+        <f t="shared" si="12"/>
+        <v>10765</v>
       </c>
       <c r="T18" s="7">
-        <v>173</v>
+        <f t="shared" si="12"/>
+        <v>10644</v>
       </c>
       <c r="U18" s="7">
-        <v>71</v>
+        <f>U16-U17</f>
+        <v>10183</v>
       </c>
       <c r="V18" s="7">
-        <v>174</v>
-      </c>
-      <c r="W18" s="7"/>
+        <f>V16-V17</f>
+        <v>12025</v>
+      </c>
+      <c r="W18" s="7">
+        <f>W16-W17</f>
+        <v>12805</v>
+      </c>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
@@ -2324,66 +2457,70 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="7">
-        <v>601</v>
+        <v>25</v>
       </c>
       <c r="D19" s="7">
-        <v>617</v>
+        <v>21</v>
       </c>
       <c r="E19" s="7">
-        <v>644</v>
+        <v>20</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G19" s="7">
-        <v>657</v>
+        <v>17</v>
       </c>
       <c r="H19" s="7">
-        <v>707</v>
+        <v>19</v>
       </c>
       <c r="I19" s="7">
-        <v>724</v>
+        <v>20</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K19" s="7">
-        <v>746</v>
+        <v>19</v>
       </c>
       <c r="L19" s="7">
-        <v>712</v>
+        <v>18</v>
       </c>
       <c r="M19" s="7">
-        <v>798</v>
-      </c>
-      <c r="N19" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7">
-        <v>3001</v>
+        <v>129</v>
       </c>
       <c r="Q19" s="7">
-        <v>3042</v>
+        <v>154</v>
       </c>
       <c r="R19" s="7">
-        <v>2373</v>
+        <v>61</v>
       </c>
       <c r="S19" s="7">
-        <v>2547</v>
+        <v>86</v>
       </c>
       <c r="T19" s="7">
-        <v>2763</v>
+        <v>112</v>
       </c>
       <c r="U19" s="7">
-        <v>2528</v>
+        <v>83</v>
       </c>
       <c r="V19" s="7">
-        <f>+SUM(G19:J19)</f>
-        <v>2088</v>
-      </c>
-      <c r="W19" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="W19" s="7">
+        <v>81</v>
+      </c>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
@@ -2392,66 +2529,70 @@
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" s="7">
-        <v>1766</v>
+        <v>39</v>
       </c>
       <c r="D20" s="7">
-        <v>1965</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7">
-        <v>1926</v>
+        <v>5</v>
       </c>
       <c r="F20" s="7">
-        <v>2551</v>
+        <v>10</v>
       </c>
       <c r="G20" s="7">
-        <v>1822</v>
+        <v>2</v>
       </c>
       <c r="H20" s="7">
-        <v>1930</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>2114</v>
+        <v>113</v>
       </c>
       <c r="J20" s="7">
-        <v>2992</v>
+        <v>53</v>
       </c>
       <c r="K20" s="7">
-        <v>1870</v>
+        <v>1</v>
       </c>
       <c r="L20" s="7">
-        <v>1837</v>
+        <v>1</v>
       </c>
       <c r="M20" s="7">
-        <v>1943</v>
-      </c>
-      <c r="N20" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7">
-        <v>4450</v>
+        <v>48</v>
       </c>
       <c r="Q20" s="7">
-        <v>4997</v>
+        <v>56</v>
       </c>
       <c r="R20" s="7">
-        <v>4601</v>
+        <v>42</v>
       </c>
       <c r="S20" s="7">
-        <v>4782</v>
+        <v>28</v>
       </c>
       <c r="T20" s="7">
-        <v>5601</v>
+        <v>173</v>
       </c>
       <c r="U20" s="7">
-        <v>5547</v>
+        <v>71</v>
       </c>
       <c r="V20" s="7">
-        <f>+SUM(G20:J20)</f>
-        <v>8858</v>
-      </c>
-      <c r="W20" s="7"/>
+        <v>174</v>
+      </c>
+      <c r="W20" s="7">
+        <v>41</v>
+      </c>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
@@ -2459,67 +2600,72 @@
       <c r="AB20" s="7"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B21" s="14" t="s">
-        <v>76</v>
+      <c r="B21" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="7">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="D21" s="7">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="E21" s="7">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="F21" s="7">
         <v>0</v>
       </c>
       <c r="G21" s="7">
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="H21" s="7">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="I21" s="7">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="J21" s="7">
         <v>0</v>
       </c>
       <c r="K21" s="7">
-        <v>2615</v>
+        <v>746</v>
       </c>
       <c r="L21" s="7">
-        <v>2549</v>
+        <v>712</v>
       </c>
       <c r="M21" s="7">
-        <v>2740</v>
-      </c>
-      <c r="N21" s="7"/>
+        <v>798</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="3"/>
+        <v>823</v>
+      </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7">
-        <v>1576</v>
+        <v>3001</v>
       </c>
       <c r="Q21" s="7">
-        <v>1652</v>
+        <v>3042</v>
       </c>
       <c r="R21" s="7">
-        <v>1379</v>
+        <v>2373</v>
       </c>
       <c r="S21" s="7">
-        <v>1481</v>
+        <v>2547</v>
       </c>
       <c r="T21" s="7">
-        <v>1651</v>
+        <v>2763</v>
       </c>
       <c r="U21" s="7">
-        <v>1839</v>
+        <v>2528</v>
       </c>
       <c r="V21" s="7">
         <f>+SUM(G21:J21)</f>
-        <v>0</v>
-      </c>
-      <c r="W21" s="7"/>
+        <v>2088</v>
+      </c>
+      <c r="W21" s="7">
+        <v>3079</v>
+      </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
@@ -2528,72 +2674,71 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="7">
-        <v>0</v>
+        <v>1766</v>
       </c>
       <c r="D22" s="7">
-        <v>0</v>
+        <v>1965</v>
       </c>
       <c r="E22" s="7">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="F22" s="7">
-        <v>0</v>
+        <v>2551</v>
       </c>
       <c r="G22" s="7">
-        <v>0</v>
+        <v>1822</v>
       </c>
       <c r="H22" s="7">
-        <v>0</v>
+        <v>1930</v>
       </c>
       <c r="I22" s="7">
-        <v>0</v>
+        <v>2114</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <v>2992</v>
       </c>
       <c r="K22" s="7">
-        <v>0</v>
+        <v>1870</v>
       </c>
       <c r="L22" s="7">
-        <v>0</v>
+        <v>1837</v>
       </c>
       <c r="M22" s="7">
-        <v>0</v>
-      </c>
-      <c r="N22" s="7"/>
+        <v>1943</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="3"/>
+        <v>2142</v>
+      </c>
       <c r="O22" s="7"/>
       <c r="P22" s="7">
-        <f>105+41</f>
-        <v>146</v>
+        <v>4450</v>
       </c>
       <c r="Q22" s="7">
-        <f>134+18</f>
-        <v>152</v>
+        <v>4997</v>
       </c>
       <c r="R22" s="7">
-        <f>116+111</f>
-        <v>227</v>
+        <v>4601</v>
       </c>
       <c r="S22" s="7">
-        <f>76+6</f>
-        <v>82</v>
+        <v>4782</v>
       </c>
       <c r="T22" s="7">
-        <f>182+63</f>
-        <v>245</v>
+        <v>5601</v>
       </c>
       <c r="U22" s="7">
-        <f>137+19</f>
-        <v>156</v>
+        <v>5547</v>
       </c>
       <c r="V22" s="7">
         <f>+SUM(G22:J22)</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="7"/>
+        <v>8858</v>
+      </c>
+      <c r="W22" s="7">
+        <v>7792</v>
+      </c>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
@@ -2601,84 +2746,72 @@
       <c r="AB22" s="7"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B23" s="7" t="s">
-        <v>30</v>
+      <c r="B23" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="C23" s="7">
-        <f t="shared" ref="C23:F23" si="12">C16+C17+C18-C19-C20</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D23" s="7">
-        <f t="shared" si="12"/>
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7">
-        <f t="shared" si="12"/>
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7">
-        <f t="shared" si="12"/>
-        <v>-376</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7">
-        <f>G16+G17+G18-G19-G20</f>
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" ref="H23:M23" si="13">H16+H17+H18-H19-H20</f>
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="I23" s="7">
-        <f t="shared" si="13"/>
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" si="13"/>
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" si="13"/>
-        <v>609</v>
+        <v>2615</v>
       </c>
       <c r="L23" s="7">
-        <f>L16+L17+L18-L19-L20</f>
-        <v>547</v>
+        <v>2549</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" si="13"/>
-        <v>736</v>
-      </c>
-      <c r="N23" s="7"/>
+        <v>2740</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="3"/>
+        <v>-7904</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7">
-        <f t="shared" ref="P23:T23" si="14">P16+P17+P18-SUM(P19:P22)</f>
-        <v>2367</v>
+        <v>1576</v>
       </c>
       <c r="Q23" s="7">
-        <f t="shared" si="14"/>
-        <v>2660</v>
+        <v>1652</v>
       </c>
       <c r="R23" s="7">
-        <f t="shared" si="14"/>
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="S23" s="7">
-        <f t="shared" si="14"/>
-        <v>1987</v>
+        <v>1481</v>
       </c>
       <c r="T23" s="7">
-        <f t="shared" si="14"/>
-        <v>669</v>
+        <v>1651</v>
       </c>
       <c r="U23" s="7">
-        <f>U16+U17+U18-SUM(U19:U22)</f>
-        <v>267</v>
+        <v>1839</v>
       </c>
       <c r="V23" s="7">
-        <f>V16+V17+V18-SUM(V19:V22)</f>
-        <v>1334</v>
-      </c>
-      <c r="W23" s="7"/>
+        <f>+SUM(G23:J23)</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="7">
+        <v>0</v>
+      </c>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
@@ -2687,65 +2820,77 @@
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C24" s="7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F24" s="7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H24" s="7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I24" s="7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J24" s="7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M24" s="7">
-        <v>12</v>
-      </c>
-      <c r="N24" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7">
-        <v>57</v>
+        <f>105+41</f>
+        <v>146</v>
       </c>
       <c r="Q24" s="7">
-        <v>64</v>
+        <f>134+18</f>
+        <v>152</v>
       </c>
       <c r="R24" s="7">
-        <v>29</v>
+        <f>116+111</f>
+        <v>227</v>
       </c>
       <c r="S24" s="7">
-        <v>19</v>
+        <f>76+6</f>
+        <v>82</v>
       </c>
       <c r="T24" s="7">
-        <v>39</v>
+        <f>182+63</f>
+        <v>245</v>
       </c>
       <c r="U24" s="7">
-        <v>79</v>
+        <f>137+19</f>
+        <v>156</v>
       </c>
       <c r="V24" s="7">
-        <v>101</v>
-      </c>
-      <c r="W24" s="7"/>
+        <f>+SUM(G24:J24)</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="7">
+        <v>0</v>
+      </c>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
@@ -2754,65 +2899,89 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C25" s="7">
-        <v>41</v>
+        <f t="shared" ref="C25:F25" si="13">C18+C19+C20-C21-C22</f>
+        <v>60</v>
       </c>
       <c r="D25" s="7">
-        <v>71</v>
+        <f t="shared" si="13"/>
+        <v>175</v>
       </c>
       <c r="E25" s="7">
-        <v>115</v>
+        <f t="shared" si="13"/>
+        <v>410</v>
       </c>
       <c r="F25" s="7">
-        <v>63</v>
+        <f t="shared" si="13"/>
+        <v>-376</v>
       </c>
       <c r="G25" s="7">
-        <v>115</v>
+        <f>G18+G19+G20-G21-G22</f>
+        <v>336</v>
       </c>
       <c r="H25" s="7">
-        <v>62</v>
+        <f t="shared" ref="H25:N25" si="14">H18+H19+H20-H21-H22</f>
+        <v>347</v>
       </c>
       <c r="I25" s="7">
-        <v>25</v>
+        <f t="shared" si="14"/>
+        <v>596</v>
       </c>
       <c r="J25" s="7">
-        <v>115</v>
+        <f t="shared" si="14"/>
+        <v>57</v>
       </c>
       <c r="K25" s="7">
-        <v>59</v>
+        <f t="shared" si="14"/>
+        <v>609</v>
       </c>
       <c r="L25" s="7">
-        <v>67</v>
+        <f>L18+L19+L20-L21-L22</f>
+        <v>547</v>
       </c>
       <c r="M25" s="7">
-        <v>98</v>
-      </c>
-      <c r="N25" s="7"/>
+        <f t="shared" si="14"/>
+        <v>736</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="14"/>
+        <v>164</v>
+      </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7">
-        <v>47</v>
+        <f t="shared" ref="P25:T25" si="15">P18+P19+P20-SUM(P21:P24)</f>
+        <v>2367</v>
       </c>
       <c r="Q25" s="7">
-        <v>166</v>
+        <f t="shared" si="15"/>
+        <v>2660</v>
       </c>
       <c r="R25" s="7">
-        <v>196</v>
+        <f t="shared" si="15"/>
+        <v>745</v>
       </c>
       <c r="S25" s="7">
-        <v>153</v>
+        <f t="shared" si="15"/>
+        <v>1987</v>
       </c>
       <c r="T25" s="7">
-        <v>320</v>
+        <f t="shared" si="15"/>
+        <v>669</v>
       </c>
       <c r="U25" s="7">
-        <v>282</v>
+        <f>U18+U19+U20-SUM(U21:U24)</f>
+        <v>267</v>
       </c>
       <c r="V25" s="7">
-        <v>317</v>
-      </c>
-      <c r="W25" s="7"/>
+        <f>V18+V19+V20-SUM(V21:V24)</f>
+        <v>1334</v>
+      </c>
+      <c r="W25" s="7">
+        <f>W18+W19+W20-SUM(W21:W24)</f>
+        <v>2056</v>
+      </c>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
@@ -2821,83 +2990,70 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="7">
+        <v>13</v>
+      </c>
+      <c r="D26" s="7">
+        <v>19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>31</v>
+      </c>
+      <c r="F26" s="7">
+        <v>25</v>
+      </c>
+      <c r="G26" s="7">
+        <v>24</v>
+      </c>
+      <c r="H26" s="7">
+        <v>20</v>
+      </c>
+      <c r="I26" s="7">
+        <v>29</v>
+      </c>
+      <c r="J26" s="7">
+        <v>30</v>
+      </c>
+      <c r="K26" s="7">
         <v>34</v>
       </c>
-      <c r="C26" s="7">
-        <f t="shared" ref="C26" si="15">C23+C24-C25</f>
-        <v>32</v>
-      </c>
-      <c r="D26" s="7">
-        <f t="shared" ref="D26" si="16">D23+D24-D25</f>
-        <v>123</v>
-      </c>
-      <c r="E26" s="7">
-        <f t="shared" ref="E26" si="17">E23+E24-E25</f>
-        <v>326</v>
-      </c>
-      <c r="F26" s="7">
-        <f t="shared" ref="F26" si="18">F23+F24-F25</f>
-        <v>-414</v>
-      </c>
-      <c r="G26" s="7">
-        <f t="shared" ref="G26" si="19">G23+G24-G25</f>
-        <v>245</v>
-      </c>
-      <c r="H26" s="7">
-        <f t="shared" ref="H26" si="20">H23+H24-H25</f>
-        <v>305</v>
-      </c>
-      <c r="I26" s="7">
-        <f t="shared" ref="I26" si="21">I23+I24-I25</f>
-        <v>600</v>
-      </c>
-      <c r="J26" s="7">
-        <f t="shared" ref="J26:M26" si="22">J23+J24-J25</f>
-        <v>-28</v>
-      </c>
-      <c r="K26" s="7">
-        <f t="shared" si="22"/>
-        <v>584</v>
-      </c>
       <c r="L26" s="7">
-        <f t="shared" si="22"/>
-        <v>489</v>
+        <v>9</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="22"/>
-        <v>650</v>
-      </c>
-      <c r="N26" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7">
-        <f t="shared" ref="P26:T26" si="23">P23+P24-P25</f>
-        <v>2377</v>
+        <v>57</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="23"/>
-        <v>2558</v>
+        <v>64</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="23"/>
-        <v>578</v>
+        <v>29</v>
       </c>
       <c r="S26" s="7">
-        <f t="shared" si="23"/>
-        <v>1853</v>
+        <v>19</v>
       </c>
       <c r="T26" s="7">
-        <f t="shared" si="23"/>
-        <v>388</v>
+        <v>39</v>
       </c>
       <c r="U26" s="7">
-        <f>U23+U24-U25</f>
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="V26" s="7">
-        <f>+SUM(G26:J26)</f>
-        <v>1122</v>
-      </c>
-      <c r="W26" s="7"/>
+        <v>101</v>
+      </c>
+      <c r="W26" s="7">
+        <v>74</v>
+      </c>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
@@ -2906,65 +3062,70 @@
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C27" s="7">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D27" s="7">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E27" s="7">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F27" s="7">
-        <v>-14</v>
+        <v>63</v>
       </c>
       <c r="G27" s="7">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="H27" s="7">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="I27" s="7">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="J27" s="7">
-        <v>-2</v>
+        <v>115</v>
       </c>
       <c r="K27" s="7">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="L27" s="7">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="M27" s="7">
-        <v>169</v>
-      </c>
-      <c r="N27" s="7"/>
+        <v>98</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="3"/>
+        <v>86</v>
+      </c>
       <c r="O27" s="7"/>
       <c r="P27" s="7">
-        <v>669</v>
+        <v>47</v>
       </c>
       <c r="Q27" s="7">
-        <v>640</v>
+        <v>166</v>
       </c>
       <c r="R27" s="7">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="S27" s="7">
-        <v>360</v>
+        <v>153</v>
       </c>
       <c r="T27" s="7">
-        <v>134</v>
+        <v>320</v>
       </c>
       <c r="U27" s="7">
-        <v>124</v>
+        <v>282</v>
       </c>
       <c r="V27" s="7">
-        <v>297</v>
-      </c>
-      <c r="W27" s="7"/>
+        <v>317</v>
+      </c>
+      <c r="W27" s="7">
+        <v>310</v>
+      </c>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
@@ -2973,83 +3134,89 @@
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28" si="24">C26-C27</f>
-        <v>-23</v>
+        <f t="shared" ref="C28" si="16">C25+C26-C27</f>
+        <v>32</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" ref="D28" si="25">D26-D27</f>
-        <v>96</v>
+        <f t="shared" ref="D28" si="17">D25+D26-D27</f>
+        <v>123</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" ref="E28" si="26">E26-E27</f>
-        <v>271</v>
+        <f t="shared" ref="E28" si="18">E25+E26-E27</f>
+        <v>326</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" ref="F28" si="27">F26-F27</f>
-        <v>-400</v>
+        <f t="shared" ref="F28" si="19">F25+F26-F27</f>
+        <v>-414</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" ref="G28" si="28">G26-G27</f>
-        <v>171</v>
+        <f t="shared" ref="G28" si="20">G25+G26-G27</f>
+        <v>245</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" ref="H28" si="29">H26-H27</f>
-        <v>212</v>
+        <f t="shared" ref="H28" si="21">H25+H26-H27</f>
+        <v>305</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" ref="I28" si="30">I26-I27</f>
-        <v>467</v>
+        <f t="shared" ref="I28" si="22">I25+I26-I27</f>
+        <v>600</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" ref="J28:M28" si="31">J26-J27</f>
-        <v>-26</v>
+        <f t="shared" ref="J28:N28" si="23">J25+J26-J27</f>
+        <v>-28</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="31"/>
-        <v>435</v>
+        <f t="shared" si="23"/>
+        <v>584</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="31"/>
-        <v>375</v>
+        <f t="shared" si="23"/>
+        <v>489</v>
       </c>
       <c r="M28" s="7">
-        <f t="shared" si="31"/>
-        <v>481</v>
-      </c>
-      <c r="N28" s="7"/>
+        <f t="shared" si="23"/>
+        <v>650</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="23"/>
+        <v>97</v>
+      </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7">
-        <f t="shared" ref="P28:T28" si="32">P26-P27</f>
-        <v>1708</v>
+        <f t="shared" ref="P28:T28" si="24">P25+P26-P27</f>
+        <v>2377</v>
       </c>
       <c r="Q28" s="7">
-        <f t="shared" si="32"/>
-        <v>1918</v>
+        <f t="shared" si="24"/>
+        <v>2558</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" si="32"/>
-        <v>461</v>
+        <f t="shared" si="24"/>
+        <v>578</v>
       </c>
       <c r="S28" s="7">
-        <f t="shared" si="32"/>
-        <v>1493</v>
+        <f t="shared" si="24"/>
+        <v>1853</v>
       </c>
       <c r="T28" s="7">
-        <f t="shared" si="32"/>
-        <v>254</v>
+        <f t="shared" si="24"/>
+        <v>388</v>
       </c>
       <c r="U28" s="7">
-        <f>U26-U27</f>
-        <v>-60</v>
+        <f>U25+U26-U27</f>
+        <v>64</v>
       </c>
       <c r="V28" s="7">
-        <f>V26-V27</f>
-        <v>825</v>
-      </c>
-      <c r="W28" s="7"/>
+        <f>+SUM(G28:J28)</f>
+        <v>1122</v>
+      </c>
+      <c r="W28" s="7">
+        <f>+W25+W26-W27</f>
+        <v>1820</v>
+      </c>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
@@ -3058,65 +3225,70 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C29" s="7">
-        <v>-6</v>
+        <v>55</v>
       </c>
       <c r="D29" s="7">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="E29" s="7">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F29" s="7">
-        <v>42</v>
+        <v>-14</v>
       </c>
       <c r="G29" s="7">
-        <v>-1</v>
+        <v>74</v>
       </c>
       <c r="H29" s="7">
-        <v>-6</v>
+        <v>93</v>
       </c>
       <c r="I29" s="7">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="J29" s="7">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="K29" s="7">
-        <v>-7</v>
+        <v>149</v>
       </c>
       <c r="L29" s="7">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="M29" s="7">
-        <v>3</v>
-      </c>
-      <c r="N29" s="7"/>
+        <v>169</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
       <c r="O29" s="7"/>
       <c r="P29" s="7">
-        <v>-5</v>
+        <v>669</v>
       </c>
       <c r="Q29" s="7">
-        <v>59</v>
+        <v>640</v>
       </c>
       <c r="R29" s="7">
-        <v>-19</v>
+        <v>117</v>
       </c>
       <c r="S29" s="7">
-        <v>666</v>
+        <v>360</v>
       </c>
       <c r="T29" s="7">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="U29" s="7">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="V29" s="7">
-        <v>8</v>
-      </c>
-      <c r="W29" s="7"/>
+        <v>297</v>
+      </c>
+      <c r="W29" s="7">
+        <v>443</v>
+      </c>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
@@ -3125,83 +3297,89 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="7">
-        <f t="shared" ref="C30" si="33">C28+C29</f>
-        <v>-29</v>
+        <f t="shared" ref="C30" si="25">C28-C29</f>
+        <v>-23</v>
       </c>
       <c r="D30" s="7">
-        <f t="shared" ref="D30" si="34">D28+D29</f>
-        <v>95</v>
+        <f t="shared" ref="D30" si="26">D28-D29</f>
+        <v>96</v>
       </c>
       <c r="E30" s="7">
-        <f t="shared" ref="E30" si="35">E28+E29</f>
-        <v>281</v>
+        <f t="shared" ref="E30" si="27">E28-E29</f>
+        <v>271</v>
       </c>
       <c r="F30" s="7">
-        <f t="shared" ref="F30" si="36">F28+F29</f>
-        <v>-358</v>
+        <f t="shared" ref="F30" si="28">F28-F29</f>
+        <v>-400</v>
       </c>
       <c r="G30" s="7">
-        <f t="shared" ref="G30" si="37">G28+G29</f>
-        <v>170</v>
+        <f t="shared" ref="G30" si="29">G28-G29</f>
+        <v>171</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" ref="H30" si="38">H28+H29</f>
-        <v>206</v>
+        <f t="shared" ref="H30" si="30">H28-H29</f>
+        <v>212</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" ref="I30" si="39">I28+I29</f>
-        <v>474</v>
+        <f t="shared" ref="I30" si="31">I28-I29</f>
+        <v>467</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" ref="J30:M30" si="40">J28+J29</f>
-        <v>-19</v>
+        <f t="shared" ref="J30:N30" si="32">J28-J29</f>
+        <v>-26</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="40"/>
-        <v>428</v>
+        <f t="shared" si="32"/>
+        <v>435</v>
       </c>
       <c r="L30" s="7">
-        <f t="shared" si="40"/>
-        <v>381</v>
+        <f t="shared" si="32"/>
+        <v>375</v>
       </c>
       <c r="M30" s="7">
-        <f t="shared" si="40"/>
-        <v>484</v>
-      </c>
-      <c r="N30" s="7"/>
+        <f t="shared" si="32"/>
+        <v>481</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="32"/>
+        <v>86</v>
+      </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7">
-        <f t="shared" ref="P30:T30" si="41">P28+P29</f>
-        <v>1703</v>
+        <f t="shared" ref="P30:T30" si="33">P28-P29</f>
+        <v>1708</v>
       </c>
       <c r="Q30" s="7">
-        <f t="shared" si="41"/>
-        <v>1977</v>
+        <f t="shared" si="33"/>
+        <v>1918</v>
       </c>
       <c r="R30" s="7">
-        <f t="shared" si="41"/>
-        <v>442</v>
+        <f t="shared" si="33"/>
+        <v>461</v>
       </c>
       <c r="S30" s="7">
-        <f t="shared" si="41"/>
-        <v>2159</v>
+        <f t="shared" si="33"/>
+        <v>1493</v>
       </c>
       <c r="T30" s="7">
-        <f t="shared" si="41"/>
-        <v>638</v>
+        <f t="shared" si="33"/>
+        <v>254</v>
       </c>
       <c r="U30" s="7">
-        <f>U28+U29</f>
-        <v>-16</v>
+        <f>U28-U29</f>
+        <v>-60</v>
       </c>
       <c r="V30" s="7">
-        <f>V28+V29</f>
-        <v>833</v>
-      </c>
-      <c r="W30" s="7"/>
+        <f>V28-V29</f>
+        <v>825</v>
+      </c>
+      <c r="W30" s="7">
+        <f>W28-W29</f>
+        <v>1377</v>
+      </c>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
@@ -3210,65 +3388,70 @@
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="7">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="D31" s="7">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="E31" s="7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F31" s="7">
-        <v>-379</v>
+        <v>42</v>
       </c>
       <c r="G31" s="7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="7">
-        <v>16</v>
+        <v>-6</v>
       </c>
       <c r="I31" s="7">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J31" s="7">
-        <v>-39</v>
+        <v>7</v>
       </c>
       <c r="K31" s="7">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M31" s="7">
-        <v>23</v>
-      </c>
-      <c r="N31" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
       <c r="O31" s="7"/>
       <c r="P31" s="7">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="Q31" s="7">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="R31" s="7">
-        <v>11</v>
+        <v>-19</v>
       </c>
       <c r="S31" s="7">
-        <v>42</v>
+        <v>666</v>
       </c>
       <c r="T31" s="7">
-        <v>26</v>
+        <v>384</v>
       </c>
       <c r="U31" s="7">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="V31" s="7">
-        <v>764</v>
-      </c>
-      <c r="W31" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="W31" s="7">
+        <v>8</v>
+      </c>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
@@ -3277,83 +3460,89 @@
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32" si="42">C30-C31</f>
-        <v>-38</v>
+        <f t="shared" ref="C32" si="34">C30+C31</f>
+        <v>-29</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" ref="D32" si="43">D30-D31</f>
-        <v>84</v>
+        <f t="shared" ref="D32" si="35">D30+D31</f>
+        <v>95</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" ref="E32" si="44">E30-E31</f>
-        <v>260</v>
+        <f t="shared" ref="E32" si="36">E30+E31</f>
+        <v>281</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" ref="F32" si="45">F30-F31</f>
-        <v>21</v>
+        <f t="shared" ref="F32" si="37">F30+F31</f>
+        <v>-358</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" ref="G32" si="46">G30-G31</f>
+        <f t="shared" ref="G32" si="38">G30+G31</f>
         <v>170</v>
       </c>
       <c r="H32" s="7">
-        <f>H30-H31</f>
-        <v>190</v>
+        <f t="shared" ref="H32" si="39">H30+H31</f>
+        <v>206</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" ref="I32:M32" si="47">I30-I31</f>
-        <v>441</v>
+        <f t="shared" ref="I32" si="40">I30+I31</f>
+        <v>474</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="47"/>
-        <v>20</v>
+        <f t="shared" ref="J32:N32" si="41">J30+J31</f>
+        <v>-19</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="47"/>
-        <v>427</v>
+        <f t="shared" si="41"/>
+        <v>428</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="47"/>
-        <v>370</v>
+        <f t="shared" si="41"/>
+        <v>381</v>
       </c>
       <c r="M32" s="7">
-        <f t="shared" si="47"/>
-        <v>461</v>
-      </c>
-      <c r="N32" s="7"/>
+        <f t="shared" si="41"/>
+        <v>484</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="41"/>
+        <v>92</v>
+      </c>
       <c r="O32" s="7"/>
       <c r="P32" s="7">
-        <f t="shared" ref="P32:T32" si="48">P30-P31</f>
-        <v>1700</v>
+        <f t="shared" ref="P32:T32" si="42">P30+P31</f>
+        <v>1703</v>
       </c>
       <c r="Q32" s="7">
-        <f t="shared" si="48"/>
-        <v>1975</v>
+        <f t="shared" si="42"/>
+        <v>1977</v>
       </c>
       <c r="R32" s="7">
-        <f t="shared" si="48"/>
-        <v>431</v>
+        <f t="shared" si="42"/>
+        <v>442</v>
       </c>
       <c r="S32" s="7">
-        <f t="shared" si="48"/>
-        <v>2117</v>
+        <f t="shared" si="42"/>
+        <v>2159</v>
       </c>
       <c r="T32" s="7">
-        <f t="shared" si="48"/>
-        <v>612</v>
+        <f t="shared" si="42"/>
+        <v>638</v>
       </c>
       <c r="U32" s="7">
-        <f>U30-U31</f>
-        <v>-77</v>
+        <f>U30+U31</f>
+        <v>-16</v>
       </c>
       <c r="V32" s="7">
-        <f>V30-V31</f>
-        <v>69</v>
-      </c>
-      <c r="W32" s="7"/>
+        <f>V30+V31</f>
+        <v>833</v>
+      </c>
+      <c r="W32" s="7">
+        <f>W30+W31</f>
+        <v>1385</v>
+      </c>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
@@ -3361,28 +3550,71 @@
       <c r="AB32" s="7"/>
     </row>
     <row r="33" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
+      <c r="B33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="7">
+        <v>9</v>
+      </c>
+      <c r="D33" s="7">
+        <v>11</v>
+      </c>
+      <c r="E33" s="7">
+        <v>21</v>
+      </c>
+      <c r="F33" s="7">
+        <v>-379</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>16</v>
+      </c>
+      <c r="I33" s="7">
+        <v>33</v>
+      </c>
+      <c r="J33" s="7">
+        <v>-39</v>
+      </c>
+      <c r="K33" s="7">
+        <v>1</v>
+      </c>
+      <c r="L33" s="7">
+        <v>11</v>
+      </c>
+      <c r="M33" s="7">
+        <v>23</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
       <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
+      <c r="P33" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>2</v>
+      </c>
+      <c r="R33" s="7">
+        <v>11</v>
+      </c>
+      <c r="S33" s="7">
+        <v>42</v>
+      </c>
+      <c r="T33" s="7">
+        <v>26</v>
+      </c>
+      <c r="U33" s="7">
+        <v>61</v>
+      </c>
+      <c r="V33" s="7">
+        <v>764</v>
+      </c>
+      <c r="W33" s="7">
+        <v>45</v>
+      </c>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
@@ -3390,745 +3622,768 @@
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="7">
+        <f t="shared" ref="C34" si="43">C32-C33</f>
+        <v>-38</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34" si="44">D32-D33</f>
+        <v>84</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34" si="45">E32-E33</f>
+        <v>260</v>
+      </c>
+      <c r="F34" s="7">
+        <f t="shared" ref="F34" si="46">F32-F33</f>
+        <v>21</v>
+      </c>
+      <c r="G34" s="7">
+        <f t="shared" ref="G34" si="47">G32-G33</f>
+        <v>170</v>
+      </c>
+      <c r="H34" s="7">
+        <f>H32-H33</f>
+        <v>190</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" ref="I34:N34" si="48">I32-I33</f>
+        <v>441</v>
+      </c>
+      <c r="J34" s="7">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="48"/>
+        <v>427</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" si="48"/>
+        <v>370</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="48"/>
+        <v>461</v>
+      </c>
+      <c r="N34" s="7">
+        <f t="shared" si="48"/>
+        <v>82</v>
+      </c>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7">
+        <f t="shared" ref="P34:T34" si="49">P32-P33</f>
+        <v>1700</v>
+      </c>
+      <c r="Q34" s="7">
+        <f t="shared" si="49"/>
+        <v>1975</v>
+      </c>
+      <c r="R34" s="7">
+        <f t="shared" si="49"/>
+        <v>431</v>
+      </c>
+      <c r="S34" s="7">
+        <f t="shared" si="49"/>
+        <v>2117</v>
+      </c>
+      <c r="T34" s="7">
+        <f t="shared" si="49"/>
+        <v>612</v>
+      </c>
+      <c r="U34" s="7">
+        <f>U32-U33</f>
+        <v>-77</v>
+      </c>
+      <c r="V34" s="7">
+        <f>V32-V33</f>
+        <v>69</v>
+      </c>
+      <c r="W34" s="7">
+        <f>W32-W33</f>
+        <v>1340</v>
+      </c>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
+      <c r="AA34" s="7"/>
+      <c r="AB34" s="7"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C36" s="4">
         <v>-0.22</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D36" s="4">
         <v>0.47</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E36" s="4">
         <v>1.4</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4">
+      <c r="F36" s="4"/>
+      <c r="G36" s="4">
         <v>0.96</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H36" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I36" s="4">
         <v>2.48</v>
       </c>
-      <c r="J34" s="4">
-        <f>+J32/J35</f>
+      <c r="J36" s="4">
+        <f>+J34/J37</f>
         <v>0.11201401626905014</v>
       </c>
-      <c r="K34" s="4">
-        <f t="shared" ref="K34:M34" si="49">+K32/K35</f>
+      <c r="K36" s="4">
+        <f t="shared" ref="K36:N36" si="50">+K34/K37</f>
         <v>2.3914992473442207</v>
       </c>
-      <c r="L34" s="4">
-        <f t="shared" si="49"/>
+      <c r="L36" s="4">
+        <f t="shared" si="50"/>
         <v>2.0722209435125509</v>
       </c>
-      <c r="M34" s="4">
-        <f t="shared" si="49"/>
+      <c r="M36" s="4">
+        <f t="shared" si="50"/>
         <v>2.581923075001606</v>
       </c>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="9">
+      <c r="N36" s="4">
+        <f t="shared" si="50"/>
+        <v>0.45923139673213176</v>
+      </c>
+      <c r="O36" s="4"/>
+      <c r="P36" s="9">
         <v>8.44</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="Q36" s="9">
         <v>10</v>
       </c>
-      <c r="R34" s="9">
+      <c r="R36" s="9">
         <v>2.31</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S36" s="9">
         <v>7.47</v>
       </c>
-      <c r="T34" s="9">
+      <c r="T36" s="9">
         <v>1.25</v>
       </c>
-      <c r="U34" s="9">
-        <f>+U32/U35</f>
+      <c r="U36" s="9">
+        <f>+U34/U37</f>
         <v>-0.43125396263584304</v>
       </c>
-      <c r="V34" s="9">
-        <f>+V32/V35</f>
+      <c r="V36" s="9">
+        <f>+V34/V37</f>
         <v>0.38644835612822298</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="4">
-        <f t="shared" ref="C35:I35" si="50">C32/C34</f>
-        <v>172.72727272727272</v>
-      </c>
-      <c r="D35" s="4">
-        <f t="shared" si="50"/>
-        <v>178.72340425531917</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" si="50"/>
-        <v>185.71428571428572</v>
-      </c>
-      <c r="F35" s="4" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="4">
-        <f t="shared" si="50"/>
-        <v>177.08333333333334</v>
-      </c>
-      <c r="H35" s="4">
-        <f t="shared" si="50"/>
-        <v>174.31192660550457</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="50"/>
-        <v>177.82258064516128</v>
-      </c>
-      <c r="J35" s="4">
-        <v>178.54908399999999</v>
-      </c>
-      <c r="K35" s="4">
-        <v>178.54908399999999</v>
-      </c>
-      <c r="L35" s="4">
-        <v>178.55238900000001</v>
-      </c>
-      <c r="M35" s="4">
-        <v>178.54908399999999</v>
-      </c>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4">
-        <f t="shared" ref="P35:T35" si="51">P32/P34</f>
-        <v>201.4218009478673</v>
-      </c>
-      <c r="Q35" s="4">
-        <f t="shared" si="51"/>
-        <v>197.5</v>
-      </c>
-      <c r="R35" s="4">
-        <f t="shared" si="51"/>
-        <v>186.58008658008657</v>
-      </c>
-      <c r="S35" s="4">
-        <f t="shared" si="51"/>
-        <v>283.40026773761713</v>
-      </c>
-      <c r="T35" s="4">
-        <f t="shared" si="51"/>
-        <v>489.6</v>
-      </c>
-      <c r="U35" s="4">
-        <v>178.54908399999999</v>
-      </c>
-      <c r="V35" s="4">
-        <v>178.54908399999999</v>
-      </c>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
+      <c r="W36" s="9">
+        <f>+W34/W37</f>
+        <v>7.5045130685494703</v>
+      </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="10">
-        <f t="shared" ref="G37:I38" si="52">+G3/C3-1</f>
-        <v>1.4833127317676054E-2</v>
-      </c>
-      <c r="H37" s="10">
+        <v>46</v>
+      </c>
+      <c r="C37" s="4">
+        <f t="shared" ref="C37:I37" si="51">C34/C36</f>
+        <v>172.72727272727272</v>
+      </c>
+      <c r="D37" s="4">
+        <f t="shared" si="51"/>
+        <v>178.72340425531917</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="51"/>
+        <v>185.71428571428572</v>
+      </c>
+      <c r="F37" s="4" t="e">
+        <f t="shared" si="51"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G37" s="4">
+        <f t="shared" si="51"/>
+        <v>177.08333333333334</v>
+      </c>
+      <c r="H37" s="4">
+        <f t="shared" si="51"/>
+        <v>174.31192660550457</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="51"/>
+        <v>177.82258064516128</v>
+      </c>
+      <c r="J37" s="4">
+        <v>178.54908399999999</v>
+      </c>
+      <c r="K37" s="4">
+        <v>178.54908399999999</v>
+      </c>
+      <c r="L37" s="4">
+        <v>178.55238900000001</v>
+      </c>
+      <c r="M37" s="4">
+        <v>178.54908399999999</v>
+      </c>
+      <c r="N37" s="4">
+        <f>+W37</f>
+        <v>178.55922000000001</v>
+      </c>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4">
+        <f t="shared" ref="P37:T37" si="52">P34/P36</f>
+        <v>201.4218009478673</v>
+      </c>
+      <c r="Q37" s="4">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="10">
+        <v>197.5</v>
+      </c>
+      <c r="R37" s="4">
         <f t="shared" si="52"/>
-        <v>3.5220125786163514E-2</v>
-      </c>
-      <c r="J37" s="10">
-        <f>+J3/F3-1</f>
-        <v>7.2115384615385469E-3</v>
-      </c>
-      <c r="K37" s="10">
-        <f t="shared" ref="K37:N38" si="53">+K3/G3-1</f>
-        <v>1.8270401948842885E-2</v>
-      </c>
-      <c r="L37" s="10">
-        <f t="shared" si="53"/>
-        <v>4.7146401985111552E-2</v>
-      </c>
-      <c r="M37" s="10">
-        <f t="shared" si="53"/>
-        <v>5.2247873633049835E-2</v>
-      </c>
-      <c r="N37" s="10">
-        <f t="shared" si="53"/>
-        <v>-1</v>
-      </c>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="10" t="e">
-        <f t="shared" ref="Q37:U37" si="54">+Q3/P3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R37" s="10" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S37" s="10" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T37" s="10" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U37" s="10" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V37" s="10">
-        <f>+V3/U3-1</f>
-        <v>7.2115384615385469E-3</v>
+        <v>186.58008658008657</v>
+      </c>
+      <c r="S37" s="4">
+        <f t="shared" si="52"/>
+        <v>283.40026773761713</v>
+      </c>
+      <c r="T37" s="4">
+        <f t="shared" si="52"/>
+        <v>489.6</v>
+      </c>
+      <c r="U37" s="4">
+        <v>178.54908399999999</v>
+      </c>
+      <c r="V37" s="4">
+        <v>178.54908399999999</v>
+      </c>
+      <c r="W37" s="4">
+        <v>178.55922000000001</v>
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="10">
-        <f t="shared" si="52"/>
-        <v>4.9147442326980872E-2</v>
-      </c>
-      <c r="H38" s="10">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="10">
-        <f t="shared" si="52"/>
-        <v>-1.5525114155251152E-2</v>
-      </c>
-      <c r="J38" s="10">
-        <f t="shared" ref="J38" si="55">+J4/F4-1</f>
-        <v>6.2075654704170757E-2</v>
-      </c>
-      <c r="K38" s="10">
-        <f t="shared" si="53"/>
-        <v>4.8757170172084141E-2</v>
-      </c>
-      <c r="L38" s="10">
-        <f t="shared" si="53"/>
-        <v>3.3898305084745672E-2</v>
-      </c>
-      <c r="M38" s="10">
-        <f t="shared" si="53"/>
-        <v>3.4322820037105739E-2</v>
-      </c>
-      <c r="N38" s="10">
-        <f t="shared" si="53"/>
-        <v>-1</v>
-      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
-      <c r="Q38" s="10" t="e">
-        <f t="shared" ref="Q38:U38" si="56">+Q4/P4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R38" s="10" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S38" s="10" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T38" s="10" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U38" s="10" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V38" s="10">
-        <f>+V4/U4-1</f>
-        <v>6.2075654704170757E-2</v>
-      </c>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
     </row>
     <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="10">
-        <f t="shared" ref="G39:I45" si="57">+G7/C7-1</f>
-        <v>0.14844267726971494</v>
+        <f>+G3/C3-1</f>
+        <v>1.4833127317676054E-2</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="57"/>
-        <v>0.20100502512562812</v>
+        <f>+H3/D3-1</f>
+        <v>0</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="57"/>
-        <v>0.18763796909492281</v>
+        <f>+I3/E3-1</f>
+        <v>3.5220125786163514E-2</v>
       </c>
       <c r="J39" s="10">
-        <f>+J7/F7-1</f>
-        <v>0.26277897768178549</v>
+        <f>+J3/F3-1</f>
+        <v>7.2115384615385469E-3</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" ref="K39:N45" si="58">+K7/G7-1</f>
-        <v>0.14598961338718985</v>
+        <f>+K3/G3-1</f>
+        <v>1.8270401948842885E-2</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="58"/>
-        <v>4.4456066945606665E-2</v>
+        <f>+L3/H3-1</f>
+        <v>4.7146401985111552E-2</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="58"/>
-        <v>8.1784386617100413E-2</v>
+        <f>+M3/I3-1</f>
+        <v>5.2247873633049835E-2</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N3/J3-1</f>
+        <v>5.7279236276849721E-2</v>
       </c>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
       <c r="Q39" s="10" t="e">
-        <f t="shared" ref="Q39:U45" si="59">+Q7/P7-1</f>
+        <f t="shared" ref="Q39:U39" si="53">+Q3/P3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R39" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S39" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T39" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U39" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V39" s="10">
-        <f>+V7/U7-1</f>
-        <v>0.19819105046017138</v>
+        <f>+V3/U3-1</f>
+        <v>7.2115384615385469E-3</v>
+      </c>
+      <c r="W39" s="10">
+        <f>+W3/V3-1</f>
+        <v>5.7279236276849721E-2</v>
       </c>
     </row>
     <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="10">
-        <f t="shared" si="57"/>
-        <v>-4.6728971962616828E-2</v>
+        <f>+G4/C4-1</f>
+        <v>4.9147442326980872E-2</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="57"/>
-        <v>-6.9335239456754794E-2</v>
+        <f>+H4/D4-1</f>
+        <v>0</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="57"/>
-        <v>-8.2210242587601123E-2</v>
+        <f>+I4/E4-1</f>
+        <v>-1.5525114155251152E-2</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" ref="J40:J45" si="60">+J8/F8-1</f>
-        <v>0.15789473684210531</v>
+        <f t="shared" ref="J40" si="54">+J4/F4-1</f>
+        <v>6.2075654704170757E-2</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="58"/>
-        <v>5.525846702317283E-2</v>
+        <f>+K4/G4-1</f>
+        <v>4.8757170172084141E-2</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="58"/>
-        <v>2.8417818740399392E-2</v>
+        <f>+L4/H4-1</f>
+        <v>3.3898305084745672E-2</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="58"/>
-        <v>-4.6989720998531603E-2</v>
+        <f>+M4/I4-1</f>
+        <v>3.4322820037105739E-2</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N4/J4-1</f>
+        <v>3.7442922374429255E-2</v>
       </c>
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
       <c r="Q40" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="Q40:U40" si="55">+Q4/P4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R40" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S40" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T40" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U40" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" ref="V40:V45" si="61">+V8/U8-1</f>
-        <v>-1.7436290477102934E-2</v>
+        <f>+V4/U4-1</f>
+        <v>6.2075654704170757E-2</v>
+      </c>
+      <c r="W40" s="10">
+        <f>+W4/V4-1</f>
+        <v>3.7442922374429255E-2</v>
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="10">
-        <f t="shared" si="57"/>
-        <v>1.4705882352941124E-2</v>
+        <f>+G7/C7-1</f>
+        <v>0.14844267726971494</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="57"/>
-        <v>7.3107049608355013E-2</v>
+        <f>+H7/D7-1</f>
+        <v>0.20100502512562812</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="57"/>
-        <v>8.7356321839080486E-2</v>
+        <f>+I7/E7-1</f>
+        <v>0.18763796909492281</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="60"/>
-        <v>0.18507462686567155</v>
+        <f>+J7/F7-1</f>
+        <v>0.26277897768178549</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="58"/>
-        <v>0.14715719063545141</v>
+        <f>+K7/G7-1</f>
+        <v>0.14598961338718985</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="58"/>
-        <v>-2.9197080291970767E-2</v>
+        <f>+L7/H7-1</f>
+        <v>4.4456066945606665E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="58"/>
-        <v>1.0570824524311906E-3</v>
+        <f>+M7/I7-1</f>
+        <v>8.1784386617100413E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N7/J7-1</f>
+        <v>4.0478905359178974E-2</v>
       </c>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
       <c r="Q41" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+Q7/P7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R41" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+R7/Q7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S41" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+S7/R7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T41" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+T7/S7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U41" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+U7/T7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="61"/>
-        <v>8.4326018808777325E-2</v>
+        <f>+V7/U7-1</f>
+        <v>0.19819105046017138</v>
+      </c>
+      <c r="W41" s="10">
+        <f>+W7/V7-1</f>
+        <v>7.7473182359952375E-2</v>
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="10">
-        <f t="shared" si="57"/>
-        <v>5.9523809523809534E-2</v>
+        <f>+G8/C8-1</f>
+        <v>-4.6728971962616828E-2</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="57"/>
-        <v>0.24833333333333329</v>
+        <f>+H8/D8-1</f>
+        <v>-6.9335239456754794E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="57"/>
-        <v>9.1127098321343025E-2</v>
+        <f>+I8/E8-1</f>
+        <v>-8.2210242587601123E-2</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="60"/>
-        <v>0.26344086021505375</v>
+        <f>+J8/F8-1</f>
+        <v>0.15789473684210531</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="58"/>
-        <v>1.74438202247191</v>
+        <f>+K8/G8-1</f>
+        <v>5.525846702317283E-2</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="58"/>
-        <v>1.4272363150867822</v>
+        <f>+L8/H8-1</f>
+        <v>2.8417818740399392E-2</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="58"/>
-        <v>1.2120879120879122</v>
+        <f>+M8/I8-1</f>
+        <v>-4.6989720998531603E-2</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N8/J8-1</f>
+        <v>-5.663189269746649E-2</v>
       </c>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+Q8/P8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R42" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+R8/Q8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S42" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+S8/R8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T42" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+T8/S8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U42" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+U8/T8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="61"/>
-        <v>0.16140350877192988</v>
+        <f>+V8/U8-1</f>
+        <v>-1.7436290477102934E-2</v>
+      </c>
+      <c r="W42" s="10">
+        <f>+W8/V8-1</f>
+        <v>-7.9953198127925562E-3</v>
       </c>
     </row>
     <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="10">
-        <f t="shared" si="57"/>
-        <v>7.1452199801521621E-2</v>
+        <f>+G9/C9-1</f>
+        <v>1.4705882352941124E-2</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="57"/>
-        <v>0.15183752417794971</v>
+        <f>+H9/D9-1</f>
+        <v>7.3107049608355013E-2</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="57"/>
-        <v>0.10289389067524124</v>
+        <f>+I9/E9-1</f>
+        <v>8.7356321839080486E-2</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.3356973995271868</v>
+        <f>+J9/F9-1</f>
+        <v>0.18507462686567155</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="58"/>
-        <v>0.16085211485026241</v>
+        <f>+K9/G9-1</f>
+        <v>0.14715719063545141</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="58"/>
-        <v>-0.30702490904002244</v>
+        <f>+L9/H9-1</f>
+        <v>-2.9197080291970767E-2</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" si="58"/>
-        <v>-6.095944871455039E-3</v>
+        <f>+M9/I9-1</f>
+        <v>1.0570824524311906E-3</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N9/J9-1</f>
+        <v>6.9269521410579404E-2</v>
       </c>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+Q9/P9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R43" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+R9/Q9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S43" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+S9/R9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T43" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+T9/S9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U43" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+U9/T9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.15658362989323837</v>
+        <f>+V9/U9-1</f>
+        <v>8.4326018808777325E-2</v>
+      </c>
+      <c r="W43" s="10">
+        <f>+W9/V9-1</f>
+        <v>4.7412546978895742E-2</v>
       </c>
     </row>
     <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="10">
-        <f t="shared" si="57"/>
-        <v>-1.3605442176870763E-2</v>
+        <f>+G10/C10-1</f>
+        <v>5.9523809523809534E-2</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="57"/>
-        <v>3.0501089324618702E-2</v>
+        <f>+H10/D10-1</f>
+        <v>0.24833333333333329</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="57"/>
-        <v>2.6051188299817118E-2</v>
+        <f>+I10/E10-1</f>
+        <v>9.1127098321343025E-2</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="60"/>
-        <v>0.10140562248995977</v>
+        <f>+J10/F10-1</f>
+        <v>0.26344086021505375</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="58"/>
-        <v>4.403183023872681E-2</v>
+        <f>+K10/G10-1</f>
+        <v>0.2219101123595506</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="58"/>
-        <v>7.2410147991543328E-2</v>
+        <f>+L10/H10-1</f>
+        <v>1.735647530040052E-2</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="58"/>
-        <v>6.1469933184855163E-2</v>
+        <f>+M10/I10-1</f>
+        <v>2.7472527472527375E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" si="58"/>
-        <v>-1</v>
+        <f>+N10/J10-1</f>
+        <v>3.1914893617022155E-3</v>
       </c>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
       <c r="Q44" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+Q10/P10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R44" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+R10/Q10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S44" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+S10/R10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T44" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+T10/S10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U44" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f>+U10/T10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V44" s="10">
-        <f t="shared" si="61"/>
-        <v>4.5824847250509171E-2</v>
+        <f>+V10/U10-1</f>
+        <v>0.16140350877192988</v>
+      </c>
+      <c r="W44" s="10">
+        <f>+W10/V10-1</f>
+        <v>6.042296072507547E-2</v>
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="10">
-        <f t="shared" si="57"/>
-        <v>-3.5294117647058809E-2</v>
+        <f t="shared" ref="G45:I47" si="56">+G13/C13-1</f>
+        <v>7.1452199801521621E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="57"/>
-        <v>-8.6419753086419804E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.15183752417794971</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="57"/>
-        <v>7.9487179487179427E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.10289389067524124</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="60"/>
-        <v>7.9545454545454586E-2</v>
+        <f t="shared" ref="J45:J47" si="57">+J13/F13-1</f>
+        <v>0.3356973995271868</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="58"/>
-        <v>0.29268292682926833</v>
+        <f t="shared" ref="K45:N47" si="58">+K13/G13-1</f>
+        <v>0.16085211485026241</v>
       </c>
       <c r="L45" s="10">
         <f t="shared" si="58"/>
-        <v>0.2081081081081082</v>
+        <v>-0.30702490904002244</v>
       </c>
       <c r="M45" s="10">
         <f t="shared" si="58"/>
-        <v>0.178147268408551</v>
+        <v>-6.095944871455039E-3</v>
       </c>
       <c r="N45" s="10">
         <f t="shared" si="58"/>
-        <v>-1</v>
+        <v>0.25250737463126849</v>
       </c>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="10" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="Q45:U47" si="59">+Q13/P13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R45" s="10" t="e">
@@ -4148,450 +4403,572 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V45" s="10">
-        <f t="shared" si="61"/>
-        <v>7.3924731182795078E-3</v>
+        <f t="shared" ref="V45:W47" si="60">+V13/U13-1</f>
+        <v>0.15658362989323837</v>
+      </c>
+      <c r="W45" s="10">
+        <f t="shared" si="60"/>
+        <v>1.8389982110912362E-2</v>
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="12">
-        <f>G14/C14-1</f>
-        <v>3.4888130451270483E-2</v>
-      </c>
-      <c r="H46" s="12">
-        <f t="shared" ref="H46:J46" si="62">H14/D14-1</f>
-        <v>8.9650009358038574E-2</v>
-      </c>
-      <c r="I46" s="12">
-        <f t="shared" si="62"/>
-        <v>7.3178863143857242E-2</v>
-      </c>
-      <c r="J46" s="12">
-        <f t="shared" si="62"/>
-        <v>0.23960931005818797</v>
-      </c>
-      <c r="K46" s="12">
-        <f t="shared" ref="K46" si="63">K14/G14-1</f>
-        <v>0.1273360205203371</v>
-      </c>
-      <c r="L46" s="12">
-        <f t="shared" ref="L46" si="64">L14/H14-1</f>
-        <v>2.2329096530401937E-2</v>
-      </c>
-      <c r="M46" s="12">
-        <f t="shared" ref="M46" si="65">M14/I14-1</f>
-        <v>2.982292637465056E-2</v>
-      </c>
-      <c r="N46" s="12">
-        <f t="shared" ref="N46" si="66">N14/J14-1</f>
-        <v>-1</v>
+      <c r="B46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="10">
+        <f t="shared" si="56"/>
+        <v>-1.3605442176870763E-2</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="56"/>
+        <v>3.0501089324618702E-2</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="56"/>
+        <v>2.6051188299817118E-2</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="57"/>
+        <v>0.10140562248995977</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="58"/>
+        <v>4.403183023872681E-2</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="58"/>
+        <v>7.2410147991543328E-2</v>
+      </c>
+      <c r="M46" s="10">
+        <f t="shared" si="58"/>
+        <v>6.1469933184855163E-2</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="58"/>
+        <v>8.6599817684594349E-2</v>
       </c>
       <c r="O46" s="4"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10">
-        <f t="shared" ref="Q46:T46" si="67">Q14/P14-1</f>
-        <v>7.8713210130047839E-2</v>
-      </c>
-      <c r="R46" s="10">
-        <f t="shared" si="67"/>
-        <v>-0.22017766497461932</v>
-      </c>
-      <c r="S46" s="10">
-        <f t="shared" si="67"/>
-        <v>0.15183075671277457</v>
-      </c>
-      <c r="T46" s="10">
-        <f t="shared" si="67"/>
-        <v>6.0139399076952094E-2</v>
-      </c>
-      <c r="U46" s="10">
-        <f>U14/T14-1</f>
-        <v>-4.8154235706987736E-2</v>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R46" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S46" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U46" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="V46" s="10">
-        <f>V14/U14-1</f>
-        <v>0.10528772109954732</v>
+        <f t="shared" si="60"/>
+        <v>4.5824847250509171E-2</v>
+      </c>
+      <c r="W46" s="10">
+        <f t="shared" si="60"/>
+        <v>6.669912366114894E-2</v>
       </c>
     </row>
     <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="10">
+        <f t="shared" si="56"/>
+        <v>-3.5294117647058809E-2</v>
+      </c>
+      <c r="H47" s="10">
+        <f t="shared" si="56"/>
+        <v>-8.6419753086419804E-2</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="56"/>
+        <v>7.9487179487179427E-2</v>
+      </c>
+      <c r="J47" s="10">
+        <f t="shared" si="57"/>
+        <v>7.9545454545454586E-2</v>
+      </c>
+      <c r="K47" s="10">
+        <f t="shared" si="58"/>
+        <v>0.29268292682926833</v>
+      </c>
+      <c r="L47" s="10">
+        <f t="shared" si="58"/>
+        <v>0.2081081081081082</v>
+      </c>
+      <c r="M47" s="10">
+        <f t="shared" si="58"/>
+        <v>0.178147268408551</v>
+      </c>
+      <c r="N47" s="10">
+        <f t="shared" si="58"/>
+        <v>0.17894736842105252</v>
+      </c>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R47" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S47" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U47" s="10" t="e">
+        <f t="shared" si="59"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V47" s="10">
+        <f t="shared" si="60"/>
+        <v>7.3924731182795078E-3</v>
+      </c>
+      <c r="W47" s="10">
+        <f t="shared" si="60"/>
+        <v>0.21080720480320214</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="12">
+        <f>G16/C16-1</f>
+        <v>3.4888130451270483E-2</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" ref="H48:J48" si="61">H16/D16-1</f>
+        <v>8.9650009358038574E-2</v>
+      </c>
+      <c r="I48" s="12">
+        <f t="shared" si="61"/>
+        <v>7.3178863143857242E-2</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="61"/>
+        <v>0.23960931005818797</v>
+      </c>
+      <c r="K48" s="12">
+        <f t="shared" ref="K48" si="62">K16/G16-1</f>
+        <v>0.1273360205203371</v>
+      </c>
+      <c r="L48" s="12">
+        <f t="shared" ref="L48" si="63">L16/H16-1</f>
+        <v>2.2329096530401937E-2</v>
+      </c>
+      <c r="M48" s="12">
+        <f t="shared" ref="M48" si="64">M16/I16-1</f>
+        <v>2.982292637465056E-2</v>
+      </c>
+      <c r="N48" s="12">
+        <f t="shared" ref="N48" si="65">N16/J16-1</f>
+        <v>1.8608549874266522E-2</v>
+      </c>
+      <c r="O48" s="4"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="12">
+        <f t="shared" ref="Q48:T48" si="66">Q16/P16-1</f>
+        <v>7.8713210130047839E-2</v>
+      </c>
+      <c r="R48" s="12">
+        <f t="shared" si="66"/>
+        <v>-0.22017766497461932</v>
+      </c>
+      <c r="S48" s="12">
+        <f t="shared" si="66"/>
+        <v>0.15183075671277457</v>
+      </c>
+      <c r="T48" s="12">
+        <f t="shared" si="66"/>
+        <v>6.0139399076952094E-2</v>
+      </c>
+      <c r="U48" s="12">
+        <f>U16/T16-1</f>
+        <v>-4.8154235706987736E-2</v>
+      </c>
+      <c r="V48" s="12">
+        <f>V16/U16-1</f>
+        <v>0.10528772109954732</v>
+      </c>
+      <c r="W48" s="12">
+        <f>W16/V16-1</f>
+        <v>4.7629101042942157E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B49" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="10">
-        <f t="shared" ref="C47:G47" si="68">C16/C14</f>
+      <c r="C49" s="10">
+        <f t="shared" ref="C49:G49" si="67">C18/C16</f>
         <v>0.44804702313234734</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D49" s="10">
+        <f t="shared" si="67"/>
+        <v>0.50870297585626056</v>
+      </c>
+      <c r="E49" s="10">
+        <f t="shared" si="67"/>
+        <v>0.49258209701616934</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="67"/>
+        <v>0.44638403990024939</v>
+      </c>
+      <c r="G49" s="10">
+        <f t="shared" si="67"/>
+        <v>0.51227555881275189</v>
+      </c>
+      <c r="H49" s="10">
+        <f>H18/H16</f>
+        <v>0.50824458948814843</v>
+      </c>
+      <c r="I49" s="10">
+        <f t="shared" ref="I49:J49" si="68">I18/I16</f>
+        <v>0.51273687480584029</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="68"/>
-        <v>0.50870297585626056</v>
-      </c>
-      <c r="E47" s="10">
-        <f t="shared" si="68"/>
-        <v>0.49258209701616934</v>
-      </c>
-      <c r="F47" s="10">
-        <f t="shared" si="68"/>
-        <v>0.44638403990024939</v>
-      </c>
-      <c r="G47" s="10">
-        <f t="shared" si="68"/>
-        <v>0.51227555881275189</v>
-      </c>
-      <c r="H47" s="10">
-        <f>H16/H14</f>
-        <v>0.50824458948814843</v>
-      </c>
-      <c r="I47" s="10">
-        <f t="shared" ref="I47:J47" si="69">I16/I14</f>
-        <v>0.51273687480584029</v>
-      </c>
-      <c r="J47" s="10">
+        <v>0.49790444258172672</v>
+      </c>
+      <c r="K49" s="10">
+        <f t="shared" ref="K49:N49" si="69">K18/K16</f>
+        <v>0.52088412156671537</v>
+      </c>
+      <c r="L49" s="10">
         <f t="shared" si="69"/>
-        <v>0.49790444258172672</v>
-      </c>
-      <c r="K47" s="10">
-        <f t="shared" ref="K47:N47" si="70">K16/K14</f>
-        <v>0.52088412156671537</v>
-      </c>
-      <c r="L47" s="10">
-        <f t="shared" si="70"/>
         <v>0.51696908602150538</v>
       </c>
-      <c r="M47" s="10">
-        <f t="shared" si="70"/>
+      <c r="M49" s="10">
+        <f t="shared" si="69"/>
         <v>0.51809954751131226</v>
       </c>
-      <c r="N47" s="10" t="e">
-        <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O47" s="4"/>
-      <c r="P47" s="10">
-        <f t="shared" ref="P47:T47" si="71">P16/P14</f>
-        <v>0.51850330823636781</v>
-      </c>
-      <c r="Q47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.52000846023688663</v>
-      </c>
-      <c r="R47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.50024410089503657</v>
-      </c>
-      <c r="S47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.50696995384760291</v>
-      </c>
-      <c r="T47" s="10">
-        <f t="shared" si="71"/>
-        <v>0.47283550264315222</v>
-      </c>
-      <c r="U47" s="10">
-        <f>U16/U14</f>
-        <v>0.47524151771129886</v>
-      </c>
-      <c r="V47" s="10">
-        <f>V16/V14</f>
-        <v>0.5077481737955496</v>
-      </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="10">
-        <f t="shared" ref="C48:G48" si="72">C23/C14</f>
-        <v>1.1376564277588168E-2</v>
-      </c>
-      <c r="D48" s="10">
-        <f t="shared" si="72"/>
-        <v>3.2753134942915964E-2</v>
-      </c>
-      <c r="E48" s="10">
-        <f t="shared" si="72"/>
-        <v>6.8344724120686776E-2</v>
-      </c>
-      <c r="F48" s="10">
-        <f t="shared" si="72"/>
-        <v>-7.813798836242726E-2</v>
-      </c>
-      <c r="G48" s="10">
-        <f t="shared" si="72"/>
-        <v>6.1561011359472333E-2</v>
-      </c>
-      <c r="H48" s="10">
-        <f>H23/H14</f>
-        <v>5.960151150807283E-2</v>
-      </c>
-      <c r="I48" s="10">
-        <f t="shared" ref="I48:J48" si="73">I23/I14</f>
-        <v>9.2575333954644304E-2</v>
-      </c>
-      <c r="J48" s="10">
-        <f t="shared" si="73"/>
-        <v>9.5557418273260683E-3</v>
-      </c>
-      <c r="K48" s="10">
-        <f t="shared" ref="K48:N48" si="74">K23/K14</f>
-        <v>9.8976109215017066E-2</v>
-      </c>
-      <c r="L48" s="10">
-        <f t="shared" si="74"/>
-        <v>9.1901881720430109E-2</v>
-      </c>
-      <c r="M48" s="10">
-        <f t="shared" si="74"/>
-        <v>0.11101055806938159</v>
-      </c>
-      <c r="N48" s="10" t="e">
-        <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O48" s="4"/>
-      <c r="P48" s="10">
-        <f t="shared" ref="P48:T48" si="75">P23/P14</f>
-        <v>0.1080082135523614</v>
-      </c>
-      <c r="Q48" s="10">
-        <f t="shared" si="75"/>
-        <v>0.11252115059221658</v>
-      </c>
-      <c r="R48" s="10">
-        <f t="shared" si="75"/>
-        <v>4.0412259289395173E-2</v>
-      </c>
-      <c r="S48" s="10">
-        <f t="shared" si="75"/>
-        <v>9.3576339832344355E-2</v>
-      </c>
-      <c r="T48" s="10">
-        <f t="shared" si="75"/>
-        <v>2.9718804140198125E-2</v>
-      </c>
-      <c r="U48" s="10">
-        <f>U23/U14</f>
-        <v>1.2460913800345358E-2</v>
-      </c>
-      <c r="V48" s="10">
-        <f>V23/V14</f>
-        <v>5.6327323396529155E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C49" s="10">
-        <f t="shared" ref="C49:G49" si="76">C32/C14</f>
-        <v>-7.2051573758058398E-3</v>
-      </c>
-      <c r="D49" s="10">
-        <f t="shared" si="76"/>
-        <v>1.5721504772599662E-2</v>
-      </c>
-      <c r="E49" s="10">
-        <f t="shared" si="76"/>
-        <v>4.3340556759459907E-2</v>
-      </c>
-      <c r="F49" s="10">
-        <f t="shared" si="76"/>
-        <v>4.3640897755610969E-3</v>
-      </c>
-      <c r="G49" s="10">
-        <f t="shared" si="76"/>
-        <v>3.1146940271161598E-2</v>
-      </c>
-      <c r="H49" s="10">
-        <f>H32/H14</f>
-        <v>3.2634833390587425E-2</v>
-      </c>
-      <c r="I49" s="10">
-        <f t="shared" ref="I49:J49" si="77">I32/I14</f>
-        <v>6.8499534016775401E-2</v>
-      </c>
-      <c r="J49" s="10">
-        <f t="shared" si="77"/>
-        <v>3.3528918692372171E-3</v>
-      </c>
-      <c r="K49" s="10">
-        <f t="shared" ref="K49:N49" si="78">K32/K14</f>
-        <v>6.9397042093287828E-2</v>
-      </c>
-      <c r="L49" s="10">
-        <f t="shared" si="78"/>
-        <v>6.2163978494623656E-2</v>
-      </c>
-      <c r="M49" s="10">
-        <f t="shared" si="78"/>
-        <v>6.953242835595777E-2</v>
-      </c>
-      <c r="N49" s="10" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
+      <c r="N49" s="10">
+        <f t="shared" si="69"/>
+        <v>0.50822909809084926</v>
       </c>
       <c r="O49" s="4"/>
       <c r="P49" s="10">
-        <f t="shared" ref="P49:T49" si="79">P32/P14</f>
-        <v>7.7572438968742871E-2</v>
+        <f t="shared" ref="P49:T49" si="70">P18/P16</f>
+        <v>0.51850330823636781</v>
       </c>
       <c r="Q49" s="10">
-        <f t="shared" si="79"/>
-        <v>8.3544839255499159E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.52000846023688663</v>
       </c>
       <c r="R49" s="10">
-        <f t="shared" si="79"/>
-        <v>2.3379441280173583E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.50024410089503657</v>
       </c>
       <c r="S49" s="10">
-        <f t="shared" si="79"/>
-        <v>9.9698596590373931E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.50696995384760291</v>
       </c>
       <c r="T49" s="10">
-        <f t="shared" si="79"/>
-        <v>2.7186708720181245E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.47283550264315222</v>
       </c>
       <c r="U49" s="10">
-        <f>U32/U14</f>
-        <v>-3.5935968637700096E-3</v>
+        <f>U18/U16</f>
+        <v>0.47524151771129886</v>
       </c>
       <c r="V49" s="10">
-        <f>V32/V14</f>
-        <v>2.9134822446480598E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
+        <f>V18/V16</f>
+        <v>0.5077481737955496</v>
+      </c>
+      <c r="W49" s="10">
+        <f>W18/W16</f>
+        <v>0.51610172907178264</v>
+      </c>
+    </row>
+    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" ref="C50:G50" si="80">C27/C26</f>
-        <v>1.71875</v>
+        <f t="shared" ref="C50:G50" si="71">C25/C16</f>
+        <v>1.1376564277588168E-2</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="80"/>
-        <v>0.21951219512195122</v>
+        <f t="shared" si="71"/>
+        <v>3.2753134942915964E-2</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="80"/>
-        <v>0.16871165644171779</v>
+        <f t="shared" si="71"/>
+        <v>6.8344724120686776E-2</v>
       </c>
       <c r="F50" s="10">
-        <f t="shared" si="80"/>
-        <v>3.3816425120772944E-2</v>
+        <f t="shared" si="71"/>
+        <v>-7.813798836242726E-2</v>
       </c>
       <c r="G50" s="10">
-        <f t="shared" si="80"/>
-        <v>0.30204081632653063</v>
+        <f t="shared" si="71"/>
+        <v>6.1561011359472333E-2</v>
       </c>
       <c r="H50" s="10">
-        <f>H27/H26</f>
-        <v>0.30491803278688523</v>
+        <f>H25/H16</f>
+        <v>5.960151150807283E-2</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" ref="I50:J50" si="81">I27/I26</f>
-        <v>0.22166666666666668</v>
+        <f t="shared" ref="I50:J50" si="72">I25/I16</f>
+        <v>9.2575333954644304E-2</v>
       </c>
       <c r="J50" s="10">
-        <f t="shared" si="81"/>
-        <v>7.1428571428571425E-2</v>
+        <f t="shared" si="72"/>
+        <v>9.5557418273260683E-3</v>
       </c>
       <c r="K50" s="10">
-        <f t="shared" ref="K50:N50" si="82">K27/K26</f>
-        <v>0.25513698630136988</v>
+        <f t="shared" ref="K50:N50" si="73">K25/K16</f>
+        <v>9.8976109215017066E-2</v>
       </c>
       <c r="L50" s="10">
-        <f t="shared" si="82"/>
-        <v>0.23312883435582821</v>
+        <f t="shared" si="73"/>
+        <v>9.1901881720430109E-2</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" si="82"/>
-        <v>0.26</v>
-      </c>
-      <c r="N50" s="10" t="e">
-        <f t="shared" si="82"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="73"/>
+        <v>0.11101055806938159</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="73"/>
+        <v>2.6991441737985518E-2</v>
       </c>
       <c r="O50" s="4"/>
       <c r="P50" s="10">
-        <f t="shared" ref="P50:T50" si="83">P27/P26</f>
+        <f t="shared" ref="P50:T50" si="74">P25/P16</f>
+        <v>0.1080082135523614</v>
+      </c>
+      <c r="Q50" s="10">
+        <f t="shared" si="74"/>
+        <v>0.11252115059221658</v>
+      </c>
+      <c r="R50" s="10">
+        <f t="shared" si="74"/>
+        <v>4.0412259289395173E-2</v>
+      </c>
+      <c r="S50" s="10">
+        <f t="shared" si="74"/>
+        <v>9.3576339832344355E-2</v>
+      </c>
+      <c r="T50" s="10">
+        <f t="shared" si="74"/>
+        <v>2.9718804140198125E-2</v>
+      </c>
+      <c r="U50" s="10">
+        <f>U25/U16</f>
+        <v>1.2460913800345358E-2</v>
+      </c>
+      <c r="V50" s="10">
+        <f>V25/V16</f>
+        <v>5.6327323396529155E-2</v>
+      </c>
+      <c r="W50" s="10">
+        <f>W25/W16</f>
+        <v>8.2866470517109353E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="10">
+        <f t="shared" ref="C51:G51" si="75">C34/C16</f>
+        <v>-7.2051573758058398E-3</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="75"/>
+        <v>1.5721504772599662E-2</v>
+      </c>
+      <c r="E51" s="10">
+        <f t="shared" si="75"/>
+        <v>4.3340556759459907E-2</v>
+      </c>
+      <c r="F51" s="10">
+        <f t="shared" si="75"/>
+        <v>4.3640897755610969E-3</v>
+      </c>
+      <c r="G51" s="10">
+        <f t="shared" si="75"/>
+        <v>3.1146940271161598E-2</v>
+      </c>
+      <c r="H51" s="10">
+        <f>H34/H16</f>
+        <v>3.2634833390587425E-2</v>
+      </c>
+      <c r="I51" s="10">
+        <f t="shared" ref="I51:J51" si="76">I34/I16</f>
+        <v>6.8499534016775401E-2</v>
+      </c>
+      <c r="J51" s="10">
+        <f t="shared" si="76"/>
+        <v>3.3528918692372171E-3</v>
+      </c>
+      <c r="K51" s="10">
+        <f t="shared" ref="K51:N51" si="77">K34/K16</f>
+        <v>6.9397042093287828E-2</v>
+      </c>
+      <c r="L51" s="10">
+        <f t="shared" si="77"/>
+        <v>6.2163978494623656E-2</v>
+      </c>
+      <c r="M51" s="10">
+        <f t="shared" si="77"/>
+        <v>6.953242835595777E-2</v>
+      </c>
+      <c r="N51" s="10">
+        <f t="shared" si="77"/>
+        <v>1.3495720868992759E-2</v>
+      </c>
+      <c r="O51" s="4"/>
+      <c r="P51" s="10">
+        <f t="shared" ref="P51:T51" si="78">P34/P16</f>
+        <v>7.7572438968742871E-2</v>
+      </c>
+      <c r="Q51" s="10">
+        <f t="shared" si="78"/>
+        <v>8.3544839255499159E-2</v>
+      </c>
+      <c r="R51" s="10">
+        <f t="shared" si="78"/>
+        <v>2.3379441280173583E-2</v>
+      </c>
+      <c r="S51" s="10">
+        <f t="shared" si="78"/>
+        <v>9.9698596590373931E-2</v>
+      </c>
+      <c r="T51" s="10">
+        <f t="shared" si="78"/>
+        <v>2.7186708720181245E-2</v>
+      </c>
+      <c r="U51" s="10">
+        <f>U34/U16</f>
+        <v>-3.5935968637700096E-3</v>
+      </c>
+      <c r="V51" s="10">
+        <f>V34/V16</f>
+        <v>2.9134822446480598E-3</v>
+      </c>
+      <c r="W51" s="10">
+        <f>W34/W16</f>
+        <v>5.4008302768933134E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="10">
+        <f t="shared" ref="C52:G52" si="79">C29/C28</f>
+        <v>1.71875</v>
+      </c>
+      <c r="D52" s="10">
+        <f t="shared" si="79"/>
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="E52" s="10">
+        <f t="shared" si="79"/>
+        <v>0.16871165644171779</v>
+      </c>
+      <c r="F52" s="10">
+        <f t="shared" si="79"/>
+        <v>3.3816425120772944E-2</v>
+      </c>
+      <c r="G52" s="10">
+        <f t="shared" si="79"/>
+        <v>0.30204081632653063</v>
+      </c>
+      <c r="H52" s="10">
+        <f>H29/H28</f>
+        <v>0.30491803278688523</v>
+      </c>
+      <c r="I52" s="10">
+        <f t="shared" ref="I52:J52" si="80">I29/I28</f>
+        <v>0.22166666666666668</v>
+      </c>
+      <c r="J52" s="10">
+        <f t="shared" si="80"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="K52" s="10">
+        <f t="shared" ref="K52:N52" si="81">K29/K28</f>
+        <v>0.25513698630136988</v>
+      </c>
+      <c r="L52" s="10">
+        <f t="shared" si="81"/>
+        <v>0.23312883435582821</v>
+      </c>
+      <c r="M52" s="10">
+        <f t="shared" si="81"/>
+        <v>0.26</v>
+      </c>
+      <c r="N52" s="10">
+        <f t="shared" si="81"/>
+        <v>0.1134020618556701</v>
+      </c>
+      <c r="O52" s="4"/>
+      <c r="P52" s="10">
+        <f t="shared" ref="P52:T52" si="82">P29/P28</f>
         <v>0.28144720235591081</v>
       </c>
-      <c r="Q50" s="10">
-        <f t="shared" si="83"/>
+      <c r="Q52" s="10">
+        <f t="shared" si="82"/>
         <v>0.2501954652071931</v>
       </c>
-      <c r="R50" s="10">
-        <f t="shared" si="83"/>
+      <c r="R52" s="10">
+        <f t="shared" si="82"/>
         <v>0.20242214532871972</v>
       </c>
-      <c r="S50" s="10">
-        <f t="shared" si="83"/>
+      <c r="S52" s="10">
+        <f t="shared" si="82"/>
         <v>0.19427954668105774</v>
       </c>
-      <c r="T50" s="10">
-        <f t="shared" si="83"/>
+      <c r="T52" s="10">
+        <f t="shared" si="82"/>
         <v>0.34536082474226804</v>
       </c>
-      <c r="U50" s="10">
-        <f>U27/U26</f>
+      <c r="U52" s="10">
+        <f>U29/U28</f>
         <v>1.9375</v>
       </c>
-      <c r="V50" s="10">
-        <f>V27/V26</f>
+      <c r="V52" s="10">
+        <f>V29/V28</f>
         <v>0.26470588235294118</v>
       </c>
-    </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-    </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-    </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="10">
+        <f>W29/W28</f>
+        <v>0.2434065934065934</v>
+      </c>
+    </row>
+    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4613,7 +4990,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4635,7 +5012,7 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -4657,7 +5034,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -4679,7 +5056,7 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4701,7 +5078,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -4723,7 +5100,7 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -4745,7 +5122,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4767,7 +5144,7 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -4789,7 +5166,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -4811,7 +5188,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -4833,7 +5210,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -9321,10 +9698,55 @@
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
     </row>
+    <row r="268" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="C268" s="4"/>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="4"/>
+      <c r="G268" s="4"/>
+      <c r="H268" s="4"/>
+      <c r="I268" s="4"/>
+      <c r="J268" s="4"/>
+      <c r="K268" s="4"/>
+      <c r="L268" s="4"/>
+      <c r="M268" s="4"/>
+      <c r="N268" s="4"/>
+      <c r="O268" s="4"/>
+      <c r="P268" s="4"/>
+      <c r="Q268" s="4"/>
+      <c r="R268" s="4"/>
+      <c r="S268" s="4"/>
+      <c r="T268" s="4"/>
+      <c r="U268" s="4"/>
+      <c r="V268" s="4"/>
+    </row>
+    <row r="269" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="C269" s="4"/>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4"/>
+      <c r="G269" s="4"/>
+      <c r="H269" s="4"/>
+      <c r="I269" s="4"/>
+      <c r="J269" s="4"/>
+      <c r="K269" s="4"/>
+      <c r="L269" s="4"/>
+      <c r="M269" s="4"/>
+      <c r="N269" s="4"/>
+      <c r="O269" s="4"/>
+      <c r="P269" s="4"/>
+      <c r="Q269" s="4"/>
+      <c r="R269" s="4"/>
+      <c r="S269" s="4"/>
+      <c r="T269" s="4"/>
+      <c r="U269" s="4"/>
+      <c r="V269" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{777F0A24-6202-4F38-8863-082BB9D3BFF0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ADS.xlsx
+++ b/ADS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7899ACCD-F853-45ED-BD15-20652B3144EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1038B84-9B1D-4E9D-94F3-D2DD771ABF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="85">
   <si>
     <t>Adidas</t>
   </si>
@@ -299,6 +299,18 @@
   <si>
     <t>n.a.</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -316,6 +328,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -371,12 +389,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -397,33 +409,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -803,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="14">
-        <v>141.80000000000001</v>
+        <v>147.4</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
@@ -824,10 +839,10 @@
         <v>46</v>
       </c>
       <c r="I3" s="2">
-        <v>178.55922000000001</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>74</v>
+        <v>177.192477</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
@@ -850,7 +865,7 @@
       </c>
       <c r="I4" s="15">
         <f>I2*I3</f>
-        <v>25319.697396000003</v>
+        <v>26118.171109800001</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -873,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="15">
-        <v>1617</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>74</v>
+        <v>873</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
@@ -896,11 +911,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="15">
-        <f>1996+645</f>
-        <v>2641</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>74</v>
+        <f>1005+1992</f>
+        <v>2997</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
@@ -921,7 +936,7 @@
       </c>
       <c r="I7" s="15">
         <f>I4-I5+I6</f>
-        <v>26343.697396000003</v>
+        <v>28242.171109800001</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
@@ -1321,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8AFDA6-8DF7-49F6-9902-DB49A0E15CEA}">
-  <dimension ref="A1:AC269"/>
+  <dimension ref="A1:AG269"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1329,12 +1344,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1371,33 +1386,45 @@
       <c r="N2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="AA2" s="16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>49</v>
       </c>
@@ -1437,27 +1464,33 @@
       <c r="N3" s="7">
         <v>886</v>
       </c>
-      <c r="O3" s="7"/>
+      <c r="O3" s="7">
+        <v>876</v>
+      </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
-      <c r="U3" s="7">
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7">
         <v>832</v>
       </c>
-      <c r="V3" s="7">
+      <c r="Z3" s="7">
         <v>838</v>
       </c>
-      <c r="W3" s="7">
+      <c r="AA3" s="7">
         <v>886</v>
       </c>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>50</v>
       </c>
@@ -1497,27 +1530,33 @@
       <c r="N4" s="7">
         <v>1136</v>
       </c>
-      <c r="O4" s="7"/>
+      <c r="O4" s="7">
+        <v>1124</v>
+      </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
-      <c r="U4" s="7">
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7">
         <v>1031</v>
       </c>
-      <c r="V4" s="7">
+      <c r="Z4" s="7">
         <v>1095</v>
       </c>
-      <c r="W4" s="7">
+      <c r="AA4" s="7">
         <v>1136</v>
       </c>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1558,7 +1597,7 @@
         <v>1933</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" ref="L5:N5" si="1">+L3+L4</f>
+        <f t="shared" ref="L5:O5" si="1">+L3+L4</f>
         <v>1942</v>
       </c>
       <c r="M5" s="8">
@@ -1569,45 +1608,52 @@
         <f t="shared" si="1"/>
         <v>2022</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:W5" si="2">+P3+P4</f>
+      <c r="O5" s="8">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="8">
+        <f t="shared" ref="T5:AA5" si="2">+T3+T4</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="U5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R5" s="8">
+      <c r="V5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S5" s="8">
+      <c r="W5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T5" s="8">
+      <c r="X5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U5" s="8">
+      <c r="Y5" s="8">
         <f t="shared" si="2"/>
         <v>1863</v>
       </c>
-      <c r="V5" s="8">
+      <c r="Z5" s="8">
         <f t="shared" si="2"/>
         <v>1933</v>
       </c>
-      <c r="W5" s="8">
+      <c r="AA5" s="8">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -1635,8 +1681,12 @@
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
@@ -1674,32 +1724,38 @@
         <v>2328</v>
       </c>
       <c r="N7" s="7">
-        <f>+W7-SUM(K7:M7)</f>
+        <f>+AA7-SUM(K7:M7)</f>
         <v>1825</v>
       </c>
-      <c r="O7" s="7"/>
+      <c r="O7" s="7">
+        <v>2090</v>
+      </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
-      <c r="U7" s="7">
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7">
         <v>6302</v>
       </c>
-      <c r="V7" s="7">
+      <c r="Z7" s="7">
         <v>7551</v>
       </c>
-      <c r="W7" s="7">
+      <c r="AA7" s="7">
         <v>8136</v>
       </c>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
@@ -1737,32 +1793,38 @@
         <v>1298</v>
       </c>
       <c r="N8" s="7">
-        <f t="shared" ref="N8:N33" si="3">+W8-SUM(K8:M8)</f>
+        <f t="shared" ref="N8:N33" si="3">+AA8-SUM(K8:M8)</f>
         <v>1266</v>
       </c>
-      <c r="O8" s="7"/>
+      <c r="O8" s="7">
+        <v>1200</v>
+      </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
-      <c r="U8" s="7">
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7">
         <v>5219</v>
       </c>
-      <c r="V8" s="7">
+      <c r="Z8" s="7">
         <v>5128</v>
       </c>
-      <c r="W8" s="7">
+      <c r="AA8" s="7">
         <v>5087</v>
       </c>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>57</v>
       </c>
@@ -1803,29 +1865,35 @@
         <f t="shared" si="3"/>
         <v>849</v>
       </c>
-      <c r="O9" s="7"/>
+      <c r="O9" s="7">
+        <v>1135</v>
+      </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="7">
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7">
         <v>3190</v>
       </c>
-      <c r="V9" s="7">
+      <c r="Z9" s="7">
         <v>3459</v>
       </c>
-      <c r="W9" s="7">
+      <c r="AA9" s="7">
         <v>3623</v>
       </c>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
       <c r="AB9" s="7"/>
       <c r="AC9" s="7"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>64</v>
       </c>
@@ -1865,29 +1933,35 @@
       <c r="N10" s="7">
         <v>943</v>
       </c>
-      <c r="O10" s="7"/>
+      <c r="O10" s="7">
+        <v>869</v>
+      </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
-      <c r="U10" s="7">
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7">
         <v>2850</v>
       </c>
-      <c r="V10" s="7">
+      <c r="Z10" s="7">
         <v>3310</v>
       </c>
-      <c r="W10" s="7">
+      <c r="AA10" s="7">
         <v>3510</v>
       </c>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>78</v>
       </c>
@@ -1927,39 +2001,45 @@
       <c r="N11" s="7">
         <v>835</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q11" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>80</v>
-      </c>
+      <c r="O11" s="7">
+        <v>831</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
       <c r="T11" s="18" t="s">
         <v>80</v>
       </c>
       <c r="U11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="W11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="X11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z11" s="7">
         <v>2772</v>
       </c>
-      <c r="W11" s="7">
+      <c r="AA11" s="7">
         <v>2926</v>
       </c>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
       <c r="AC11" s="7"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B12" s="17" t="s">
         <v>79</v>
       </c>
@@ -1999,39 +2079,45 @@
       <c r="N12" s="7">
         <v>319</v>
       </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S12" s="18" t="s">
-        <v>80</v>
-      </c>
+      <c r="O12" s="7">
+        <v>405</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
       <c r="T12" s="18" t="s">
         <v>80</v>
       </c>
       <c r="U12" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="V12" s="7">
+      <c r="V12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="W12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="X12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z12" s="7">
         <v>1339</v>
       </c>
-      <c r="W12" s="7">
+      <c r="AA12" s="7">
         <v>1406</v>
       </c>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>65</v>
       </c>
@@ -2072,29 +2158,35 @@
         <f t="shared" si="3"/>
         <v>4246</v>
       </c>
-      <c r="O13" s="7"/>
+      <c r="O13" s="7">
+        <v>3699</v>
+      </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
-      <c r="U13" s="7">
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7">
         <v>12083</v>
       </c>
-      <c r="V13" s="7">
+      <c r="Z13" s="7">
         <v>13975</v>
       </c>
-      <c r="W13" s="7">
+      <c r="AA13" s="7">
         <v>14232</v>
       </c>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
       <c r="AC13" s="7"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>66</v>
       </c>
@@ -2135,29 +2227,35 @@
         <f t="shared" si="3"/>
         <v>2384</v>
       </c>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>2442</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
-      <c r="U14" s="7">
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7">
         <v>7856</v>
       </c>
-      <c r="V14" s="7">
+      <c r="Z14" s="7">
         <v>8216</v>
       </c>
-      <c r="W14" s="7">
+      <c r="AA14" s="7">
         <v>8764</v>
       </c>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
       <c r="AC14" s="7"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>67</v>
       </c>
@@ -2198,29 +2296,35 @@
         <f t="shared" si="3"/>
         <v>448</v>
       </c>
-      <c r="O15" s="7"/>
+      <c r="O15" s="7">
+        <v>451</v>
+      </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
-      <c r="U15" s="7">
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7">
         <v>1488</v>
       </c>
-      <c r="V15" s="7">
+      <c r="Z15" s="7">
         <v>1499</v>
       </c>
-      <c r="W15" s="7">
+      <c r="AA15" s="7">
         <v>1815</v>
       </c>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
       <c r="AC15" s="7"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
@@ -2261,38 +2365,44 @@
         <f t="shared" si="3"/>
         <v>6076</v>
       </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8">
+      <c r="O16" s="8">
+        <v>6592</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8">
         <v>21915</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="U16" s="8">
         <v>23640</v>
       </c>
-      <c r="R16" s="8">
+      <c r="V16" s="8">
         <v>18435</v>
       </c>
-      <c r="S16" s="8">
+      <c r="W16" s="8">
         <v>21234</v>
       </c>
-      <c r="T16" s="8">
+      <c r="X16" s="8">
         <v>22511</v>
       </c>
-      <c r="U16" s="8">
+      <c r="Y16" s="8">
         <v>21427</v>
       </c>
-      <c r="V16" s="8">
+      <c r="Z16" s="8">
         <v>23683</v>
       </c>
-      <c r="W16" s="8">
+      <c r="AA16" s="8">
         <v>24811</v>
       </c>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+    </row>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
@@ -2333,38 +2443,44 @@
         <f t="shared" si="3"/>
         <v>2988</v>
       </c>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7">
+      <c r="O17" s="7">
+        <v>3223</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7">
         <v>10552</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="U17" s="7">
         <v>11347</v>
       </c>
-      <c r="R17" s="7">
+      <c r="V17" s="7">
         <v>9213</v>
       </c>
-      <c r="S17" s="7">
+      <c r="W17" s="7">
         <v>10469</v>
       </c>
-      <c r="T17" s="7">
+      <c r="X17" s="7">
         <v>11867</v>
       </c>
-      <c r="U17" s="7">
+      <c r="Y17" s="7">
         <v>11244</v>
       </c>
-      <c r="V17" s="7">
+      <c r="Z17" s="7">
         <v>11658</v>
       </c>
-      <c r="W17" s="7">
+      <c r="AA17" s="7">
         <v>12006</v>
       </c>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="7"/>
+    </row>
+    <row r="18" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
         <v>25</v>
       </c>
@@ -2397,7 +2513,7 @@
         <v>3301</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" ref="J18:N18" si="11">J16-J17</f>
+        <f t="shared" ref="J18:O18" si="11">J16-J17</f>
         <v>2970</v>
       </c>
       <c r="K18" s="7">
@@ -2416,46 +2532,53 @@
         <f t="shared" si="11"/>
         <v>3088</v>
       </c>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7">
-        <f t="shared" ref="P18:T18" si="12">P16-P17</f>
+      <c r="O18" s="7">
+        <f t="shared" si="11"/>
+        <v>3369</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7">
+        <f t="shared" ref="T18:X18" si="12">T16-T17</f>
         <v>11363</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="U18" s="7">
         <f t="shared" si="12"/>
         <v>12293</v>
       </c>
-      <c r="R18" s="7">
+      <c r="V18" s="7">
         <f t="shared" si="12"/>
         <v>9222</v>
       </c>
-      <c r="S18" s="7">
+      <c r="W18" s="7">
         <f t="shared" si="12"/>
         <v>10765</v>
       </c>
-      <c r="T18" s="7">
+      <c r="X18" s="7">
         <f t="shared" si="12"/>
         <v>10644</v>
       </c>
-      <c r="U18" s="7">
-        <f>U16-U17</f>
+      <c r="Y18" s="7">
+        <f>Y16-Y17</f>
         <v>10183</v>
       </c>
-      <c r="V18" s="7">
-        <f>V16-V17</f>
+      <c r="Z18" s="7">
+        <f>Z16-Z17</f>
         <v>12025</v>
       </c>
-      <c r="W18" s="7">
-        <f>W16-W17</f>
+      <c r="AA18" s="7">
+        <f>AA16-AA17</f>
         <v>12805</v>
       </c>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
       <c r="AB18" s="7"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+    </row>
+    <row r="19" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>26</v>
       </c>
@@ -2496,38 +2619,44 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7">
+      <c r="O19" s="7">
+        <v>19</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7">
         <v>129</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="U19" s="7">
         <v>154</v>
       </c>
-      <c r="R19" s="7">
+      <c r="V19" s="7">
         <v>61</v>
       </c>
-      <c r="S19" s="7">
+      <c r="W19" s="7">
         <v>86</v>
       </c>
-      <c r="T19" s="7">
+      <c r="X19" s="7">
         <v>112</v>
       </c>
-      <c r="U19" s="7">
+      <c r="Y19" s="7">
         <v>83</v>
       </c>
-      <c r="V19" s="7">
+      <c r="Z19" s="7">
         <v>81</v>
       </c>
-      <c r="W19" s="7">
+      <c r="AA19" s="7">
         <v>81</v>
       </c>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+    </row>
+    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
@@ -2568,38 +2697,44 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7">
+      <c r="O20" s="7">
+        <v>1</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7">
         <v>48</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="U20" s="7">
         <v>56</v>
       </c>
-      <c r="R20" s="7">
+      <c r="V20" s="7">
         <v>42</v>
       </c>
-      <c r="S20" s="7">
+      <c r="W20" s="7">
         <v>28</v>
       </c>
-      <c r="T20" s="7">
+      <c r="X20" s="7">
         <v>173</v>
       </c>
-      <c r="U20" s="7">
+      <c r="Y20" s="7">
         <v>71</v>
       </c>
-      <c r="V20" s="7">
+      <c r="Z20" s="7">
         <v>174</v>
       </c>
-      <c r="W20" s="7">
+      <c r="AA20" s="7">
         <v>41</v>
       </c>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
       <c r="AB20" s="7"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7"/>
+    </row>
+    <row r="21" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
         <v>28</v>
       </c>
@@ -2640,39 +2775,45 @@
         <f t="shared" si="3"/>
         <v>823</v>
       </c>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7">
+      <c r="O21" s="7">
+        <v>756</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7">
         <v>3001</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="U21" s="7">
         <v>3042</v>
       </c>
-      <c r="R21" s="7">
+      <c r="V21" s="7">
         <v>2373</v>
       </c>
-      <c r="S21" s="7">
+      <c r="W21" s="7">
         <v>2547</v>
       </c>
-      <c r="T21" s="7">
+      <c r="X21" s="7">
         <v>2763</v>
       </c>
-      <c r="U21" s="7">
+      <c r="Y21" s="7">
         <v>2528</v>
       </c>
-      <c r="V21" s="7">
+      <c r="Z21" s="7">
         <f>+SUM(G21:J21)</f>
         <v>2088</v>
       </c>
-      <c r="W21" s="7">
+      <c r="AA21" s="7">
         <v>3079</v>
       </c>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="7"/>
+      <c r="AF21" s="7"/>
+    </row>
+    <row r="22" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
@@ -2713,39 +2854,45 @@
         <f t="shared" si="3"/>
         <v>2142</v>
       </c>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7">
+      <c r="O22" s="7">
+        <v>1927</v>
+      </c>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7">
         <v>4450</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="U22" s="7">
         <v>4997</v>
       </c>
-      <c r="R22" s="7">
+      <c r="V22" s="7">
         <v>4601</v>
       </c>
-      <c r="S22" s="7">
+      <c r="W22" s="7">
         <v>4782</v>
       </c>
-      <c r="T22" s="7">
+      <c r="X22" s="7">
         <v>5601</v>
       </c>
-      <c r="U22" s="7">
+      <c r="Y22" s="7">
         <v>5547</v>
       </c>
-      <c r="V22" s="7">
+      <c r="Z22" s="7">
         <f>+SUM(G22:J22)</f>
         <v>8858</v>
       </c>
-      <c r="W22" s="7">
+      <c r="AA22" s="7">
         <v>7792</v>
       </c>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="7"/>
+      <c r="AD22" s="7"/>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="7"/>
+    </row>
+    <row r="23" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B23" s="13" t="s">
         <v>76</v>
       </c>
@@ -2786,39 +2933,46 @@
         <f t="shared" si="3"/>
         <v>-7904</v>
       </c>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7">
+      <c r="O23" s="7">
+        <f>+O21+O22</f>
+        <v>2683</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7">
         <v>1576</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="U23" s="7">
         <v>1652</v>
       </c>
-      <c r="R23" s="7">
+      <c r="V23" s="7">
         <v>1379</v>
       </c>
-      <c r="S23" s="7">
+      <c r="W23" s="7">
         <v>1481</v>
       </c>
-      <c r="T23" s="7">
+      <c r="X23" s="7">
         <v>1651</v>
       </c>
-      <c r="U23" s="7">
+      <c r="Y23" s="7">
         <v>1839</v>
       </c>
-      <c r="V23" s="7">
+      <c r="Z23" s="7">
         <f>+SUM(G23:J23)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="7">
+      <c r="AA23" s="7">
         <v>0</v>
       </c>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="7"/>
+    </row>
+    <row r="24" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
         <v>27</v>
       </c>
@@ -2859,45 +3013,51 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7">
+      <c r="O24" s="7">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7">
         <f>105+41</f>
         <v>146</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="U24" s="7">
         <f>134+18</f>
         <v>152</v>
       </c>
-      <c r="R24" s="7">
+      <c r="V24" s="7">
         <f>116+111</f>
         <v>227</v>
       </c>
-      <c r="S24" s="7">
+      <c r="W24" s="7">
         <f>76+6</f>
         <v>82</v>
       </c>
-      <c r="T24" s="7">
+      <c r="X24" s="7">
         <f>182+63</f>
         <v>245</v>
       </c>
-      <c r="U24" s="7">
+      <c r="Y24" s="7">
         <f>137+19</f>
         <v>156</v>
       </c>
-      <c r="V24" s="7">
+      <c r="Z24" s="7">
         <f>+SUM(G24:J24)</f>
         <v>0</v>
       </c>
-      <c r="W24" s="7">
+      <c r="AA24" s="7">
         <v>0</v>
       </c>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
       <c r="AB24" s="7"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="7"/>
+    </row>
+    <row r="25" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
         <v>30</v>
       </c>
@@ -2922,7 +3082,7 @@
         <v>336</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" ref="H25:N25" si="14">H18+H19+H20-H21-H22</f>
+        <f t="shared" ref="H25:O25" si="14">H18+H19+H20-H21-H22</f>
         <v>347</v>
       </c>
       <c r="I25" s="7">
@@ -2949,46 +3109,53 @@
         <f t="shared" si="14"/>
         <v>164</v>
       </c>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7">
-        <f t="shared" ref="P25:T25" si="15">P18+P19+P20-SUM(P21:P24)</f>
+      <c r="O25" s="7">
+        <f t="shared" si="14"/>
+        <v>706</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7">
+        <f t="shared" ref="T25:X25" si="15">T18+T19+T20-SUM(T21:T24)</f>
         <v>2367</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="U25" s="7">
         <f t="shared" si="15"/>
         <v>2660</v>
       </c>
-      <c r="R25" s="7">
+      <c r="V25" s="7">
         <f t="shared" si="15"/>
         <v>745</v>
       </c>
-      <c r="S25" s="7">
+      <c r="W25" s="7">
         <f t="shared" si="15"/>
         <v>1987</v>
       </c>
-      <c r="T25" s="7">
+      <c r="X25" s="7">
         <f t="shared" si="15"/>
         <v>669</v>
       </c>
-      <c r="U25" s="7">
-        <f>U18+U19+U20-SUM(U21:U24)</f>
+      <c r="Y25" s="7">
+        <f>Y18+Y19+Y20-SUM(Y21:Y24)</f>
         <v>267</v>
       </c>
-      <c r="V25" s="7">
-        <f>V18+V19+V20-SUM(V21:V24)</f>
+      <c r="Z25" s="7">
+        <f>Z18+Z19+Z20-SUM(Z21:Z24)</f>
         <v>1334</v>
       </c>
-      <c r="W25" s="7">
-        <f>W18+W19+W20-SUM(W21:W24)</f>
+      <c r="AA25" s="7">
+        <f>AA18+AA19+AA20-SUM(AA21:AA24)</f>
         <v>2056</v>
       </c>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+      <c r="AF25" s="7"/>
+    </row>
+    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
         <v>32</v>
       </c>
@@ -3029,38 +3196,44 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7">
+      <c r="O26" s="7">
+        <v>11</v>
+      </c>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7">
         <v>57</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="U26" s="7">
         <v>64</v>
       </c>
-      <c r="R26" s="7">
+      <c r="V26" s="7">
         <v>29</v>
       </c>
-      <c r="S26" s="7">
+      <c r="W26" s="7">
         <v>19</v>
       </c>
-      <c r="T26" s="7">
+      <c r="X26" s="7">
         <v>39</v>
       </c>
-      <c r="U26" s="7">
+      <c r="Y26" s="7">
         <v>79</v>
       </c>
-      <c r="V26" s="7">
+      <c r="Z26" s="7">
         <v>101</v>
       </c>
-      <c r="W26" s="7">
+      <c r="AA26" s="7">
         <v>74</v>
       </c>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="7"/>
+      <c r="AF26" s="7"/>
+    </row>
+    <row r="27" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
         <v>33</v>
       </c>
@@ -3101,38 +3274,44 @@
         <f t="shared" si="3"/>
         <v>86</v>
       </c>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7">
+      <c r="O27" s="7">
+        <v>70</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7">
         <v>47</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="U27" s="7">
         <v>166</v>
       </c>
-      <c r="R27" s="7">
+      <c r="V27" s="7">
         <v>196</v>
       </c>
-      <c r="S27" s="7">
+      <c r="W27" s="7">
         <v>153</v>
       </c>
-      <c r="T27" s="7">
+      <c r="X27" s="7">
         <v>320</v>
       </c>
-      <c r="U27" s="7">
+      <c r="Y27" s="7">
         <v>282</v>
       </c>
-      <c r="V27" s="7">
+      <c r="Z27" s="7">
         <v>317</v>
       </c>
-      <c r="W27" s="7">
+      <c r="AA27" s="7">
         <v>310</v>
       </c>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="7"/>
+      <c r="AD27" s="7"/>
+      <c r="AE27" s="7"/>
+      <c r="AF27" s="7"/>
+    </row>
+    <row r="28" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
         <v>34</v>
       </c>
@@ -3165,7 +3344,7 @@
         <v>600</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" ref="J28:N28" si="23">J25+J26-J27</f>
+        <f t="shared" ref="J28:O28" si="23">J25+J26-J27</f>
         <v>-28</v>
       </c>
       <c r="K28" s="7">
@@ -3184,46 +3363,53 @@
         <f t="shared" si="23"/>
         <v>97</v>
       </c>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7">
-        <f t="shared" ref="P28:T28" si="24">P25+P26-P27</f>
+      <c r="O28" s="7">
+        <f t="shared" si="23"/>
+        <v>647</v>
+      </c>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7">
+        <f t="shared" ref="T28:X28" si="24">T25+T26-T27</f>
         <v>2377</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="U28" s="7">
         <f t="shared" si="24"/>
         <v>2558</v>
       </c>
-      <c r="R28" s="7">
+      <c r="V28" s="7">
         <f t="shared" si="24"/>
         <v>578</v>
       </c>
-      <c r="S28" s="7">
+      <c r="W28" s="7">
         <f t="shared" si="24"/>
         <v>1853</v>
       </c>
-      <c r="T28" s="7">
+      <c r="X28" s="7">
         <f t="shared" si="24"/>
         <v>388</v>
       </c>
-      <c r="U28" s="7">
-        <f>U25+U26-U27</f>
+      <c r="Y28" s="7">
+        <f>Y25+Y26-Y27</f>
         <v>64</v>
       </c>
-      <c r="V28" s="7">
+      <c r="Z28" s="7">
         <f>+SUM(G28:J28)</f>
         <v>1122</v>
       </c>
-      <c r="W28" s="7">
-        <f>+W25+W26-W27</f>
+      <c r="AA28" s="7">
+        <f>+AA25+AA26-AA27</f>
         <v>1820</v>
       </c>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
-      <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="7"/>
+      <c r="AE28" s="7"/>
+      <c r="AF28" s="7"/>
+    </row>
+    <row r="29" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>35</v>
       </c>
@@ -3264,38 +3450,44 @@
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7">
+      <c r="O29" s="7">
+        <v>161</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7">
         <v>669</v>
       </c>
-      <c r="Q29" s="7">
+      <c r="U29" s="7">
         <v>640</v>
       </c>
-      <c r="R29" s="7">
+      <c r="V29" s="7">
         <v>117</v>
       </c>
-      <c r="S29" s="7">
+      <c r="W29" s="7">
         <v>360</v>
       </c>
-      <c r="T29" s="7">
+      <c r="X29" s="7">
         <v>134</v>
       </c>
-      <c r="U29" s="7">
+      <c r="Y29" s="7">
         <v>124</v>
       </c>
-      <c r="V29" s="7">
+      <c r="Z29" s="7">
         <v>297</v>
       </c>
-      <c r="W29" s="7">
+      <c r="AA29" s="7">
         <v>443</v>
       </c>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
-      <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="7"/>
+      <c r="AD29" s="7"/>
+      <c r="AE29" s="7"/>
+      <c r="AF29" s="7"/>
+    </row>
+    <row r="30" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
         <v>37</v>
       </c>
@@ -3328,7 +3520,7 @@
         <v>467</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" ref="J30:N30" si="32">J28-J29</f>
+        <f t="shared" ref="J30:O30" si="32">J28-J29</f>
         <v>-26</v>
       </c>
       <c r="K30" s="7">
@@ -3347,46 +3539,53 @@
         <f t="shared" si="32"/>
         <v>86</v>
       </c>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7">
-        <f t="shared" ref="P30:T30" si="33">P28-P29</f>
+      <c r="O30" s="7">
+        <f t="shared" si="32"/>
+        <v>486</v>
+      </c>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7">
+        <f t="shared" ref="T30:X30" si="33">T28-T29</f>
         <v>1708</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="U30" s="7">
         <f t="shared" si="33"/>
         <v>1918</v>
       </c>
-      <c r="R30" s="7">
+      <c r="V30" s="7">
         <f t="shared" si="33"/>
         <v>461</v>
       </c>
-      <c r="S30" s="7">
+      <c r="W30" s="7">
         <f t="shared" si="33"/>
         <v>1493</v>
       </c>
-      <c r="T30" s="7">
+      <c r="X30" s="7">
         <f t="shared" si="33"/>
         <v>254</v>
       </c>
-      <c r="U30" s="7">
-        <f>U28-U29</f>
+      <c r="Y30" s="7">
+        <f>Y28-Y29</f>
         <v>-60</v>
       </c>
-      <c r="V30" s="7">
-        <f>V28-V29</f>
+      <c r="Z30" s="7">
+        <f>Z28-Z29</f>
         <v>825</v>
       </c>
-      <c r="W30" s="7">
-        <f>W28-W29</f>
+      <c r="AA30" s="7">
+        <f>AA28-AA29</f>
         <v>1377</v>
       </c>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
-    </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="7"/>
+      <c r="AD30" s="7"/>
+      <c r="AE30" s="7"/>
+      <c r="AF30" s="7"/>
+    </row>
+    <row r="31" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
         <v>38</v>
       </c>
@@ -3427,38 +3626,44 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7">
+      <c r="O31" s="7">
+        <v>3</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7">
         <v>-5</v>
       </c>
-      <c r="Q31" s="7">
+      <c r="U31" s="7">
         <v>59</v>
       </c>
-      <c r="R31" s="7">
+      <c r="V31" s="7">
         <v>-19</v>
       </c>
-      <c r="S31" s="7">
+      <c r="W31" s="7">
         <v>666</v>
       </c>
-      <c r="T31" s="7">
+      <c r="X31" s="7">
         <v>384</v>
       </c>
-      <c r="U31" s="7">
+      <c r="Y31" s="7">
         <v>44</v>
       </c>
-      <c r="V31" s="7">
+      <c r="Z31" s="7">
         <v>8</v>
       </c>
-      <c r="W31" s="7">
+      <c r="AA31" s="7">
         <v>8</v>
       </c>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-      <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
-    </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
+    </row>
+    <row r="32" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
         <v>36</v>
       </c>
@@ -3491,7 +3696,7 @@
         <v>474</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" ref="J32:N32" si="41">J30+J31</f>
+        <f t="shared" ref="J32:O32" si="41">J30+J31</f>
         <v>-19</v>
       </c>
       <c r="K32" s="7">
@@ -3510,46 +3715,53 @@
         <f t="shared" si="41"/>
         <v>92</v>
       </c>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7">
-        <f t="shared" ref="P32:T32" si="42">P30+P31</f>
+      <c r="O32" s="7">
+        <f t="shared" si="41"/>
+        <v>489</v>
+      </c>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7">
+        <f t="shared" ref="T32:X32" si="42">T30+T31</f>
         <v>1703</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="U32" s="7">
         <f t="shared" si="42"/>
         <v>1977</v>
       </c>
-      <c r="R32" s="7">
+      <c r="V32" s="7">
         <f t="shared" si="42"/>
         <v>442</v>
       </c>
-      <c r="S32" s="7">
+      <c r="W32" s="7">
         <f t="shared" si="42"/>
         <v>2159</v>
       </c>
-      <c r="T32" s="7">
+      <c r="X32" s="7">
         <f t="shared" si="42"/>
         <v>638</v>
       </c>
-      <c r="U32" s="7">
-        <f>U30+U31</f>
+      <c r="Y32" s="7">
+        <f>Y30+Y31</f>
         <v>-16</v>
       </c>
-      <c r="V32" s="7">
-        <f>V30+V31</f>
+      <c r="Z32" s="7">
+        <f>Z30+Z31</f>
         <v>833</v>
       </c>
-      <c r="W32" s="7">
-        <f>W30+W31</f>
+      <c r="AA32" s="7">
+        <f>AA30+AA31</f>
         <v>1385</v>
       </c>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="7"/>
+      <c r="AD32" s="7"/>
+      <c r="AE32" s="7"/>
+      <c r="AF32" s="7"/>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
         <v>39</v>
       </c>
@@ -3590,38 +3802,44 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7">
+      <c r="O33" s="7">
+        <v>5</v>
+      </c>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7">
         <v>3</v>
       </c>
-      <c r="Q33" s="7">
+      <c r="U33" s="7">
         <v>2</v>
       </c>
-      <c r="R33" s="7">
+      <c r="V33" s="7">
         <v>11</v>
       </c>
-      <c r="S33" s="7">
+      <c r="W33" s="7">
         <v>42</v>
       </c>
-      <c r="T33" s="7">
+      <c r="X33" s="7">
         <v>26</v>
       </c>
-      <c r="U33" s="7">
+      <c r="Y33" s="7">
         <v>61</v>
       </c>
-      <c r="V33" s="7">
+      <c r="Z33" s="7">
         <v>764</v>
       </c>
-      <c r="W33" s="7">
+      <c r="AA33" s="7">
         <v>45</v>
       </c>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
-      <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
+      <c r="AE33" s="7"/>
+      <c r="AF33" s="7"/>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
         <v>40</v>
       </c>
@@ -3650,7 +3868,7 @@
         <v>190</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" ref="I34:N34" si="48">I32-I33</f>
+        <f t="shared" ref="I34:O34" si="48">I32-I33</f>
         <v>441</v>
       </c>
       <c r="J34" s="7">
@@ -3673,46 +3891,53 @@
         <f t="shared" si="48"/>
         <v>82</v>
       </c>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7">
-        <f t="shared" ref="P34:T34" si="49">P32-P33</f>
+      <c r="O34" s="7">
+        <f t="shared" si="48"/>
+        <v>484</v>
+      </c>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7">
+        <f t="shared" ref="T34:X34" si="49">T32-T33</f>
         <v>1700</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="U34" s="7">
         <f t="shared" si="49"/>
         <v>1975</v>
       </c>
-      <c r="R34" s="7">
+      <c r="V34" s="7">
         <f t="shared" si="49"/>
         <v>431</v>
       </c>
-      <c r="S34" s="7">
+      <c r="W34" s="7">
         <f t="shared" si="49"/>
         <v>2117</v>
       </c>
-      <c r="T34" s="7">
+      <c r="X34" s="7">
         <f t="shared" si="49"/>
         <v>612</v>
       </c>
-      <c r="U34" s="7">
-        <f>U32-U33</f>
+      <c r="Y34" s="7">
+        <f>Y32-Y33</f>
         <v>-77</v>
       </c>
-      <c r="V34" s="7">
-        <f>V32-V33</f>
+      <c r="Z34" s="7">
+        <f>Z32-Z33</f>
         <v>69</v>
       </c>
-      <c r="W34" s="7">
-        <f>W32-W33</f>
+      <c r="AA34" s="7">
+        <f>AA32-AA33</f>
         <v>1340</v>
       </c>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
       <c r="AB34" s="7"/>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="7"/>
+      <c r="AD34" s="7"/>
+      <c r="AE34" s="7"/>
+      <c r="AF34" s="7"/>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -3740,8 +3965,12 @@
       <c r="Z35" s="7"/>
       <c r="AA35" s="7"/>
       <c r="AB35" s="7"/>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="7"/>
+      <c r="AE35" s="7"/>
+      <c r="AF35" s="7"/>
+    </row>
+    <row r="36" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
@@ -3769,7 +3998,7 @@
         <v>0.11201401626905014</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" ref="K36:N36" si="50">+K34/K37</f>
+        <f t="shared" ref="K36:O36" si="50">+K34/K37</f>
         <v>2.3914992473442207</v>
       </c>
       <c r="L36" s="4">
@@ -3784,36 +4013,43 @@
         <f t="shared" si="50"/>
         <v>0.45923139673213176</v>
       </c>
-      <c r="O36" s="4"/>
-      <c r="P36" s="9">
+      <c r="O36" s="4">
+        <f t="shared" si="50"/>
+        <v>2.7314929403012975</v>
+      </c>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="9">
         <v>8.44</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="U36" s="9">
         <v>10</v>
       </c>
-      <c r="R36" s="9">
+      <c r="V36" s="9">
         <v>2.31</v>
       </c>
-      <c r="S36" s="9">
+      <c r="W36" s="9">
         <v>7.47</v>
       </c>
-      <c r="T36" s="9">
+      <c r="X36" s="9">
         <v>1.25</v>
       </c>
-      <c r="U36" s="9">
-        <f>+U34/U37</f>
+      <c r="Y36" s="9">
+        <f>+Y34/Y37</f>
         <v>-0.43125396263584304</v>
       </c>
-      <c r="V36" s="9">
-        <f>+V34/V37</f>
+      <c r="Z36" s="9">
+        <f>+Z34/Z37</f>
         <v>0.38644835612822298</v>
       </c>
-      <c r="W36" s="9">
-        <f>+W34/W37</f>
+      <c r="AA36" s="9">
+        <f>+AA34/AA37</f>
         <v>7.5045130685494703</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>46</v>
       </c>
@@ -3858,41 +4094,47 @@
         <v>178.54908399999999</v>
       </c>
       <c r="N37" s="4">
-        <f>+W37</f>
+        <f>+AA37</f>
         <v>178.55922000000001</v>
       </c>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4">
-        <f t="shared" ref="P37:T37" si="52">P34/P36</f>
+      <c r="O37" s="4">
+        <v>177.192477</v>
+      </c>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4">
+        <f t="shared" ref="T37:X37" si="52">T34/T36</f>
         <v>201.4218009478673</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="U37" s="4">
         <f t="shared" si="52"/>
         <v>197.5</v>
       </c>
-      <c r="R37" s="4">
+      <c r="V37" s="4">
         <f t="shared" si="52"/>
         <v>186.58008658008657</v>
       </c>
-      <c r="S37" s="4">
+      <c r="W37" s="4">
         <f t="shared" si="52"/>
         <v>283.40026773761713</v>
       </c>
-      <c r="T37" s="4">
+      <c r="X37" s="4">
         <f t="shared" si="52"/>
         <v>489.6</v>
       </c>
-      <c r="U37" s="4">
+      <c r="Y37" s="4">
         <v>178.54908399999999</v>
       </c>
-      <c r="V37" s="4">
+      <c r="Z37" s="4">
         <v>178.54908399999999</v>
       </c>
-      <c r="W37" s="4">
+      <c r="AA37" s="4">
         <v>178.55922000000001</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3913,8 +4155,12 @@
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>58</v>
       </c>
@@ -3923,69 +4169,76 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="10">
-        <f>+G3/C3-1</f>
+        <f t="shared" ref="G39:O39" si="53">+G3/C3-1</f>
         <v>1.4833127317676054E-2</v>
       </c>
       <c r="H39" s="10">
-        <f>+H3/D3-1</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I39" s="10">
-        <f>+I3/E3-1</f>
+        <f t="shared" si="53"/>
         <v>3.5220125786163514E-2</v>
       </c>
       <c r="J39" s="10">
-        <f>+J3/F3-1</f>
+        <f t="shared" si="53"/>
         <v>7.2115384615385469E-3</v>
       </c>
       <c r="K39" s="10">
-        <f>+K3/G3-1</f>
+        <f t="shared" si="53"/>
         <v>1.8270401948842885E-2</v>
       </c>
       <c r="L39" s="10">
-        <f>+L3/H3-1</f>
+        <f t="shared" si="53"/>
         <v>4.7146401985111552E-2</v>
       </c>
       <c r="M39" s="10">
-        <f>+M3/I3-1</f>
+        <f t="shared" si="53"/>
         <v>5.2247873633049835E-2</v>
       </c>
       <c r="N39" s="10">
-        <f>+N3/J3-1</f>
+        <f t="shared" si="53"/>
         <v>5.7279236276849721E-2</v>
       </c>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="10" t="e">
-        <f t="shared" ref="Q39:U39" si="53">+Q3/P3-1</f>
+      <c r="O39" s="10">
+        <f t="shared" si="53"/>
+        <v>4.7846889952153138E-2</v>
+      </c>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="10" t="e">
+        <f t="shared" ref="U39:Y39" si="54">+U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="10" t="e">
-        <f t="shared" si="53"/>
+      <c r="V39" s="10" t="e">
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S39" s="10" t="e">
-        <f t="shared" si="53"/>
+      <c r="W39" s="10" t="e">
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T39" s="10" t="e">
-        <f t="shared" si="53"/>
+      <c r="X39" s="10" t="e">
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U39" s="10" t="e">
-        <f t="shared" si="53"/>
+      <c r="Y39" s="10" t="e">
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V39" s="10">
-        <f>+V3/U3-1</f>
+      <c r="Z39" s="10">
+        <f>+Z3/Y3-1</f>
         <v>7.2115384615385469E-3</v>
       </c>
-      <c r="W39" s="10">
-        <f>+W3/V3-1</f>
+      <c r="AA39" s="10">
+        <f>+AA3/Z3-1</f>
         <v>5.7279236276849721E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
@@ -4006,7 +4259,7 @@
         <v>-1.5525114155251152E-2</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" ref="J40" si="54">+J4/F4-1</f>
+        <f t="shared" ref="J40" si="55">+J4/F4-1</f>
         <v>6.2075654704170757E-2</v>
       </c>
       <c r="K40" s="10">
@@ -4025,38 +4278,45 @@
         <f>+N4/J4-1</f>
         <v>3.7442922374429255E-2</v>
       </c>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="10" t="e">
-        <f t="shared" ref="Q40:U40" si="55">+Q4/P4-1</f>
+      <c r="O40" s="10">
+        <f>+O4/K4-1</f>
+        <v>2.4612579762989917E-2</v>
+      </c>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="10" t="e">
+        <f t="shared" ref="U40:Y40" si="56">+U4/T4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R40" s="10" t="e">
-        <f t="shared" si="55"/>
+      <c r="V40" s="10" t="e">
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S40" s="10" t="e">
-        <f t="shared" si="55"/>
+      <c r="W40" s="10" t="e">
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T40" s="10" t="e">
-        <f t="shared" si="55"/>
+      <c r="X40" s="10" t="e">
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U40" s="10" t="e">
-        <f t="shared" si="55"/>
+      <c r="Y40" s="10" t="e">
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V40" s="10">
-        <f>+V4/U4-1</f>
+      <c r="Z40" s="10">
+        <f>+Z4/Y4-1</f>
         <v>6.2075654704170757E-2</v>
       </c>
-      <c r="W40" s="10">
-        <f>+W4/V4-1</f>
+      <c r="AA40" s="10">
+        <f>+AA4/Z4-1</f>
         <v>3.7442922374429255E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
@@ -4065,69 +4325,76 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="10">
-        <f>+G7/C7-1</f>
+        <f t="shared" ref="G41:O44" si="57">+G7/C7-1</f>
         <v>0.14844267726971494</v>
       </c>
       <c r="H41" s="10">
-        <f>+H7/D7-1</f>
+        <f t="shared" si="57"/>
         <v>0.20100502512562812</v>
       </c>
       <c r="I41" s="10">
-        <f>+I7/E7-1</f>
+        <f t="shared" si="57"/>
         <v>0.18763796909492281</v>
       </c>
       <c r="J41" s="10">
-        <f>+J7/F7-1</f>
+        <f t="shared" si="57"/>
         <v>0.26277897768178549</v>
       </c>
       <c r="K41" s="10">
-        <f>+K7/G7-1</f>
+        <f t="shared" si="57"/>
         <v>0.14598961338718985</v>
       </c>
       <c r="L41" s="10">
-        <f>+L7/H7-1</f>
+        <f t="shared" si="57"/>
         <v>4.4456066945606665E-2</v>
       </c>
       <c r="M41" s="10">
-        <f>+M7/I7-1</f>
+        <f t="shared" si="57"/>
         <v>8.1784386617100413E-2</v>
       </c>
       <c r="N41" s="10">
-        <f>+N7/J7-1</f>
+        <f t="shared" si="57"/>
         <v>4.0478905359178974E-2</v>
       </c>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="10" t="e">
-        <f>+Q7/P7-1</f>
+      <c r="O41" s="10">
+        <f t="shared" si="57"/>
+        <v>5.2366565961732059E-2</v>
+      </c>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="10" t="e">
+        <f t="shared" ref="U41:AA44" si="58">+U7/T7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="10" t="e">
-        <f>+R7/Q7-1</f>
+      <c r="V41" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S41" s="10" t="e">
-        <f>+S7/R7-1</f>
+      <c r="W41" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T41" s="10" t="e">
-        <f>+T7/S7-1</f>
+      <c r="X41" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U41" s="10" t="e">
-        <f>+U7/T7-1</f>
+      <c r="Y41" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V41" s="10">
-        <f>+V7/U7-1</f>
+      <c r="Z41" s="10">
+        <f t="shared" si="58"/>
         <v>0.19819105046017138</v>
       </c>
-      <c r="W41" s="10">
-        <f>+W7/V7-1</f>
+      <c r="AA41" s="10">
+        <f t="shared" si="58"/>
         <v>7.7473182359952375E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>61</v>
       </c>
@@ -4136,69 +4403,76 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="10">
-        <f>+G8/C8-1</f>
+        <f t="shared" si="57"/>
         <v>-4.6728971962616828E-2</v>
       </c>
       <c r="H42" s="10">
-        <f>+H8/D8-1</f>
+        <f t="shared" si="57"/>
         <v>-6.9335239456754794E-2</v>
       </c>
       <c r="I42" s="10">
-        <f>+I8/E8-1</f>
+        <f t="shared" si="57"/>
         <v>-8.2210242587601123E-2</v>
       </c>
       <c r="J42" s="10">
-        <f>+J8/F8-1</f>
+        <f t="shared" si="57"/>
         <v>0.15789473684210531</v>
       </c>
       <c r="K42" s="10">
-        <f>+K8/G8-1</f>
+        <f t="shared" si="57"/>
         <v>5.525846702317283E-2</v>
       </c>
       <c r="L42" s="10">
-        <f>+L8/H8-1</f>
+        <f t="shared" si="57"/>
         <v>2.8417818740399392E-2</v>
       </c>
       <c r="M42" s="10">
-        <f>+M8/I8-1</f>
+        <f t="shared" si="57"/>
         <v>-4.6989720998531603E-2</v>
       </c>
       <c r="N42" s="10">
-        <f>+N8/J8-1</f>
+        <f t="shared" si="57"/>
         <v>-5.663189269746649E-2</v>
       </c>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="10" t="e">
-        <f>+Q8/P8-1</f>
+      <c r="O42" s="10">
+        <f t="shared" si="57"/>
+        <v>1.3513513513513598E-2</v>
+      </c>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R42" s="10" t="e">
-        <f>+R8/Q8-1</f>
+      <c r="V42" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S42" s="10" t="e">
-        <f>+S8/R8-1</f>
+      <c r="W42" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T42" s="10" t="e">
-        <f>+T8/S8-1</f>
+      <c r="X42" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U42" s="10" t="e">
-        <f>+U8/T8-1</f>
+      <c r="Y42" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V42" s="10">
-        <f>+V8/U8-1</f>
+      <c r="Z42" s="10">
+        <f t="shared" si="58"/>
         <v>-1.7436290477102934E-2</v>
       </c>
-      <c r="W42" s="10">
-        <f>+W8/V8-1</f>
+      <c r="AA42" s="10">
+        <f t="shared" si="58"/>
         <v>-7.9953198127925562E-3</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>62</v>
       </c>
@@ -4207,69 +4481,76 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="10">
-        <f>+G9/C9-1</f>
+        <f t="shared" si="57"/>
         <v>1.4705882352941124E-2</v>
       </c>
       <c r="H43" s="10">
-        <f>+H9/D9-1</f>
+        <f t="shared" si="57"/>
         <v>7.3107049608355013E-2</v>
       </c>
       <c r="I43" s="10">
-        <f>+I9/E9-1</f>
+        <f t="shared" si="57"/>
         <v>8.7356321839080486E-2</v>
       </c>
       <c r="J43" s="10">
-        <f>+J9/F9-1</f>
+        <f t="shared" si="57"/>
         <v>0.18507462686567155</v>
       </c>
       <c r="K43" s="10">
-        <f>+K9/G9-1</f>
+        <f t="shared" si="57"/>
         <v>0.14715719063545141</v>
       </c>
       <c r="L43" s="10">
-        <f>+L9/H9-1</f>
+        <f t="shared" si="57"/>
         <v>-2.9197080291970767E-2</v>
       </c>
       <c r="M43" s="10">
-        <f>+M9/I9-1</f>
+        <f t="shared" si="57"/>
         <v>1.0570824524311906E-3</v>
       </c>
       <c r="N43" s="10">
-        <f>+N9/J9-1</f>
+        <f t="shared" si="57"/>
         <v>6.9269521410579404E-2</v>
       </c>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="10" t="e">
-        <f>+Q9/P9-1</f>
+      <c r="O43" s="10">
+        <f t="shared" si="57"/>
+        <v>0.10301263362487845</v>
+      </c>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R43" s="10" t="e">
-        <f>+R9/Q9-1</f>
+      <c r="V43" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S43" s="10" t="e">
-        <f>+S9/R9-1</f>
+      <c r="W43" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T43" s="10" t="e">
-        <f>+T9/S9-1</f>
+      <c r="X43" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U43" s="10" t="e">
-        <f>+U9/T9-1</f>
+      <c r="Y43" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V43" s="10">
-        <f>+V9/U9-1</f>
+      <c r="Z43" s="10">
+        <f t="shared" si="58"/>
         <v>8.4326018808777325E-2</v>
       </c>
-      <c r="W43" s="10">
-        <f>+W9/V9-1</f>
+      <c r="AA43" s="10">
+        <f t="shared" si="58"/>
         <v>4.7412546978895742E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>63</v>
       </c>
@@ -4278,69 +4559,76 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="10">
-        <f>+G10/C10-1</f>
+        <f t="shared" si="57"/>
         <v>5.9523809523809534E-2</v>
       </c>
       <c r="H44" s="10">
-        <f>+H10/D10-1</f>
+        <f t="shared" si="57"/>
         <v>0.24833333333333329</v>
       </c>
       <c r="I44" s="10">
-        <f>+I10/E10-1</f>
+        <f t="shared" si="57"/>
         <v>9.1127098321343025E-2</v>
       </c>
       <c r="J44" s="10">
-        <f>+J10/F10-1</f>
+        <f t="shared" si="57"/>
         <v>0.26344086021505375</v>
       </c>
       <c r="K44" s="10">
-        <f>+K10/G10-1</f>
+        <f t="shared" si="57"/>
         <v>0.2219101123595506</v>
       </c>
       <c r="L44" s="10">
-        <f>+L10/H10-1</f>
+        <f t="shared" si="57"/>
         <v>1.735647530040052E-2</v>
       </c>
       <c r="M44" s="10">
-        <f>+M10/I10-1</f>
+        <f t="shared" si="57"/>
         <v>2.7472527472527375E-2</v>
       </c>
       <c r="N44" s="10">
-        <f>+N10/J10-1</f>
+        <f t="shared" si="57"/>
         <v>3.1914893617022155E-3</v>
       </c>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="10" t="e">
-        <f>+Q10/P10-1</f>
+      <c r="O44" s="10">
+        <f t="shared" si="57"/>
+        <v>-1.1494252873562871E-3</v>
+      </c>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R44" s="10" t="e">
-        <f>+R10/Q10-1</f>
+      <c r="V44" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S44" s="10" t="e">
-        <f>+S10/R10-1</f>
+      <c r="W44" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T44" s="10" t="e">
-        <f>+T10/S10-1</f>
+      <c r="X44" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U44" s="10" t="e">
-        <f>+U10/T10-1</f>
+      <c r="Y44" s="10" t="e">
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V44" s="10">
-        <f>+V10/U10-1</f>
+      <c r="Z44" s="10">
+        <f t="shared" si="58"/>
         <v>0.16140350877192988</v>
       </c>
-      <c r="W44" s="10">
-        <f>+W10/V10-1</f>
+      <c r="AA44" s="10">
+        <f t="shared" si="58"/>
         <v>6.042296072507547E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>68</v>
       </c>
@@ -4349,69 +4637,76 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="10">
-        <f t="shared" ref="G45:I47" si="56">+G13/C13-1</f>
+        <f t="shared" ref="G45:I47" si="59">+G13/C13-1</f>
         <v>7.1452199801521621E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.15183752417794971</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.10289389067524124</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" ref="J45:J47" si="57">+J13/F13-1</f>
+        <f t="shared" ref="J45:J47" si="60">+J13/F13-1</f>
         <v>0.3356973995271868</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" ref="K45:N47" si="58">+K13/G13-1</f>
+        <f t="shared" ref="K45:O47" si="61">+K13/G13-1</f>
         <v>0.16085211485026241</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-0.30702490904002244</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-6.095944871455039E-3</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.25250737463126849</v>
       </c>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="10" t="e">
-        <f t="shared" ref="Q45:U47" si="59">+Q13/P13-1</f>
+      <c r="O45" s="10">
+        <f t="shared" si="61"/>
+        <v>-1.6223404255319096E-2</v>
+      </c>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="10" t="e">
+        <f t="shared" ref="U45:Y47" si="62">+U13/T13-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R45" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="V45" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S45" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="W45" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T45" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="X45" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U45" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="Y45" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V45" s="10">
-        <f t="shared" ref="V45:W47" si="60">+V13/U13-1</f>
+      <c r="Z45" s="10">
+        <f t="shared" ref="Z45:AA47" si="63">+Z13/Y13-1</f>
         <v>0.15658362989323837</v>
       </c>
-      <c r="W45" s="10">
-        <f t="shared" si="60"/>
+      <c r="AA45" s="10">
+        <f t="shared" si="63"/>
         <v>1.8389982110912362E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>69</v>
       </c>
@@ -4420,69 +4715,76 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-1.3605442176870763E-2</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>3.0501089324618702E-2</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>2.6051188299817118E-2</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.10140562248995977</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>4.403183023872681E-2</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>7.2410147991543328E-2</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>6.1469933184855163E-2</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>8.6599817684594349E-2</v>
       </c>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="O46" s="10">
+        <f t="shared" si="61"/>
+        <v>0.24085365853658547</v>
+      </c>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R46" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="V46" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S46" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="W46" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T46" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="X46" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U46" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="Y46" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V46" s="10">
-        <f t="shared" si="60"/>
+      <c r="Z46" s="10">
+        <f t="shared" si="63"/>
         <v>4.5824847250509171E-2</v>
       </c>
-      <c r="W46" s="10">
-        <f t="shared" si="60"/>
+      <c r="AA46" s="10">
+        <f t="shared" si="63"/>
         <v>6.669912366114894E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>70</v>
       </c>
@@ -4491,69 +4793,76 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-3.5294117647058809E-2</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-8.6419753086419804E-2</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>7.9487179487179427E-2</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>7.9545454545454586E-2</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.29268292682926833</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.2081081081081082</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.178147268408551</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.17894736842105252</v>
       </c>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="O47" s="10">
+        <f t="shared" si="61"/>
+        <v>6.3679245283018826E-2</v>
+      </c>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R47" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="V47" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S47" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="W47" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T47" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="X47" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U47" s="10" t="e">
-        <f t="shared" si="59"/>
+      <c r="Y47" s="10" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V47" s="10">
-        <f t="shared" si="60"/>
+      <c r="Z47" s="10">
+        <f t="shared" si="63"/>
         <v>7.3924731182795078E-3</v>
       </c>
-      <c r="W47" s="10">
-        <f t="shared" si="60"/>
+      <c r="AA47" s="10">
+        <f t="shared" si="63"/>
         <v>0.21080720480320214</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4566,86 +4875,93 @@
         <v>3.4888130451270483E-2</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" ref="H48:J48" si="61">H16/D16-1</f>
+        <f t="shared" ref="H48:J48" si="64">H16/D16-1</f>
         <v>8.9650009358038574E-2</v>
       </c>
       <c r="I48" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>7.3178863143857242E-2</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0.23960931005818797</v>
       </c>
       <c r="K48" s="12">
-        <f t="shared" ref="K48" si="62">K16/G16-1</f>
+        <f t="shared" ref="K48" si="65">K16/G16-1</f>
         <v>0.1273360205203371</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" ref="L48" si="63">L16/H16-1</f>
+        <f t="shared" ref="L48" si="66">L16/H16-1</f>
         <v>2.2329096530401937E-2</v>
       </c>
       <c r="M48" s="12">
-        <f t="shared" ref="M48" si="64">M16/I16-1</f>
+        <f t="shared" ref="M48" si="67">M16/I16-1</f>
         <v>2.982292637465056E-2</v>
       </c>
       <c r="N48" s="12">
-        <f t="shared" ref="N48" si="65">N16/J16-1</f>
+        <f t="shared" ref="N48:O48" si="68">N16/J16-1</f>
         <v>1.8608549874266522E-2</v>
       </c>
-      <c r="O48" s="4"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="12">
-        <f t="shared" ref="Q48:T48" si="66">Q16/P16-1</f>
+      <c r="O48" s="12">
+        <f t="shared" si="68"/>
+        <v>7.1347310255160057E-2</v>
+      </c>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="12"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="12">
+        <f t="shared" ref="U48:X48" si="69">U16/T16-1</f>
         <v>7.8713210130047839E-2</v>
       </c>
-      <c r="R48" s="12">
-        <f t="shared" si="66"/>
+      <c r="V48" s="12">
+        <f t="shared" si="69"/>
         <v>-0.22017766497461932</v>
       </c>
-      <c r="S48" s="12">
-        <f t="shared" si="66"/>
+      <c r="W48" s="12">
+        <f t="shared" si="69"/>
         <v>0.15183075671277457</v>
       </c>
-      <c r="T48" s="12">
-        <f t="shared" si="66"/>
+      <c r="X48" s="12">
+        <f t="shared" si="69"/>
         <v>6.0139399076952094E-2</v>
       </c>
-      <c r="U48" s="12">
-        <f>U16/T16-1</f>
+      <c r="Y48" s="12">
+        <f>Y16/X16-1</f>
         <v>-4.8154235706987736E-2</v>
       </c>
-      <c r="V48" s="12">
-        <f>V16/U16-1</f>
+      <c r="Z48" s="12">
+        <f>Z16/Y16-1</f>
         <v>0.10528772109954732</v>
       </c>
-      <c r="W48" s="12">
-        <f>W16/V16-1</f>
+      <c r="AA48" s="12">
+        <f>AA16/Z16-1</f>
         <v>4.7629101042942157E-2</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" ref="C49:G49" si="67">C18/C16</f>
+        <f t="shared" ref="C49:G49" si="70">C18/C16</f>
         <v>0.44804702313234734</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.50870297585626056</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.49258209701616934</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.44638403990024939</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.51227555881275189</v>
       </c>
       <c r="H49" s="10">
@@ -4653,85 +4969,92 @@
         <v>0.50824458948814843</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" ref="I49:J49" si="68">I18/I16</f>
+        <f t="shared" ref="I49:J49" si="71">I18/I16</f>
         <v>0.51273687480584029</v>
       </c>
       <c r="J49" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>0.49790444258172672</v>
       </c>
       <c r="K49" s="10">
-        <f t="shared" ref="K49:N49" si="69">K18/K16</f>
+        <f t="shared" ref="K49:N49" si="72">K18/K16</f>
         <v>0.52088412156671537</v>
       </c>
       <c r="L49" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.51696908602150538</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.51809954751131226</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.50822909809084926</v>
       </c>
-      <c r="O49" s="4"/>
-      <c r="P49" s="10">
-        <f t="shared" ref="P49:T49" si="70">P18/P16</f>
+      <c r="O49" s="10">
+        <f t="shared" ref="O49" si="73">O18/O16</f>
+        <v>0.51107402912621358</v>
+      </c>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="10">
+        <f t="shared" ref="T49:X49" si="74">T18/T16</f>
         <v>0.51850330823636781</v>
       </c>
-      <c r="Q49" s="10">
-        <f t="shared" si="70"/>
+      <c r="U49" s="10">
+        <f t="shared" si="74"/>
         <v>0.52000846023688663</v>
       </c>
-      <c r="R49" s="10">
-        <f t="shared" si="70"/>
+      <c r="V49" s="10">
+        <f t="shared" si="74"/>
         <v>0.50024410089503657</v>
       </c>
-      <c r="S49" s="10">
-        <f t="shared" si="70"/>
+      <c r="W49" s="10">
+        <f t="shared" si="74"/>
         <v>0.50696995384760291</v>
       </c>
-      <c r="T49" s="10">
-        <f t="shared" si="70"/>
+      <c r="X49" s="10">
+        <f t="shared" si="74"/>
         <v>0.47283550264315222</v>
       </c>
-      <c r="U49" s="10">
-        <f>U18/U16</f>
+      <c r="Y49" s="10">
+        <f>Y18/Y16</f>
         <v>0.47524151771129886</v>
       </c>
-      <c r="V49" s="10">
-        <f>V18/V16</f>
+      <c r="Z49" s="10">
+        <f>Z18/Z16</f>
         <v>0.5077481737955496</v>
       </c>
-      <c r="W49" s="10">
-        <f>W18/W16</f>
+      <c r="AA49" s="10">
+        <f>AA18/AA16</f>
         <v>0.51610172907178264</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" ref="C50:G50" si="71">C25/C16</f>
+        <f t="shared" ref="C50:G50" si="75">C25/C16</f>
         <v>1.1376564277588168E-2</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>3.2753134942915964E-2</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>6.8344724120686776E-2</v>
       </c>
       <c r="F50" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>-7.813798836242726E-2</v>
       </c>
       <c r="G50" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>6.1561011359472333E-2</v>
       </c>
       <c r="H50" s="10">
@@ -4739,85 +5062,92 @@
         <v>5.960151150807283E-2</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" ref="I50:J50" si="72">I25/I16</f>
+        <f t="shared" ref="I50:J50" si="76">I25/I16</f>
         <v>9.2575333954644304E-2</v>
       </c>
       <c r="J50" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>9.5557418273260683E-3</v>
       </c>
       <c r="K50" s="10">
-        <f t="shared" ref="K50:N50" si="73">K25/K16</f>
+        <f t="shared" ref="K50:N50" si="77">K25/K16</f>
         <v>9.8976109215017066E-2</v>
       </c>
       <c r="L50" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>9.1901881720430109E-2</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.11101055806938159</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.6991441737985518E-2</v>
       </c>
-      <c r="O50" s="4"/>
-      <c r="P50" s="10">
-        <f t="shared" ref="P50:T50" si="74">P25/P16</f>
+      <c r="O50" s="10">
+        <f t="shared" ref="O50" si="78">O25/O16</f>
+        <v>0.10709951456310679</v>
+      </c>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="10">
+        <f t="shared" ref="T50:X50" si="79">T25/T16</f>
         <v>0.1080082135523614</v>
       </c>
-      <c r="Q50" s="10">
-        <f t="shared" si="74"/>
+      <c r="U50" s="10">
+        <f t="shared" si="79"/>
         <v>0.11252115059221658</v>
       </c>
-      <c r="R50" s="10">
-        <f t="shared" si="74"/>
+      <c r="V50" s="10">
+        <f t="shared" si="79"/>
         <v>4.0412259289395173E-2</v>
       </c>
-      <c r="S50" s="10">
-        <f t="shared" si="74"/>
+      <c r="W50" s="10">
+        <f t="shared" si="79"/>
         <v>9.3576339832344355E-2</v>
       </c>
-      <c r="T50" s="10">
-        <f t="shared" si="74"/>
+      <c r="X50" s="10">
+        <f t="shared" si="79"/>
         <v>2.9718804140198125E-2</v>
       </c>
-      <c r="U50" s="10">
-        <f>U25/U16</f>
+      <c r="Y50" s="10">
+        <f>Y25/Y16</f>
         <v>1.2460913800345358E-2</v>
       </c>
-      <c r="V50" s="10">
-        <f>V25/V16</f>
+      <c r="Z50" s="10">
+        <f>Z25/Z16</f>
         <v>5.6327323396529155E-2</v>
       </c>
-      <c r="W50" s="10">
-        <f>W25/W16</f>
+      <c r="AA50" s="10">
+        <f>AA25/AA16</f>
         <v>8.2866470517109353E-2</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" ref="C51:G51" si="75">C34/C16</f>
+        <f t="shared" ref="C51:G51" si="80">C34/C16</f>
         <v>-7.2051573758058398E-3</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>1.5721504772599662E-2</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>4.3340556759459907E-2</v>
       </c>
       <c r="F51" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>4.3640897755610969E-3</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>3.1146940271161598E-2</v>
       </c>
       <c r="H51" s="10">
@@ -4825,85 +5155,92 @@
         <v>3.2634833390587425E-2</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" ref="I51:J51" si="76">I34/I16</f>
+        <f t="shared" ref="I51:J51" si="81">I34/I16</f>
         <v>6.8499534016775401E-2</v>
       </c>
       <c r="J51" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>3.3528918692372171E-3</v>
       </c>
       <c r="K51" s="10">
-        <f t="shared" ref="K51:N51" si="77">K34/K16</f>
+        <f t="shared" ref="K51:N51" si="82">K34/K16</f>
         <v>6.9397042093287828E-2</v>
       </c>
       <c r="L51" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>6.2163978494623656E-2</v>
       </c>
       <c r="M51" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>6.953242835595777E-2</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>1.3495720868992759E-2</v>
       </c>
-      <c r="O51" s="4"/>
-      <c r="P51" s="10">
-        <f t="shared" ref="P51:T51" si="78">P34/P16</f>
+      <c r="O51" s="10">
+        <f t="shared" ref="O51" si="83">O34/O16</f>
+        <v>7.3422330097087374E-2</v>
+      </c>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="10">
+        <f t="shared" ref="T51:X51" si="84">T34/T16</f>
         <v>7.7572438968742871E-2</v>
       </c>
-      <c r="Q51" s="10">
-        <f t="shared" si="78"/>
+      <c r="U51" s="10">
+        <f t="shared" si="84"/>
         <v>8.3544839255499159E-2</v>
       </c>
-      <c r="R51" s="10">
-        <f t="shared" si="78"/>
+      <c r="V51" s="10">
+        <f t="shared" si="84"/>
         <v>2.3379441280173583E-2</v>
       </c>
-      <c r="S51" s="10">
-        <f t="shared" si="78"/>
+      <c r="W51" s="10">
+        <f t="shared" si="84"/>
         <v>9.9698596590373931E-2</v>
       </c>
-      <c r="T51" s="10">
-        <f t="shared" si="78"/>
+      <c r="X51" s="10">
+        <f t="shared" si="84"/>
         <v>2.7186708720181245E-2</v>
       </c>
-      <c r="U51" s="10">
-        <f>U34/U16</f>
+      <c r="Y51" s="10">
+        <f>Y34/Y16</f>
         <v>-3.5935968637700096E-3</v>
       </c>
-      <c r="V51" s="10">
-        <f>V34/V16</f>
+      <c r="Z51" s="10">
+        <f>Z34/Z16</f>
         <v>2.9134822446480598E-3</v>
       </c>
-      <c r="W51" s="10">
-        <f>W34/W16</f>
+      <c r="AA51" s="10">
+        <f>AA34/AA16</f>
         <v>5.4008302768933134E-2</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="10">
-        <f t="shared" ref="C52:G52" si="79">C29/C28</f>
+        <f t="shared" ref="C52:G52" si="85">C29/C28</f>
         <v>1.71875</v>
       </c>
       <c r="D52" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0.21951219512195122</v>
       </c>
       <c r="E52" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0.16871165644171779</v>
       </c>
       <c r="F52" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>3.3816425120772944E-2</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0.30204081632653063</v>
       </c>
       <c r="H52" s="10">
@@ -4911,64 +5248,71 @@
         <v>0.30491803278688523</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" ref="I52:J52" si="80">I29/I28</f>
+        <f t="shared" ref="I52:J52" si="86">I29/I28</f>
         <v>0.22166666666666668</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="K52" s="10">
-        <f t="shared" ref="K52:N52" si="81">K29/K28</f>
+        <f t="shared" ref="K52:N52" si="87">K29/K28</f>
         <v>0.25513698630136988</v>
       </c>
       <c r="L52" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0.23312883435582821</v>
       </c>
       <c r="M52" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0.26</v>
       </c>
       <c r="N52" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0.1134020618556701</v>
       </c>
-      <c r="O52" s="4"/>
-      <c r="P52" s="10">
-        <f t="shared" ref="P52:T52" si="82">P29/P28</f>
+      <c r="O52" s="10">
+        <f t="shared" ref="O52" si="88">O29/O28</f>
+        <v>0.24884080370942813</v>
+      </c>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="10">
+        <f t="shared" ref="T52:X52" si="89">T29/T28</f>
         <v>0.28144720235591081</v>
       </c>
-      <c r="Q52" s="10">
-        <f t="shared" si="82"/>
+      <c r="U52" s="10">
+        <f t="shared" si="89"/>
         <v>0.2501954652071931</v>
       </c>
-      <c r="R52" s="10">
-        <f t="shared" si="82"/>
+      <c r="V52" s="10">
+        <f t="shared" si="89"/>
         <v>0.20242214532871972</v>
       </c>
-      <c r="S52" s="10">
-        <f t="shared" si="82"/>
+      <c r="W52" s="10">
+        <f t="shared" si="89"/>
         <v>0.19427954668105774</v>
       </c>
-      <c r="T52" s="10">
-        <f t="shared" si="82"/>
+      <c r="X52" s="10">
+        <f t="shared" si="89"/>
         <v>0.34536082474226804</v>
       </c>
-      <c r="U52" s="10">
-        <f>U29/U28</f>
+      <c r="Y52" s="10">
+        <f>Y29/Y28</f>
         <v>1.9375</v>
       </c>
-      <c r="V52" s="10">
-        <f>V29/V28</f>
+      <c r="Z52" s="10">
+        <f>Z29/Z28</f>
         <v>0.26470588235294118</v>
       </c>
-      <c r="W52" s="10">
-        <f>W29/W28</f>
+      <c r="AA52" s="10">
+        <f>AA29/AA28</f>
         <v>0.2434065934065934</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4989,8 +5333,12 @@
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
-    </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+    </row>
+    <row r="54" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -5011,8 +5359,12 @@
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
-    </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+    </row>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -5033,8 +5385,12 @@
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
-    </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+    </row>
+    <row r="56" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -5055,8 +5411,12 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
-    </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+    </row>
+    <row r="57" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -5077,8 +5437,12 @@
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
-    </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+    </row>
+    <row r="58" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -5099,8 +5463,12 @@
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
-    </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -5121,8 +5489,12 @@
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
-    </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+    </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -5143,8 +5515,12 @@
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
-    </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -5165,8 +5541,12 @@
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
-    </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -5187,8 +5567,12 @@
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
-    </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -5209,8 +5593,12 @@
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
-    </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -5231,8 +5619,12 @@
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
-    </row>
-    <row r="65" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+    </row>
+    <row r="65" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -5253,8 +5645,12 @@
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
-    </row>
-    <row r="66" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -5275,8 +5671,12 @@
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
-    </row>
-    <row r="67" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+    </row>
+    <row r="67" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -5297,8 +5697,12 @@
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
-    </row>
-    <row r="68" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+    </row>
+    <row r="68" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -5319,8 +5723,12 @@
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
-    </row>
-    <row r="69" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -5341,8 +5749,12 @@
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
-    </row>
-    <row r="70" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+    </row>
+    <row r="70" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -5363,8 +5775,12 @@
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
-    </row>
-    <row r="71" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+    </row>
+    <row r="71" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -5385,8 +5801,12 @@
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
-    </row>
-    <row r="72" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+    </row>
+    <row r="72" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -5407,8 +5827,12 @@
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
-    </row>
-    <row r="73" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -5429,8 +5853,12 @@
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
-    </row>
-    <row r="74" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+    </row>
+    <row r="74" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -5451,8 +5879,12 @@
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
-    </row>
-    <row r="75" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+    </row>
+    <row r="75" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -5473,8 +5905,12 @@
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
-    </row>
-    <row r="76" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+    </row>
+    <row r="76" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -5495,8 +5931,12 @@
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
-    </row>
-    <row r="77" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+    </row>
+    <row r="77" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -5517,8 +5957,12 @@
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
-    </row>
-    <row r="78" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+    </row>
+    <row r="78" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -5539,8 +5983,12 @@
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
-    </row>
-    <row r="79" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+    </row>
+    <row r="79" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -5561,8 +6009,12 @@
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
-    </row>
-    <row r="80" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+    </row>
+    <row r="80" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -5583,8 +6035,12 @@
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -5605,8 +6061,12 @@
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -5627,8 +6087,12 @@
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -5649,8 +6113,12 @@
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -5671,8 +6139,12 @@
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -5693,8 +6165,12 @@
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -5715,8 +6191,12 @@
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -5737,8 +6217,12 @@
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -5759,8 +6243,12 @@
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -5781,8 +6269,12 @@
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="4"/>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -5803,8 +6295,12 @@
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -5825,8 +6321,12 @@
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -5847,8 +6347,12 @@
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -5869,8 +6373,12 @@
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="4"/>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -5891,8 +6399,12 @@
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -5913,8 +6425,12 @@
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -5935,8 +6451,12 @@
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -5957,8 +6477,12 @@
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -5979,8 +6503,12 @@
       <c r="T98" s="4"/>
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -6001,8 +6529,12 @@
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -6023,8 +6555,12 @@
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -6045,8 +6581,12 @@
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -6067,8 +6607,12 @@
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
-    </row>
-    <row r="103" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+    </row>
+    <row r="103" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -6089,8 +6633,12 @@
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
-    </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+    </row>
+    <row r="104" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -6111,8 +6659,12 @@
       <c r="T104" s="4"/>
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
-    </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+    </row>
+    <row r="105" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -6133,8 +6685,12 @@
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
-    </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+    </row>
+    <row r="106" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -6155,8 +6711,12 @@
       <c r="T106" s="4"/>
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
-    </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="4"/>
+    </row>
+    <row r="107" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -6177,8 +6737,12 @@
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
-    </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+    </row>
+    <row r="108" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -6199,8 +6763,12 @@
       <c r="T108" s="4"/>
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
-    </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+    </row>
+    <row r="109" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -6221,8 +6789,12 @@
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
-    </row>
-    <row r="110" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+    </row>
+    <row r="110" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -6243,8 +6815,12 @@
       <c r="T110" s="4"/>
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
-    </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+    </row>
+    <row r="111" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -6265,8 +6841,12 @@
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
-    </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+    </row>
+    <row r="112" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -6287,8 +6867,12 @@
       <c r="T112" s="4"/>
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
-    </row>
-    <row r="113" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+    </row>
+    <row r="113" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -6309,8 +6893,12 @@
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
-    </row>
-    <row r="114" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+    </row>
+    <row r="114" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -6331,8 +6919,12 @@
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
-    </row>
-    <row r="115" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+    </row>
+    <row r="115" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -6353,8 +6945,12 @@
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
-    </row>
-    <row r="116" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+    </row>
+    <row r="116" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -6375,8 +6971,12 @@
       <c r="T116" s="4"/>
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
-    </row>
-    <row r="117" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
+    </row>
+    <row r="117" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -6397,8 +6997,12 @@
       <c r="T117" s="4"/>
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
-    </row>
-    <row r="118" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
+    </row>
+    <row r="118" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -6419,8 +7023,12 @@
       <c r="T118" s="4"/>
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
-    </row>
-    <row r="119" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+    </row>
+    <row r="119" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -6441,8 +7049,12 @@
       <c r="T119" s="4"/>
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
-    </row>
-    <row r="120" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+    </row>
+    <row r="120" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -6463,8 +7075,12 @@
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
-    </row>
-    <row r="121" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
+    </row>
+    <row r="121" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -6485,8 +7101,12 @@
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
       <c r="V121" s="4"/>
-    </row>
-    <row r="122" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
+    </row>
+    <row r="122" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -6507,8 +7127,12 @@
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
-    </row>
-    <row r="123" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W122" s="4"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="4"/>
+    </row>
+    <row r="123" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -6529,8 +7153,12 @@
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
-    </row>
-    <row r="124" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+    </row>
+    <row r="124" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -6551,8 +7179,12 @@
       <c r="T124" s="4"/>
       <c r="U124" s="4"/>
       <c r="V124" s="4"/>
-    </row>
-    <row r="125" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W124" s="4"/>
+      <c r="X124" s="4"/>
+      <c r="Y124" s="4"/>
+      <c r="Z124" s="4"/>
+    </row>
+    <row r="125" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -6573,8 +7205,12 @@
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
       <c r="V125" s="4"/>
-    </row>
-    <row r="126" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W125" s="4"/>
+      <c r="X125" s="4"/>
+      <c r="Y125" s="4"/>
+      <c r="Z125" s="4"/>
+    </row>
+    <row r="126" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -6595,8 +7231,12 @@
       <c r="T126" s="4"/>
       <c r="U126" s="4"/>
       <c r="V126" s="4"/>
-    </row>
-    <row r="127" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W126" s="4"/>
+      <c r="X126" s="4"/>
+      <c r="Y126" s="4"/>
+      <c r="Z126" s="4"/>
+    </row>
+    <row r="127" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -6617,8 +7257,12 @@
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
       <c r="V127" s="4"/>
-    </row>
-    <row r="128" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W127" s="4"/>
+      <c r="X127" s="4"/>
+      <c r="Y127" s="4"/>
+      <c r="Z127" s="4"/>
+    </row>
+    <row r="128" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -6639,8 +7283,12 @@
       <c r="T128" s="4"/>
       <c r="U128" s="4"/>
       <c r="V128" s="4"/>
-    </row>
-    <row r="129" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W128" s="4"/>
+      <c r="X128" s="4"/>
+      <c r="Y128" s="4"/>
+      <c r="Z128" s="4"/>
+    </row>
+    <row r="129" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -6661,8 +7309,12 @@
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
       <c r="V129" s="4"/>
-    </row>
-    <row r="130" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W129" s="4"/>
+      <c r="X129" s="4"/>
+      <c r="Y129" s="4"/>
+      <c r="Z129" s="4"/>
+    </row>
+    <row r="130" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -6683,8 +7335,12 @@
       <c r="T130" s="4"/>
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
-    </row>
-    <row r="131" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W130" s="4"/>
+      <c r="X130" s="4"/>
+      <c r="Y130" s="4"/>
+      <c r="Z130" s="4"/>
+    </row>
+    <row r="131" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -6705,8 +7361,12 @@
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
-    </row>
-    <row r="132" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W131" s="4"/>
+      <c r="X131" s="4"/>
+      <c r="Y131" s="4"/>
+      <c r="Z131" s="4"/>
+    </row>
+    <row r="132" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -6727,8 +7387,12 @@
       <c r="T132" s="4"/>
       <c r="U132" s="4"/>
       <c r="V132" s="4"/>
-    </row>
-    <row r="133" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W132" s="4"/>
+      <c r="X132" s="4"/>
+      <c r="Y132" s="4"/>
+      <c r="Z132" s="4"/>
+    </row>
+    <row r="133" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -6749,8 +7413,12 @@
       <c r="T133" s="4"/>
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
-    </row>
-    <row r="134" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W133" s="4"/>
+      <c r="X133" s="4"/>
+      <c r="Y133" s="4"/>
+      <c r="Z133" s="4"/>
+    </row>
+    <row r="134" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -6771,8 +7439,12 @@
       <c r="T134" s="4"/>
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
-    </row>
-    <row r="135" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W134" s="4"/>
+      <c r="X134" s="4"/>
+      <c r="Y134" s="4"/>
+      <c r="Z134" s="4"/>
+    </row>
+    <row r="135" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -6793,8 +7465,12 @@
       <c r="T135" s="4"/>
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
-    </row>
-    <row r="136" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W135" s="4"/>
+      <c r="X135" s="4"/>
+      <c r="Y135" s="4"/>
+      <c r="Z135" s="4"/>
+    </row>
+    <row r="136" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -6815,8 +7491,12 @@
       <c r="T136" s="4"/>
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
-    </row>
-    <row r="137" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W136" s="4"/>
+      <c r="X136" s="4"/>
+      <c r="Y136" s="4"/>
+      <c r="Z136" s="4"/>
+    </row>
+    <row r="137" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -6837,8 +7517,12 @@
       <c r="T137" s="4"/>
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
-    </row>
-    <row r="138" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W137" s="4"/>
+      <c r="X137" s="4"/>
+      <c r="Y137" s="4"/>
+      <c r="Z137" s="4"/>
+    </row>
+    <row r="138" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -6859,8 +7543,12 @@
       <c r="T138" s="4"/>
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
-    </row>
-    <row r="139" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W138" s="4"/>
+      <c r="X138" s="4"/>
+      <c r="Y138" s="4"/>
+      <c r="Z138" s="4"/>
+    </row>
+    <row r="139" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -6881,8 +7569,12 @@
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
-    </row>
-    <row r="140" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W139" s="4"/>
+      <c r="X139" s="4"/>
+      <c r="Y139" s="4"/>
+      <c r="Z139" s="4"/>
+    </row>
+    <row r="140" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -6903,8 +7595,12 @@
       <c r="T140" s="4"/>
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
-    </row>
-    <row r="141" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W140" s="4"/>
+      <c r="X140" s="4"/>
+      <c r="Y140" s="4"/>
+      <c r="Z140" s="4"/>
+    </row>
+    <row r="141" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -6925,8 +7621,12 @@
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
-    </row>
-    <row r="142" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W141" s="4"/>
+      <c r="X141" s="4"/>
+      <c r="Y141" s="4"/>
+      <c r="Z141" s="4"/>
+    </row>
+    <row r="142" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -6947,8 +7647,12 @@
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
-    </row>
-    <row r="143" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W142" s="4"/>
+      <c r="X142" s="4"/>
+      <c r="Y142" s="4"/>
+      <c r="Z142" s="4"/>
+    </row>
+    <row r="143" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -6969,8 +7673,12 @@
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
-    </row>
-    <row r="144" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W143" s="4"/>
+      <c r="X143" s="4"/>
+      <c r="Y143" s="4"/>
+      <c r="Z143" s="4"/>
+    </row>
+    <row r="144" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -6991,8 +7699,12 @@
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
-    </row>
-    <row r="145" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W144" s="4"/>
+      <c r="X144" s="4"/>
+      <c r="Y144" s="4"/>
+      <c r="Z144" s="4"/>
+    </row>
+    <row r="145" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -7013,8 +7725,12 @@
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
-    </row>
-    <row r="146" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W145" s="4"/>
+      <c r="X145" s="4"/>
+      <c r="Y145" s="4"/>
+      <c r="Z145" s="4"/>
+    </row>
+    <row r="146" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -7035,8 +7751,12 @@
       <c r="T146" s="4"/>
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
-    </row>
-    <row r="147" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W146" s="4"/>
+      <c r="X146" s="4"/>
+      <c r="Y146" s="4"/>
+      <c r="Z146" s="4"/>
+    </row>
+    <row r="147" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -7057,8 +7777,12 @@
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
-    </row>
-    <row r="148" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W147" s="4"/>
+      <c r="X147" s="4"/>
+      <c r="Y147" s="4"/>
+      <c r="Z147" s="4"/>
+    </row>
+    <row r="148" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -7079,8 +7803,12 @@
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
-    </row>
-    <row r="149" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W148" s="4"/>
+      <c r="X148" s="4"/>
+      <c r="Y148" s="4"/>
+      <c r="Z148" s="4"/>
+    </row>
+    <row r="149" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -7101,8 +7829,12 @@
       <c r="T149" s="4"/>
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
-    </row>
-    <row r="150" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W149" s="4"/>
+      <c r="X149" s="4"/>
+      <c r="Y149" s="4"/>
+      <c r="Z149" s="4"/>
+    </row>
+    <row r="150" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -7123,8 +7855,12 @@
       <c r="T150" s="4"/>
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
-    </row>
-    <row r="151" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W150" s="4"/>
+      <c r="X150" s="4"/>
+      <c r="Y150" s="4"/>
+      <c r="Z150" s="4"/>
+    </row>
+    <row r="151" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -7145,8 +7881,12 @@
       <c r="T151" s="4"/>
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
-    </row>
-    <row r="152" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W151" s="4"/>
+      <c r="X151" s="4"/>
+      <c r="Y151" s="4"/>
+      <c r="Z151" s="4"/>
+    </row>
+    <row r="152" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -7167,8 +7907,12 @@
       <c r="T152" s="4"/>
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
-    </row>
-    <row r="153" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W152" s="4"/>
+      <c r="X152" s="4"/>
+      <c r="Y152" s="4"/>
+      <c r="Z152" s="4"/>
+    </row>
+    <row r="153" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -7189,8 +7933,12 @@
       <c r="T153" s="4"/>
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
-    </row>
-    <row r="154" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W153" s="4"/>
+      <c r="X153" s="4"/>
+      <c r="Y153" s="4"/>
+      <c r="Z153" s="4"/>
+    </row>
+    <row r="154" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -7211,8 +7959,12 @@
       <c r="T154" s="4"/>
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
-    </row>
-    <row r="155" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W154" s="4"/>
+      <c r="X154" s="4"/>
+      <c r="Y154" s="4"/>
+      <c r="Z154" s="4"/>
+    </row>
+    <row r="155" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -7233,8 +7985,12 @@
       <c r="T155" s="4"/>
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
-    </row>
-    <row r="156" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W155" s="4"/>
+      <c r="X155" s="4"/>
+      <c r="Y155" s="4"/>
+      <c r="Z155" s="4"/>
+    </row>
+    <row r="156" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -7255,8 +8011,12 @@
       <c r="T156" s="4"/>
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
-    </row>
-    <row r="157" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W156" s="4"/>
+      <c r="X156" s="4"/>
+      <c r="Y156" s="4"/>
+      <c r="Z156" s="4"/>
+    </row>
+    <row r="157" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -7277,8 +8037,12 @@
       <c r="T157" s="4"/>
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
-    </row>
-    <row r="158" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W157" s="4"/>
+      <c r="X157" s="4"/>
+      <c r="Y157" s="4"/>
+      <c r="Z157" s="4"/>
+    </row>
+    <row r="158" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -7299,8 +8063,12 @@
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
       <c r="V158" s="4"/>
-    </row>
-    <row r="159" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W158" s="4"/>
+      <c r="X158" s="4"/>
+      <c r="Y158" s="4"/>
+      <c r="Z158" s="4"/>
+    </row>
+    <row r="159" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -7321,8 +8089,12 @@
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
       <c r="V159" s="4"/>
-    </row>
-    <row r="160" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+    </row>
+    <row r="160" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -7343,8 +8115,12 @@
       <c r="T160" s="4"/>
       <c r="U160" s="4"/>
       <c r="V160" s="4"/>
-    </row>
-    <row r="161" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W160" s="4"/>
+      <c r="X160" s="4"/>
+      <c r="Y160" s="4"/>
+      <c r="Z160" s="4"/>
+    </row>
+    <row r="161" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -7365,8 +8141,12 @@
       <c r="T161" s="4"/>
       <c r="U161" s="4"/>
       <c r="V161" s="4"/>
-    </row>
-    <row r="162" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+      <c r="Z161" s="4"/>
+    </row>
+    <row r="162" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -7387,8 +8167,12 @@
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
-    </row>
-    <row r="163" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+      <c r="Z162" s="4"/>
+    </row>
+    <row r="163" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -7409,8 +8193,12 @@
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
       <c r="V163" s="4"/>
-    </row>
-    <row r="164" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+      <c r="Z163" s="4"/>
+    </row>
+    <row r="164" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -7431,8 +8219,12 @@
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
-    </row>
-    <row r="165" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+      <c r="Z164" s="4"/>
+    </row>
+    <row r="165" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -7453,8 +8245,12 @@
       <c r="T165" s="4"/>
       <c r="U165" s="4"/>
       <c r="V165" s="4"/>
-    </row>
-    <row r="166" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W165" s="4"/>
+      <c r="X165" s="4"/>
+      <c r="Y165" s="4"/>
+      <c r="Z165" s="4"/>
+    </row>
+    <row r="166" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -7475,8 +8271,12 @@
       <c r="T166" s="4"/>
       <c r="U166" s="4"/>
       <c r="V166" s="4"/>
-    </row>
-    <row r="167" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W166" s="4"/>
+      <c r="X166" s="4"/>
+      <c r="Y166" s="4"/>
+      <c r="Z166" s="4"/>
+    </row>
+    <row r="167" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -7497,8 +8297,12 @@
       <c r="T167" s="4"/>
       <c r="U167" s="4"/>
       <c r="V167" s="4"/>
-    </row>
-    <row r="168" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W167" s="4"/>
+      <c r="X167" s="4"/>
+      <c r="Y167" s="4"/>
+      <c r="Z167" s="4"/>
+    </row>
+    <row r="168" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -7519,8 +8323,12 @@
       <c r="T168" s="4"/>
       <c r="U168" s="4"/>
       <c r="V168" s="4"/>
-    </row>
-    <row r="169" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W168" s="4"/>
+      <c r="X168" s="4"/>
+      <c r="Y168" s="4"/>
+      <c r="Z168" s="4"/>
+    </row>
+    <row r="169" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -7541,8 +8349,12 @@
       <c r="T169" s="4"/>
       <c r="U169" s="4"/>
       <c r="V169" s="4"/>
-    </row>
-    <row r="170" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W169" s="4"/>
+      <c r="X169" s="4"/>
+      <c r="Y169" s="4"/>
+      <c r="Z169" s="4"/>
+    </row>
+    <row r="170" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -7563,8 +8375,12 @@
       <c r="T170" s="4"/>
       <c r="U170" s="4"/>
       <c r="V170" s="4"/>
-    </row>
-    <row r="171" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+      <c r="Z170" s="4"/>
+    </row>
+    <row r="171" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -7585,8 +8401,12 @@
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
-    </row>
-    <row r="172" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
+      <c r="Y171" s="4"/>
+      <c r="Z171" s="4"/>
+    </row>
+    <row r="172" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -7607,8 +8427,12 @@
       <c r="T172" s="4"/>
       <c r="U172" s="4"/>
       <c r="V172" s="4"/>
-    </row>
-    <row r="173" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+      <c r="Z172" s="4"/>
+    </row>
+    <row r="173" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -7629,8 +8453,12 @@
       <c r="T173" s="4"/>
       <c r="U173" s="4"/>
       <c r="V173" s="4"/>
-    </row>
-    <row r="174" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+      <c r="Z173" s="4"/>
+    </row>
+    <row r="174" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -7651,8 +8479,12 @@
       <c r="T174" s="4"/>
       <c r="U174" s="4"/>
       <c r="V174" s="4"/>
-    </row>
-    <row r="175" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+      <c r="Z174" s="4"/>
+    </row>
+    <row r="175" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -7673,8 +8505,12 @@
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
-    </row>
-    <row r="176" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+      <c r="Z175" s="4"/>
+    </row>
+    <row r="176" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -7695,8 +8531,12 @@
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
       <c r="V176" s="4"/>
-    </row>
-    <row r="177" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+      <c r="Z176" s="4"/>
+    </row>
+    <row r="177" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -7717,8 +8557,12 @@
       <c r="T177" s="4"/>
       <c r="U177" s="4"/>
       <c r="V177" s="4"/>
-    </row>
-    <row r="178" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W177" s="4"/>
+      <c r="X177" s="4"/>
+      <c r="Y177" s="4"/>
+      <c r="Z177" s="4"/>
+    </row>
+    <row r="178" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -7739,8 +8583,12 @@
       <c r="T178" s="4"/>
       <c r="U178" s="4"/>
       <c r="V178" s="4"/>
-    </row>
-    <row r="179" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W178" s="4"/>
+      <c r="X178" s="4"/>
+      <c r="Y178" s="4"/>
+      <c r="Z178" s="4"/>
+    </row>
+    <row r="179" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -7761,8 +8609,12 @@
       <c r="T179" s="4"/>
       <c r="U179" s="4"/>
       <c r="V179" s="4"/>
-    </row>
-    <row r="180" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W179" s="4"/>
+      <c r="X179" s="4"/>
+      <c r="Y179" s="4"/>
+      <c r="Z179" s="4"/>
+    </row>
+    <row r="180" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -7783,8 +8635,12 @@
       <c r="T180" s="4"/>
       <c r="U180" s="4"/>
       <c r="V180" s="4"/>
-    </row>
-    <row r="181" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W180" s="4"/>
+      <c r="X180" s="4"/>
+      <c r="Y180" s="4"/>
+      <c r="Z180" s="4"/>
+    </row>
+    <row r="181" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -7805,8 +8661,12 @@
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
       <c r="V181" s="4"/>
-    </row>
-    <row r="182" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W181" s="4"/>
+      <c r="X181" s="4"/>
+      <c r="Y181" s="4"/>
+      <c r="Z181" s="4"/>
+    </row>
+    <row r="182" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -7827,8 +8687,12 @@
       <c r="T182" s="4"/>
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
-    </row>
-    <row r="183" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+      <c r="Z182" s="4"/>
+    </row>
+    <row r="183" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -7849,8 +8713,12 @@
       <c r="T183" s="4"/>
       <c r="U183" s="4"/>
       <c r="V183" s="4"/>
-    </row>
-    <row r="184" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W183" s="4"/>
+      <c r="X183" s="4"/>
+      <c r="Y183" s="4"/>
+      <c r="Z183" s="4"/>
+    </row>
+    <row r="184" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -7871,8 +8739,12 @@
       <c r="T184" s="4"/>
       <c r="U184" s="4"/>
       <c r="V184" s="4"/>
-    </row>
-    <row r="185" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+      <c r="Z184" s="4"/>
+    </row>
+    <row r="185" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -7893,8 +8765,12 @@
       <c r="T185" s="4"/>
       <c r="U185" s="4"/>
       <c r="V185" s="4"/>
-    </row>
-    <row r="186" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W185" s="4"/>
+      <c r="X185" s="4"/>
+      <c r="Y185" s="4"/>
+      <c r="Z185" s="4"/>
+    </row>
+    <row r="186" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -7915,8 +8791,12 @@
       <c r="T186" s="4"/>
       <c r="U186" s="4"/>
       <c r="V186" s="4"/>
-    </row>
-    <row r="187" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W186" s="4"/>
+      <c r="X186" s="4"/>
+      <c r="Y186" s="4"/>
+      <c r="Z186" s="4"/>
+    </row>
+    <row r="187" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -7937,8 +8817,12 @@
       <c r="T187" s="4"/>
       <c r="U187" s="4"/>
       <c r="V187" s="4"/>
-    </row>
-    <row r="188" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W187" s="4"/>
+      <c r="X187" s="4"/>
+      <c r="Y187" s="4"/>
+      <c r="Z187" s="4"/>
+    </row>
+    <row r="188" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -7959,8 +8843,12 @@
       <c r="T188" s="4"/>
       <c r="U188" s="4"/>
       <c r="V188" s="4"/>
-    </row>
-    <row r="189" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W188" s="4"/>
+      <c r="X188" s="4"/>
+      <c r="Y188" s="4"/>
+      <c r="Z188" s="4"/>
+    </row>
+    <row r="189" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -7981,8 +8869,12 @@
       <c r="T189" s="4"/>
       <c r="U189" s="4"/>
       <c r="V189" s="4"/>
-    </row>
-    <row r="190" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+    </row>
+    <row r="190" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -8003,8 +8895,12 @@
       <c r="T190" s="4"/>
       <c r="U190" s="4"/>
       <c r="V190" s="4"/>
-    </row>
-    <row r="191" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W190" s="4"/>
+      <c r="X190" s="4"/>
+      <c r="Y190" s="4"/>
+      <c r="Z190" s="4"/>
+    </row>
+    <row r="191" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -8025,8 +8921,12 @@
       <c r="T191" s="4"/>
       <c r="U191" s="4"/>
       <c r="V191" s="4"/>
-    </row>
-    <row r="192" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W191" s="4"/>
+      <c r="X191" s="4"/>
+      <c r="Y191" s="4"/>
+      <c r="Z191" s="4"/>
+    </row>
+    <row r="192" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -8047,8 +8947,12 @@
       <c r="T192" s="4"/>
       <c r="U192" s="4"/>
       <c r="V192" s="4"/>
-    </row>
-    <row r="193" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W192" s="4"/>
+      <c r="X192" s="4"/>
+      <c r="Y192" s="4"/>
+      <c r="Z192" s="4"/>
+    </row>
+    <row r="193" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -8069,8 +8973,12 @@
       <c r="T193" s="4"/>
       <c r="U193" s="4"/>
       <c r="V193" s="4"/>
-    </row>
-    <row r="194" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W193" s="4"/>
+      <c r="X193" s="4"/>
+      <c r="Y193" s="4"/>
+      <c r="Z193" s="4"/>
+    </row>
+    <row r="194" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -8091,8 +8999,12 @@
       <c r="T194" s="4"/>
       <c r="U194" s="4"/>
       <c r="V194" s="4"/>
-    </row>
-    <row r="195" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W194" s="4"/>
+      <c r="X194" s="4"/>
+      <c r="Y194" s="4"/>
+      <c r="Z194" s="4"/>
+    </row>
+    <row r="195" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -8113,8 +9025,12 @@
       <c r="T195" s="4"/>
       <c r="U195" s="4"/>
       <c r="V195" s="4"/>
-    </row>
-    <row r="196" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W195" s="4"/>
+      <c r="X195" s="4"/>
+      <c r="Y195" s="4"/>
+      <c r="Z195" s="4"/>
+    </row>
+    <row r="196" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -8135,8 +9051,12 @@
       <c r="T196" s="4"/>
       <c r="U196" s="4"/>
       <c r="V196" s="4"/>
-    </row>
-    <row r="197" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W196" s="4"/>
+      <c r="X196" s="4"/>
+      <c r="Y196" s="4"/>
+      <c r="Z196" s="4"/>
+    </row>
+    <row r="197" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -8157,8 +9077,12 @@
       <c r="T197" s="4"/>
       <c r="U197" s="4"/>
       <c r="V197" s="4"/>
-    </row>
-    <row r="198" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W197" s="4"/>
+      <c r="X197" s="4"/>
+      <c r="Y197" s="4"/>
+      <c r="Z197" s="4"/>
+    </row>
+    <row r="198" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -8179,8 +9103,12 @@
       <c r="T198" s="4"/>
       <c r="U198" s="4"/>
       <c r="V198" s="4"/>
-    </row>
-    <row r="199" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W198" s="4"/>
+      <c r="X198" s="4"/>
+      <c r="Y198" s="4"/>
+      <c r="Z198" s="4"/>
+    </row>
+    <row r="199" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -8201,8 +9129,12 @@
       <c r="T199" s="4"/>
       <c r="U199" s="4"/>
       <c r="V199" s="4"/>
-    </row>
-    <row r="200" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W199" s="4"/>
+      <c r="X199" s="4"/>
+      <c r="Y199" s="4"/>
+      <c r="Z199" s="4"/>
+    </row>
+    <row r="200" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -8223,8 +9155,12 @@
       <c r="T200" s="4"/>
       <c r="U200" s="4"/>
       <c r="V200" s="4"/>
-    </row>
-    <row r="201" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W200" s="4"/>
+      <c r="X200" s="4"/>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="4"/>
+    </row>
+    <row r="201" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -8245,8 +9181,12 @@
       <c r="T201" s="4"/>
       <c r="U201" s="4"/>
       <c r="V201" s="4"/>
-    </row>
-    <row r="202" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W201" s="4"/>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+    </row>
+    <row r="202" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -8267,8 +9207,12 @@
       <c r="T202" s="4"/>
       <c r="U202" s="4"/>
       <c r="V202" s="4"/>
-    </row>
-    <row r="203" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W202" s="4"/>
+      <c r="X202" s="4"/>
+      <c r="Y202" s="4"/>
+      <c r="Z202" s="4"/>
+    </row>
+    <row r="203" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -8289,8 +9233,12 @@
       <c r="T203" s="4"/>
       <c r="U203" s="4"/>
       <c r="V203" s="4"/>
-    </row>
-    <row r="204" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W203" s="4"/>
+      <c r="X203" s="4"/>
+      <c r="Y203" s="4"/>
+      <c r="Z203" s="4"/>
+    </row>
+    <row r="204" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -8311,8 +9259,12 @@
       <c r="T204" s="4"/>
       <c r="U204" s="4"/>
       <c r="V204" s="4"/>
-    </row>
-    <row r="205" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W204" s="4"/>
+      <c r="X204" s="4"/>
+      <c r="Y204" s="4"/>
+      <c r="Z204" s="4"/>
+    </row>
+    <row r="205" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -8333,8 +9285,12 @@
       <c r="T205" s="4"/>
       <c r="U205" s="4"/>
       <c r="V205" s="4"/>
-    </row>
-    <row r="206" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W205" s="4"/>
+      <c r="X205" s="4"/>
+      <c r="Y205" s="4"/>
+      <c r="Z205" s="4"/>
+    </row>
+    <row r="206" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -8355,8 +9311,12 @@
       <c r="T206" s="4"/>
       <c r="U206" s="4"/>
       <c r="V206" s="4"/>
-    </row>
-    <row r="207" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W206" s="4"/>
+      <c r="X206" s="4"/>
+      <c r="Y206" s="4"/>
+      <c r="Z206" s="4"/>
+    </row>
+    <row r="207" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -8377,8 +9337,12 @@
       <c r="T207" s="4"/>
       <c r="U207" s="4"/>
       <c r="V207" s="4"/>
-    </row>
-    <row r="208" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W207" s="4"/>
+      <c r="X207" s="4"/>
+      <c r="Y207" s="4"/>
+      <c r="Z207" s="4"/>
+    </row>
+    <row r="208" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -8399,8 +9363,12 @@
       <c r="T208" s="4"/>
       <c r="U208" s="4"/>
       <c r="V208" s="4"/>
-    </row>
-    <row r="209" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W208" s="4"/>
+      <c r="X208" s="4"/>
+      <c r="Y208" s="4"/>
+      <c r="Z208" s="4"/>
+    </row>
+    <row r="209" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -8421,8 +9389,12 @@
       <c r="T209" s="4"/>
       <c r="U209" s="4"/>
       <c r="V209" s="4"/>
-    </row>
-    <row r="210" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W209" s="4"/>
+      <c r="X209" s="4"/>
+      <c r="Y209" s="4"/>
+      <c r="Z209" s="4"/>
+    </row>
+    <row r="210" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -8443,8 +9415,12 @@
       <c r="T210" s="4"/>
       <c r="U210" s="4"/>
       <c r="V210" s="4"/>
-    </row>
-    <row r="211" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W210" s="4"/>
+      <c r="X210" s="4"/>
+      <c r="Y210" s="4"/>
+      <c r="Z210" s="4"/>
+    </row>
+    <row r="211" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -8465,8 +9441,12 @@
       <c r="T211" s="4"/>
       <c r="U211" s="4"/>
       <c r="V211" s="4"/>
-    </row>
-    <row r="212" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W211" s="4"/>
+      <c r="X211" s="4"/>
+      <c r="Y211" s="4"/>
+      <c r="Z211" s="4"/>
+    </row>
+    <row r="212" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -8487,8 +9467,12 @@
       <c r="T212" s="4"/>
       <c r="U212" s="4"/>
       <c r="V212" s="4"/>
-    </row>
-    <row r="213" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W212" s="4"/>
+      <c r="X212" s="4"/>
+      <c r="Y212" s="4"/>
+      <c r="Z212" s="4"/>
+    </row>
+    <row r="213" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -8509,8 +9493,12 @@
       <c r="T213" s="4"/>
       <c r="U213" s="4"/>
       <c r="V213" s="4"/>
-    </row>
-    <row r="214" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W213" s="4"/>
+      <c r="X213" s="4"/>
+      <c r="Y213" s="4"/>
+      <c r="Z213" s="4"/>
+    </row>
+    <row r="214" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -8531,8 +9519,12 @@
       <c r="T214" s="4"/>
       <c r="U214" s="4"/>
       <c r="V214" s="4"/>
-    </row>
-    <row r="215" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W214" s="4"/>
+      <c r="X214" s="4"/>
+      <c r="Y214" s="4"/>
+      <c r="Z214" s="4"/>
+    </row>
+    <row r="215" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -8553,8 +9545,12 @@
       <c r="T215" s="4"/>
       <c r="U215" s="4"/>
       <c r="V215" s="4"/>
-    </row>
-    <row r="216" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W215" s="4"/>
+      <c r="X215" s="4"/>
+      <c r="Y215" s="4"/>
+      <c r="Z215" s="4"/>
+    </row>
+    <row r="216" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -8575,8 +9571,12 @@
       <c r="T216" s="4"/>
       <c r="U216" s="4"/>
       <c r="V216" s="4"/>
-    </row>
-    <row r="217" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W216" s="4"/>
+      <c r="X216" s="4"/>
+      <c r="Y216" s="4"/>
+      <c r="Z216" s="4"/>
+    </row>
+    <row r="217" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -8597,8 +9597,12 @@
       <c r="T217" s="4"/>
       <c r="U217" s="4"/>
       <c r="V217" s="4"/>
-    </row>
-    <row r="218" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W217" s="4"/>
+      <c r="X217" s="4"/>
+      <c r="Y217" s="4"/>
+      <c r="Z217" s="4"/>
+    </row>
+    <row r="218" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -8619,8 +9623,12 @@
       <c r="T218" s="4"/>
       <c r="U218" s="4"/>
       <c r="V218" s="4"/>
-    </row>
-    <row r="219" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W218" s="4"/>
+      <c r="X218" s="4"/>
+      <c r="Y218" s="4"/>
+      <c r="Z218" s="4"/>
+    </row>
+    <row r="219" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -8641,8 +9649,12 @@
       <c r="T219" s="4"/>
       <c r="U219" s="4"/>
       <c r="V219" s="4"/>
-    </row>
-    <row r="220" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W219" s="4"/>
+      <c r="X219" s="4"/>
+      <c r="Y219" s="4"/>
+      <c r="Z219" s="4"/>
+    </row>
+    <row r="220" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -8663,8 +9675,12 @@
       <c r="T220" s="4"/>
       <c r="U220" s="4"/>
       <c r="V220" s="4"/>
-    </row>
-    <row r="221" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W220" s="4"/>
+      <c r="X220" s="4"/>
+      <c r="Y220" s="4"/>
+      <c r="Z220" s="4"/>
+    </row>
+    <row r="221" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -8685,8 +9701,12 @@
       <c r="T221" s="4"/>
       <c r="U221" s="4"/>
       <c r="V221" s="4"/>
-    </row>
-    <row r="222" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W221" s="4"/>
+      <c r="X221" s="4"/>
+      <c r="Y221" s="4"/>
+      <c r="Z221" s="4"/>
+    </row>
+    <row r="222" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -8707,8 +9727,12 @@
       <c r="T222" s="4"/>
       <c r="U222" s="4"/>
       <c r="V222" s="4"/>
-    </row>
-    <row r="223" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W222" s="4"/>
+      <c r="X222" s="4"/>
+      <c r="Y222" s="4"/>
+      <c r="Z222" s="4"/>
+    </row>
+    <row r="223" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -8729,8 +9753,12 @@
       <c r="T223" s="4"/>
       <c r="U223" s="4"/>
       <c r="V223" s="4"/>
-    </row>
-    <row r="224" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W223" s="4"/>
+      <c r="X223" s="4"/>
+      <c r="Y223" s="4"/>
+      <c r="Z223" s="4"/>
+    </row>
+    <row r="224" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -8751,8 +9779,12 @@
       <c r="T224" s="4"/>
       <c r="U224" s="4"/>
       <c r="V224" s="4"/>
-    </row>
-    <row r="225" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W224" s="4"/>
+      <c r="X224" s="4"/>
+      <c r="Y224" s="4"/>
+      <c r="Z224" s="4"/>
+    </row>
+    <row r="225" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -8773,8 +9805,12 @@
       <c r="T225" s="4"/>
       <c r="U225" s="4"/>
       <c r="V225" s="4"/>
-    </row>
-    <row r="226" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W225" s="4"/>
+      <c r="X225" s="4"/>
+      <c r="Y225" s="4"/>
+      <c r="Z225" s="4"/>
+    </row>
+    <row r="226" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -8795,8 +9831,12 @@
       <c r="T226" s="4"/>
       <c r="U226" s="4"/>
       <c r="V226" s="4"/>
-    </row>
-    <row r="227" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W226" s="4"/>
+      <c r="X226" s="4"/>
+      <c r="Y226" s="4"/>
+      <c r="Z226" s="4"/>
+    </row>
+    <row r="227" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -8817,8 +9857,12 @@
       <c r="T227" s="4"/>
       <c r="U227" s="4"/>
       <c r="V227" s="4"/>
-    </row>
-    <row r="228" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W227" s="4"/>
+      <c r="X227" s="4"/>
+      <c r="Y227" s="4"/>
+      <c r="Z227" s="4"/>
+    </row>
+    <row r="228" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -8839,8 +9883,12 @@
       <c r="T228" s="4"/>
       <c r="U228" s="4"/>
       <c r="V228" s="4"/>
-    </row>
-    <row r="229" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W228" s="4"/>
+      <c r="X228" s="4"/>
+      <c r="Y228" s="4"/>
+      <c r="Z228" s="4"/>
+    </row>
+    <row r="229" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -8861,8 +9909,12 @@
       <c r="T229" s="4"/>
       <c r="U229" s="4"/>
       <c r="V229" s="4"/>
-    </row>
-    <row r="230" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W229" s="4"/>
+      <c r="X229" s="4"/>
+      <c r="Y229" s="4"/>
+      <c r="Z229" s="4"/>
+    </row>
+    <row r="230" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -8883,8 +9935,12 @@
       <c r="T230" s="4"/>
       <c r="U230" s="4"/>
       <c r="V230" s="4"/>
-    </row>
-    <row r="231" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W230" s="4"/>
+      <c r="X230" s="4"/>
+      <c r="Y230" s="4"/>
+      <c r="Z230" s="4"/>
+    </row>
+    <row r="231" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -8905,8 +9961,12 @@
       <c r="T231" s="4"/>
       <c r="U231" s="4"/>
       <c r="V231" s="4"/>
-    </row>
-    <row r="232" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W231" s="4"/>
+      <c r="X231" s="4"/>
+      <c r="Y231" s="4"/>
+      <c r="Z231" s="4"/>
+    </row>
+    <row r="232" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -8927,8 +9987,12 @@
       <c r="T232" s="4"/>
       <c r="U232" s="4"/>
       <c r="V232" s="4"/>
-    </row>
-    <row r="233" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W232" s="4"/>
+      <c r="X232" s="4"/>
+      <c r="Y232" s="4"/>
+      <c r="Z232" s="4"/>
+    </row>
+    <row r="233" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -8949,8 +10013,12 @@
       <c r="T233" s="4"/>
       <c r="U233" s="4"/>
       <c r="V233" s="4"/>
-    </row>
-    <row r="234" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W233" s="4"/>
+      <c r="X233" s="4"/>
+      <c r="Y233" s="4"/>
+      <c r="Z233" s="4"/>
+    </row>
+    <row r="234" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -8971,8 +10039,12 @@
       <c r="T234" s="4"/>
       <c r="U234" s="4"/>
       <c r="V234" s="4"/>
-    </row>
-    <row r="235" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W234" s="4"/>
+      <c r="X234" s="4"/>
+      <c r="Y234" s="4"/>
+      <c r="Z234" s="4"/>
+    </row>
+    <row r="235" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -8993,8 +10065,12 @@
       <c r="T235" s="4"/>
       <c r="U235" s="4"/>
       <c r="V235" s="4"/>
-    </row>
-    <row r="236" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W235" s="4"/>
+      <c r="X235" s="4"/>
+      <c r="Y235" s="4"/>
+      <c r="Z235" s="4"/>
+    </row>
+    <row r="236" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -9015,8 +10091,12 @@
       <c r="T236" s="4"/>
       <c r="U236" s="4"/>
       <c r="V236" s="4"/>
-    </row>
-    <row r="237" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W236" s="4"/>
+      <c r="X236" s="4"/>
+      <c r="Y236" s="4"/>
+      <c r="Z236" s="4"/>
+    </row>
+    <row r="237" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -9037,8 +10117,12 @@
       <c r="T237" s="4"/>
       <c r="U237" s="4"/>
       <c r="V237" s="4"/>
-    </row>
-    <row r="238" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W237" s="4"/>
+      <c r="X237" s="4"/>
+      <c r="Y237" s="4"/>
+      <c r="Z237" s="4"/>
+    </row>
+    <row r="238" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -9059,8 +10143,12 @@
       <c r="T238" s="4"/>
       <c r="U238" s="4"/>
       <c r="V238" s="4"/>
-    </row>
-    <row r="239" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W238" s="4"/>
+      <c r="X238" s="4"/>
+      <c r="Y238" s="4"/>
+      <c r="Z238" s="4"/>
+    </row>
+    <row r="239" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -9081,8 +10169,12 @@
       <c r="T239" s="4"/>
       <c r="U239" s="4"/>
       <c r="V239" s="4"/>
-    </row>
-    <row r="240" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W239" s="4"/>
+      <c r="X239" s="4"/>
+      <c r="Y239" s="4"/>
+      <c r="Z239" s="4"/>
+    </row>
+    <row r="240" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -9103,8 +10195,12 @@
       <c r="T240" s="4"/>
       <c r="U240" s="4"/>
       <c r="V240" s="4"/>
-    </row>
-    <row r="241" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W240" s="4"/>
+      <c r="X240" s="4"/>
+      <c r="Y240" s="4"/>
+      <c r="Z240" s="4"/>
+    </row>
+    <row r="241" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -9125,8 +10221,12 @@
       <c r="T241" s="4"/>
       <c r="U241" s="4"/>
       <c r="V241" s="4"/>
-    </row>
-    <row r="242" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W241" s="4"/>
+      <c r="X241" s="4"/>
+      <c r="Y241" s="4"/>
+      <c r="Z241" s="4"/>
+    </row>
+    <row r="242" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -9147,8 +10247,12 @@
       <c r="T242" s="4"/>
       <c r="U242" s="4"/>
       <c r="V242" s="4"/>
-    </row>
-    <row r="243" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W242" s="4"/>
+      <c r="X242" s="4"/>
+      <c r="Y242" s="4"/>
+      <c r="Z242" s="4"/>
+    </row>
+    <row r="243" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -9169,8 +10273,12 @@
       <c r="T243" s="4"/>
       <c r="U243" s="4"/>
       <c r="V243" s="4"/>
-    </row>
-    <row r="244" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W243" s="4"/>
+      <c r="X243" s="4"/>
+      <c r="Y243" s="4"/>
+      <c r="Z243" s="4"/>
+    </row>
+    <row r="244" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -9191,8 +10299,12 @@
       <c r="T244" s="4"/>
       <c r="U244" s="4"/>
       <c r="V244" s="4"/>
-    </row>
-    <row r="245" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W244" s="4"/>
+      <c r="X244" s="4"/>
+      <c r="Y244" s="4"/>
+      <c r="Z244" s="4"/>
+    </row>
+    <row r="245" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -9213,8 +10325,12 @@
       <c r="T245" s="4"/>
       <c r="U245" s="4"/>
       <c r="V245" s="4"/>
-    </row>
-    <row r="246" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W245" s="4"/>
+      <c r="X245" s="4"/>
+      <c r="Y245" s="4"/>
+      <c r="Z245" s="4"/>
+    </row>
+    <row r="246" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -9235,8 +10351,12 @@
       <c r="T246" s="4"/>
       <c r="U246" s="4"/>
       <c r="V246" s="4"/>
-    </row>
-    <row r="247" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W246" s="4"/>
+      <c r="X246" s="4"/>
+      <c r="Y246" s="4"/>
+      <c r="Z246" s="4"/>
+    </row>
+    <row r="247" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -9257,8 +10377,12 @@
       <c r="T247" s="4"/>
       <c r="U247" s="4"/>
       <c r="V247" s="4"/>
-    </row>
-    <row r="248" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W247" s="4"/>
+      <c r="X247" s="4"/>
+      <c r="Y247" s="4"/>
+      <c r="Z247" s="4"/>
+    </row>
+    <row r="248" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -9279,8 +10403,12 @@
       <c r="T248" s="4"/>
       <c r="U248" s="4"/>
       <c r="V248" s="4"/>
-    </row>
-    <row r="249" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W248" s="4"/>
+      <c r="X248" s="4"/>
+      <c r="Y248" s="4"/>
+      <c r="Z248" s="4"/>
+    </row>
+    <row r="249" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -9301,8 +10429,12 @@
       <c r="T249" s="4"/>
       <c r="U249" s="4"/>
       <c r="V249" s="4"/>
-    </row>
-    <row r="250" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W249" s="4"/>
+      <c r="X249" s="4"/>
+      <c r="Y249" s="4"/>
+      <c r="Z249" s="4"/>
+    </row>
+    <row r="250" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -9323,8 +10455,12 @@
       <c r="T250" s="4"/>
       <c r="U250" s="4"/>
       <c r="V250" s="4"/>
-    </row>
-    <row r="251" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W250" s="4"/>
+      <c r="X250" s="4"/>
+      <c r="Y250" s="4"/>
+      <c r="Z250" s="4"/>
+    </row>
+    <row r="251" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -9345,8 +10481,12 @@
       <c r="T251" s="4"/>
       <c r="U251" s="4"/>
       <c r="V251" s="4"/>
-    </row>
-    <row r="252" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W251" s="4"/>
+      <c r="X251" s="4"/>
+      <c r="Y251" s="4"/>
+      <c r="Z251" s="4"/>
+    </row>
+    <row r="252" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -9367,8 +10507,12 @@
       <c r="T252" s="4"/>
       <c r="U252" s="4"/>
       <c r="V252" s="4"/>
-    </row>
-    <row r="253" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W252" s="4"/>
+      <c r="X252" s="4"/>
+      <c r="Y252" s="4"/>
+      <c r="Z252" s="4"/>
+    </row>
+    <row r="253" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -9389,8 +10533,12 @@
       <c r="T253" s="4"/>
       <c r="U253" s="4"/>
       <c r="V253" s="4"/>
-    </row>
-    <row r="254" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W253" s="4"/>
+      <c r="X253" s="4"/>
+      <c r="Y253" s="4"/>
+      <c r="Z253" s="4"/>
+    </row>
+    <row r="254" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -9411,8 +10559,12 @@
       <c r="T254" s="4"/>
       <c r="U254" s="4"/>
       <c r="V254" s="4"/>
-    </row>
-    <row r="255" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W254" s="4"/>
+      <c r="X254" s="4"/>
+      <c r="Y254" s="4"/>
+      <c r="Z254" s="4"/>
+    </row>
+    <row r="255" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -9433,8 +10585,12 @@
       <c r="T255" s="4"/>
       <c r="U255" s="4"/>
       <c r="V255" s="4"/>
-    </row>
-    <row r="256" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W255" s="4"/>
+      <c r="X255" s="4"/>
+      <c r="Y255" s="4"/>
+      <c r="Z255" s="4"/>
+    </row>
+    <row r="256" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -9455,8 +10611,12 @@
       <c r="T256" s="4"/>
       <c r="U256" s="4"/>
       <c r="V256" s="4"/>
-    </row>
-    <row r="257" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W256" s="4"/>
+      <c r="X256" s="4"/>
+      <c r="Y256" s="4"/>
+      <c r="Z256" s="4"/>
+    </row>
+    <row r="257" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -9477,8 +10637,12 @@
       <c r="T257" s="4"/>
       <c r="U257" s="4"/>
       <c r="V257" s="4"/>
-    </row>
-    <row r="258" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W257" s="4"/>
+      <c r="X257" s="4"/>
+      <c r="Y257" s="4"/>
+      <c r="Z257" s="4"/>
+    </row>
+    <row r="258" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -9499,8 +10663,12 @@
       <c r="T258" s="4"/>
       <c r="U258" s="4"/>
       <c r="V258" s="4"/>
-    </row>
-    <row r="259" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W258" s="4"/>
+      <c r="X258" s="4"/>
+      <c r="Y258" s="4"/>
+      <c r="Z258" s="4"/>
+    </row>
+    <row r="259" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -9521,8 +10689,12 @@
       <c r="T259" s="4"/>
       <c r="U259" s="4"/>
       <c r="V259" s="4"/>
-    </row>
-    <row r="260" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W259" s="4"/>
+      <c r="X259" s="4"/>
+      <c r="Y259" s="4"/>
+      <c r="Z259" s="4"/>
+    </row>
+    <row r="260" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -9543,8 +10715,12 @@
       <c r="T260" s="4"/>
       <c r="U260" s="4"/>
       <c r="V260" s="4"/>
-    </row>
-    <row r="261" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W260" s="4"/>
+      <c r="X260" s="4"/>
+      <c r="Y260" s="4"/>
+      <c r="Z260" s="4"/>
+    </row>
+    <row r="261" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -9565,8 +10741,12 @@
       <c r="T261" s="4"/>
       <c r="U261" s="4"/>
       <c r="V261" s="4"/>
-    </row>
-    <row r="262" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W261" s="4"/>
+      <c r="X261" s="4"/>
+      <c r="Y261" s="4"/>
+      <c r="Z261" s="4"/>
+    </row>
+    <row r="262" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -9587,8 +10767,12 @@
       <c r="T262" s="4"/>
       <c r="U262" s="4"/>
       <c r="V262" s="4"/>
-    </row>
-    <row r="263" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W262" s="4"/>
+      <c r="X262" s="4"/>
+      <c r="Y262" s="4"/>
+      <c r="Z262" s="4"/>
+    </row>
+    <row r="263" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -9609,8 +10793,12 @@
       <c r="T263" s="4"/>
       <c r="U263" s="4"/>
       <c r="V263" s="4"/>
-    </row>
-    <row r="264" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W263" s="4"/>
+      <c r="X263" s="4"/>
+      <c r="Y263" s="4"/>
+      <c r="Z263" s="4"/>
+    </row>
+    <row r="264" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -9631,8 +10819,12 @@
       <c r="T264" s="4"/>
       <c r="U264" s="4"/>
       <c r="V264" s="4"/>
-    </row>
-    <row r="265" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W264" s="4"/>
+      <c r="X264" s="4"/>
+      <c r="Y264" s="4"/>
+      <c r="Z264" s="4"/>
+    </row>
+    <row r="265" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -9653,8 +10845,12 @@
       <c r="T265" s="4"/>
       <c r="U265" s="4"/>
       <c r="V265" s="4"/>
-    </row>
-    <row r="266" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W265" s="4"/>
+      <c r="X265" s="4"/>
+      <c r="Y265" s="4"/>
+      <c r="Z265" s="4"/>
+    </row>
+    <row r="266" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
@@ -9675,8 +10871,12 @@
       <c r="T266" s="4"/>
       <c r="U266" s="4"/>
       <c r="V266" s="4"/>
-    </row>
-    <row r="267" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W266" s="4"/>
+      <c r="X266" s="4"/>
+      <c r="Y266" s="4"/>
+      <c r="Z266" s="4"/>
+    </row>
+    <row r="267" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
@@ -9697,8 +10897,12 @@
       <c r="T267" s="4"/>
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
-    </row>
-    <row r="268" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W267" s="4"/>
+      <c r="X267" s="4"/>
+      <c r="Y267" s="4"/>
+      <c r="Z267" s="4"/>
+    </row>
+    <row r="268" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -9719,8 +10923,12 @@
       <c r="T268" s="4"/>
       <c r="U268" s="4"/>
       <c r="V268" s="4"/>
-    </row>
-    <row r="269" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W268" s="4"/>
+      <c r="X268" s="4"/>
+      <c r="Y268" s="4"/>
+      <c r="Z268" s="4"/>
+    </row>
+    <row r="269" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -9741,6 +10949,10 @@
       <c r="T269" s="4"/>
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
+      <c r="W269" s="4"/>
+      <c r="X269" s="4"/>
+      <c r="Y269" s="4"/>
+      <c r="Z269" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ADS.xlsx
+++ b/ADS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1038B84-9B1D-4E9D-94F3-D2DD771ABF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A482302-6FC9-419D-BEF8-03468EEB63BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -321,13 +321,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -409,38 +415,42 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -800,465 +810,679 @@
     <col min="7" max="53" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="19">
         <v>147.4</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="19">
         <v>177.192477</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
       <c r="B4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14" t="s">
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="21">
         <f>I2*I3</f>
         <v>26118.171109800001</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="21">
         <v>873</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="21">
         <f>1005+1992</f>
         <v>2997</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="21">
         <f>I4-I5+I6</f>
         <v>28242.171109800001</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -1275,7 +1499,7 @@
       <c r="O26" s="14"/>
       <c r="P26" s="14"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1292,7 +1516,7 @@
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1309,7 +1533,7 @@
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1386,16 +1610,16 @@
       <c r="N2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="18" t="s">
         <v>84</v>
       </c>
       <c r="S2" s="5"/>
@@ -1420,7 +1644,7 @@
       <c r="Z2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AA2" s="15" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1962,19 +2186,19 @@
       <c r="AG10" s="7"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="17" t="s">
         <v>80</v>
       </c>
       <c r="G11" s="7">
@@ -2008,22 +2232,22 @@
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
-      <c r="T11" s="18" t="s">
+      <c r="T11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="U11" s="18" t="s">
+      <c r="U11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="V11" s="18" t="s">
+      <c r="V11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="W11" s="18" t="s">
+      <c r="W11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="X11" s="18" t="s">
+      <c r="X11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="Y11" s="18" t="s">
+      <c r="Y11" s="17" t="s">
         <v>80</v>
       </c>
       <c r="Z11" s="7">
@@ -2040,19 +2264,19 @@
       <c r="AG11" s="7"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="17" t="s">
         <v>80</v>
       </c>
       <c r="G12" s="7">
@@ -2086,22 +2310,22 @@
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
-      <c r="T12" s="18" t="s">
+      <c r="T12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="U12" s="18" t="s">
+      <c r="U12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="V12" s="18" t="s">
+      <c r="V12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="W12" s="18" t="s">
+      <c r="W12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="X12" s="18" t="s">
+      <c r="X12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="Y12" s="18" t="s">
+      <c r="Y12" s="17" t="s">
         <v>80</v>
       </c>
       <c r="Z12" s="7">

--- a/ADS.xlsx
+++ b/ADS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A482302-6FC9-419D-BEF8-03468EEB63BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E39D398-DE01-4C49-8D99-9A4DBB640ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{5CA27069-BA8E-4704-98A3-1B68BB8C6A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -321,13 +321,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -415,42 +421,43 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -850,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="19">
-        <v>147.4</v>
+        <v>159.1</v>
       </c>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
@@ -878,11 +885,11 @@
       <c r="H3" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="19">
-        <v>177.192477</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>81</v>
+      <c r="I3" s="4">
+        <v>176.27154200000001</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
@@ -911,9 +918,9 @@
       <c r="H4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="20">
         <f>I2*I3</f>
-        <v>26118.171109800001</v>
+        <v>28044.802332200001</v>
       </c>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
@@ -943,11 +950,11 @@
       <c r="H5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="21">
-        <v>873</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>81</v>
+      <c r="I5" s="20">
+        <v>1159</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
@@ -974,12 +981,12 @@
       <c r="H6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="21">
-        <f>1005+1992</f>
-        <v>2997</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>81</v>
+      <c r="I6" s="20">
+        <f>560+2489</f>
+        <v>3049</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -1006,9 +1013,9 @@
       <c r="H7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="20">
         <f>I4-I5+I6</f>
-        <v>28242.171109800001</v>
+        <v>29934.802332200001</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
@@ -1691,7 +1698,9 @@
       <c r="O3" s="7">
         <v>876</v>
       </c>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7">
+        <v>908</v>
+      </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -1757,7 +1766,9 @@
       <c r="O4" s="7">
         <v>1124</v>
       </c>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7">
+        <v>1126</v>
+      </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -1821,7 +1832,7 @@
         <v>1933</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" ref="L5:O5" si="1">+L3+L4</f>
+        <f t="shared" ref="L5:P5" si="1">+L3+L4</f>
         <v>1942</v>
       </c>
       <c r="M5" s="8">
@@ -1836,7 +1847,10 @@
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="P5" s="8"/>
+      <c r="P5" s="8">
+        <f t="shared" si="1"/>
+        <v>2034</v>
+      </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="7"/>
@@ -1954,7 +1968,9 @@
       <c r="O7" s="7">
         <v>2090</v>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7">
+        <v>2108</v>
+      </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -2023,7 +2039,9 @@
       <c r="O8" s="7">
         <v>1200</v>
       </c>
-      <c r="P8" s="7"/>
+      <c r="P8" s="7">
+        <v>1522</v>
+      </c>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
@@ -2092,7 +2110,9 @@
       <c r="O9" s="7">
         <v>1135</v>
       </c>
-      <c r="P9" s="7"/>
+      <c r="P9" s="7">
+        <v>953</v>
+      </c>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
@@ -2160,7 +2180,9 @@
       <c r="O10" s="7">
         <v>869</v>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="7">
+        <v>848</v>
+      </c>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
@@ -2228,7 +2250,9 @@
       <c r="O11" s="7">
         <v>831</v>
       </c>
-      <c r="P11" s="7"/>
+      <c r="P11" s="7">
+        <v>907</v>
+      </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -2306,7 +2330,9 @@
       <c r="O12" s="7">
         <v>405</v>
       </c>
-      <c r="P12" s="7"/>
+      <c r="P12" s="7">
+        <v>376</v>
+      </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
@@ -2385,7 +2411,9 @@
       <c r="O13" s="7">
         <v>3699</v>
       </c>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7">
+        <v>3492</v>
+      </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -2454,7 +2482,9 @@
       <c r="O14" s="7">
         <v>2442</v>
       </c>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7">
+        <v>2721</v>
+      </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
@@ -2523,7 +2553,9 @@
       <c r="O15" s="7">
         <v>451</v>
       </c>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7">
+        <v>530</v>
+      </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
@@ -2592,7 +2624,9 @@
       <c r="O16" s="8">
         <v>6592</v>
       </c>
-      <c r="P16" s="8"/>
+      <c r="P16" s="8">
+        <v>6743</v>
+      </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
@@ -2670,7 +2704,9 @@
       <c r="O17" s="7">
         <v>3223</v>
       </c>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7">
+        <v>3203</v>
+      </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
@@ -2737,7 +2773,7 @@
         <v>3301</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" ref="J18:O18" si="11">J16-J17</f>
+        <f t="shared" ref="J18:P18" si="11">J16-J17</f>
         <v>2970</v>
       </c>
       <c r="K18" s="7">
@@ -2760,7 +2796,10 @@
         <f t="shared" si="11"/>
         <v>3369</v>
       </c>
-      <c r="P18" s="7"/>
+      <c r="P18" s="7">
+        <f t="shared" si="11"/>
+        <v>3540</v>
+      </c>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
@@ -2846,7 +2885,9 @@
       <c r="O19" s="7">
         <v>19</v>
       </c>
-      <c r="P19" s="7"/>
+      <c r="P19" s="7">
+        <v>16</v>
+      </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -2924,7 +2965,9 @@
       <c r="O20" s="7">
         <v>1</v>
       </c>
-      <c r="P20" s="7"/>
+      <c r="P20" s="7">
+        <v>1</v>
+      </c>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
@@ -3002,7 +3045,9 @@
       <c r="O21" s="7">
         <v>756</v>
       </c>
-      <c r="P21" s="7"/>
+      <c r="P21" s="7">
+        <v>924</v>
+      </c>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -3081,7 +3126,9 @@
       <c r="O22" s="7">
         <v>1927</v>
       </c>
-      <c r="P22" s="7"/>
+      <c r="P22" s="7">
+        <v>2059</v>
+      </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
@@ -3154,14 +3201,16 @@
         <v>2740</v>
       </c>
       <c r="N23" s="7">
-        <f t="shared" si="3"/>
-        <v>-7904</v>
+        <v>2740</v>
       </c>
       <c r="O23" s="7">
         <f>+O21+O22</f>
         <v>2683</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <f>+P21+P22</f>
+        <v>2983</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -3240,7 +3289,9 @@
       <c r="O24" s="7">
         <v>0</v>
       </c>
-      <c r="P24" s="7"/>
+      <c r="P24" s="7">
+        <v>0</v>
+      </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
@@ -3286,7 +3337,7 @@
         <v>30</v>
       </c>
       <c r="C25" s="7">
-        <f t="shared" ref="C25:F25" si="13">C18+C19+C20-C21-C22</f>
+        <f t="shared" ref="C25:O25" si="13">C18+C19+C20-C21-C22-C24</f>
         <v>60</v>
       </c>
       <c r="D25" s="7">
@@ -3302,63 +3353,66 @@
         <v>-376</v>
       </c>
       <c r="G25" s="7">
-        <f>G18+G19+G20-G21-G22</f>
+        <f t="shared" si="13"/>
         <v>336</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" ref="H25:O25" si="14">H18+H19+H20-H21-H22</f>
+        <f t="shared" si="13"/>
         <v>347</v>
       </c>
       <c r="I25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>596</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>57</v>
       </c>
       <c r="K25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>609</v>
       </c>
       <c r="L25" s="7">
-        <f>L18+L19+L20-L21-L22</f>
+        <f t="shared" si="13"/>
         <v>547</v>
       </c>
       <c r="M25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>736</v>
       </c>
       <c r="N25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>164</v>
       </c>
       <c r="O25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>706</v>
       </c>
-      <c r="P25" s="7"/>
+      <c r="P25" s="7">
+        <f>P18+P19+P20-P21-P22-P24</f>
+        <v>574</v>
+      </c>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7">
-        <f t="shared" ref="T25:X25" si="15">T18+T19+T20-SUM(T21:T24)</f>
+        <f t="shared" ref="T25:X25" si="14">T18+T19+T20-SUM(T21:T24)</f>
         <v>2367</v>
       </c>
       <c r="U25" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2660</v>
       </c>
       <c r="V25" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>745</v>
       </c>
       <c r="W25" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1987</v>
       </c>
       <c r="X25" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>669</v>
       </c>
       <c r="Y25" s="7">
@@ -3423,7 +3477,9 @@
       <c r="O26" s="7">
         <v>11</v>
       </c>
-      <c r="P26" s="7"/>
+      <c r="P26" s="7">
+        <v>14</v>
+      </c>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
@@ -3501,7 +3557,9 @@
       <c r="O27" s="7">
         <v>70</v>
       </c>
-      <c r="P27" s="7"/>
+      <c r="P27" s="22">
+        <v>58</v>
+      </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -3540,79 +3598,82 @@
         <v>34</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28" si="16">C25+C26-C27</f>
+        <f t="shared" ref="C28" si="15">C25+C26-C27</f>
         <v>32</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" ref="D28" si="17">D25+D26-D27</f>
+        <f t="shared" ref="D28" si="16">D25+D26-D27</f>
         <v>123</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" ref="E28" si="18">E25+E26-E27</f>
+        <f t="shared" ref="E28" si="17">E25+E26-E27</f>
         <v>326</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" ref="F28" si="19">F25+F26-F27</f>
+        <f t="shared" ref="F28" si="18">F25+F26-F27</f>
         <v>-414</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" ref="G28" si="20">G25+G26-G27</f>
+        <f t="shared" ref="G28" si="19">G25+G26-G27</f>
         <v>245</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" ref="H28" si="21">H25+H26-H27</f>
+        <f t="shared" ref="H28" si="20">H25+H26-H27</f>
         <v>305</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" ref="I28" si="22">I25+I26-I27</f>
+        <f t="shared" ref="I28" si="21">I25+I26-I27</f>
         <v>600</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" ref="J28:O28" si="23">J25+J26-J27</f>
+        <f t="shared" ref="J28:P28" si="22">J25+J26-J27</f>
         <v>-28</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>584</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>489</v>
       </c>
       <c r="M28" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>650</v>
       </c>
       <c r="N28" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>97</v>
       </c>
       <c r="O28" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>647</v>
       </c>
-      <c r="P28" s="7"/>
+      <c r="P28" s="7">
+        <f t="shared" si="22"/>
+        <v>530</v>
+      </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7">
-        <f t="shared" ref="T28:X28" si="24">T25+T26-T27</f>
+        <f t="shared" ref="T28:X28" si="23">T25+T26-T27</f>
         <v>2377</v>
       </c>
       <c r="U28" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2558</v>
       </c>
       <c r="V28" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>578</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1853</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>388</v>
       </c>
       <c r="Y28" s="7">
@@ -3677,7 +3738,9 @@
       <c r="O29" s="7">
         <v>161</v>
       </c>
-      <c r="P29" s="7"/>
+      <c r="P29" s="7">
+        <v>133</v>
+      </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -3716,79 +3779,82 @@
         <v>37</v>
       </c>
       <c r="C30" s="7">
-        <f t="shared" ref="C30" si="25">C28-C29</f>
+        <f t="shared" ref="C30" si="24">C28-C29</f>
         <v>-23</v>
       </c>
       <c r="D30" s="7">
-        <f t="shared" ref="D30" si="26">D28-D29</f>
+        <f t="shared" ref="D30" si="25">D28-D29</f>
         <v>96</v>
       </c>
       <c r="E30" s="7">
-        <f t="shared" ref="E30" si="27">E28-E29</f>
+        <f t="shared" ref="E30" si="26">E28-E29</f>
         <v>271</v>
       </c>
       <c r="F30" s="7">
-        <f t="shared" ref="F30" si="28">F28-F29</f>
+        <f t="shared" ref="F30" si="27">F28-F29</f>
         <v>-400</v>
       </c>
       <c r="G30" s="7">
-        <f t="shared" ref="G30" si="29">G28-G29</f>
+        <f t="shared" ref="G30" si="28">G28-G29</f>
         <v>171</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" ref="H30" si="30">H28-H29</f>
+        <f t="shared" ref="H30" si="29">H28-H29</f>
         <v>212</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" ref="I30" si="31">I28-I29</f>
+        <f t="shared" ref="I30" si="30">I28-I29</f>
         <v>467</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" ref="J30:O30" si="32">J28-J29</f>
+        <f t="shared" ref="J30:P30" si="31">J28-J29</f>
         <v>-26</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>435</v>
       </c>
       <c r="L30" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>375</v>
       </c>
       <c r="M30" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>481</v>
       </c>
       <c r="N30" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>86</v>
       </c>
       <c r="O30" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>486</v>
       </c>
-      <c r="P30" s="7"/>
+      <c r="P30" s="7">
+        <f t="shared" si="31"/>
+        <v>397</v>
+      </c>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7">
-        <f t="shared" ref="T30:X30" si="33">T28-T29</f>
+        <f t="shared" ref="T30:X30" si="32">T28-T29</f>
         <v>1708</v>
       </c>
       <c r="U30" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>1918</v>
       </c>
       <c r="V30" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>461</v>
       </c>
       <c r="W30" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>1493</v>
       </c>
       <c r="X30" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>254</v>
       </c>
       <c r="Y30" s="7">
@@ -3853,7 +3919,9 @@
       <c r="O31" s="7">
         <v>3</v>
       </c>
-      <c r="P31" s="7"/>
+      <c r="P31" s="7">
+        <v>-14</v>
+      </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -3892,79 +3960,82 @@
         <v>36</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32" si="34">C30+C31</f>
+        <f t="shared" ref="C32" si="33">C30+C31</f>
         <v>-29</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" ref="D32" si="35">D30+D31</f>
+        <f t="shared" ref="D32" si="34">D30+D31</f>
         <v>95</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" ref="E32" si="36">E30+E31</f>
+        <f t="shared" ref="E32" si="35">E30+E31</f>
         <v>281</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" ref="F32" si="37">F30+F31</f>
+        <f t="shared" ref="F32" si="36">F30+F31</f>
         <v>-358</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" ref="G32" si="38">G30+G31</f>
+        <f t="shared" ref="G32" si="37">G30+G31</f>
         <v>170</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" ref="H32" si="39">H30+H31</f>
+        <f t="shared" ref="H32" si="38">H30+H31</f>
         <v>206</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" ref="I32" si="40">I30+I31</f>
+        <f t="shared" ref="I32" si="39">I30+I31</f>
         <v>474</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" ref="J32:O32" si="41">J30+J31</f>
+        <f t="shared" ref="J32:P32" si="40">J30+J31</f>
         <v>-19</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>428</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>381</v>
       </c>
       <c r="M32" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>484</v>
       </c>
       <c r="N32" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>92</v>
       </c>
       <c r="O32" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>489</v>
       </c>
-      <c r="P32" s="7"/>
+      <c r="P32" s="7">
+        <f t="shared" si="40"/>
+        <v>383</v>
+      </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
       <c r="T32" s="7">
-        <f t="shared" ref="T32:X32" si="42">T30+T31</f>
+        <f t="shared" ref="T32:X32" si="41">T30+T31</f>
         <v>1703</v>
       </c>
       <c r="U32" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1977</v>
       </c>
       <c r="V32" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>442</v>
       </c>
       <c r="W32" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>2159</v>
       </c>
       <c r="X32" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>638</v>
       </c>
       <c r="Y32" s="7">
@@ -4029,7 +4100,9 @@
       <c r="O33" s="7">
         <v>5</v>
       </c>
-      <c r="P33" s="7"/>
+      <c r="P33" s="7">
+        <v>29</v>
+      </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -4068,23 +4141,23 @@
         <v>40</v>
       </c>
       <c r="C34" s="7">
-        <f t="shared" ref="C34" si="43">C32-C33</f>
+        <f t="shared" ref="C34" si="42">C32-C33</f>
         <v>-38</v>
       </c>
       <c r="D34" s="7">
-        <f t="shared" ref="D34" si="44">D32-D33</f>
+        <f t="shared" ref="D34" si="43">D32-D33</f>
         <v>84</v>
       </c>
       <c r="E34" s="7">
-        <f t="shared" ref="E34" si="45">E32-E33</f>
+        <f t="shared" ref="E34" si="44">E32-E33</f>
         <v>260</v>
       </c>
       <c r="F34" s="7">
-        <f t="shared" ref="F34" si="46">F32-F33</f>
+        <f t="shared" ref="F34" si="45">F32-F33</f>
         <v>21</v>
       </c>
       <c r="G34" s="7">
-        <f t="shared" ref="G34" si="47">G32-G33</f>
+        <f t="shared" ref="G34" si="46">G32-G33</f>
         <v>170</v>
       </c>
       <c r="H34" s="7">
@@ -4092,55 +4165,58 @@
         <v>190</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" ref="I34:O34" si="48">I32-I33</f>
+        <f t="shared" ref="I34:P34" si="47">I32-I33</f>
         <v>441</v>
       </c>
       <c r="J34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>20</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>427</v>
       </c>
       <c r="L34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>370</v>
       </c>
       <c r="M34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>461</v>
       </c>
       <c r="N34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>82</v>
       </c>
       <c r="O34" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>484</v>
       </c>
-      <c r="P34" s="7"/>
+      <c r="P34" s="7">
+        <f t="shared" si="47"/>
+        <v>354</v>
+      </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="7">
-        <f t="shared" ref="T34:X34" si="49">T32-T33</f>
+        <f t="shared" ref="T34:X34" si="48">T32-T33</f>
         <v>1700</v>
       </c>
       <c r="U34" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>1975</v>
       </c>
       <c r="V34" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>431</v>
       </c>
       <c r="W34" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>2117</v>
       </c>
       <c r="X34" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>612</v>
       </c>
       <c r="Y34" s="7">
@@ -4222,26 +4298,29 @@
         <v>0.11201401626905014</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" ref="K36:O36" si="50">+K34/K37</f>
+        <f t="shared" ref="K36:P36" si="49">+K34/K37</f>
         <v>2.3914992473442207</v>
       </c>
       <c r="L36" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>2.0722209435125509</v>
       </c>
       <c r="M36" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>2.581923075001606</v>
       </c>
       <c r="N36" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0.45923139673213176</v>
       </c>
       <c r="O36" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>2.7314929403012975</v>
       </c>
-      <c r="P36" s="4"/>
+      <c r="P36" s="4">
+        <f t="shared" si="49"/>
+        <v>2.00826517986664</v>
+      </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
@@ -4278,31 +4357,31 @@
         <v>46</v>
       </c>
       <c r="C37" s="4">
-        <f t="shared" ref="C37:I37" si="51">C34/C36</f>
+        <f t="shared" ref="C37:I37" si="50">C34/C36</f>
         <v>172.72727272727272</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>178.72340425531917</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>185.71428571428572</v>
       </c>
       <c r="F37" s="4" t="e">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>177.08333333333334</v>
       </c>
       <c r="H37" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>174.31192660550457</v>
       </c>
       <c r="I37" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>177.82258064516128</v>
       </c>
       <c r="J37" s="4">
@@ -4324,28 +4403,30 @@
       <c r="O37" s="4">
         <v>177.192477</v>
       </c>
-      <c r="P37" s="4"/>
+      <c r="P37" s="4">
+        <v>176.27154200000001</v>
+      </c>
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4">
-        <f t="shared" ref="T37:X37" si="52">T34/T36</f>
+        <f t="shared" ref="T37:X37" si="51">T34/T36</f>
         <v>201.4218009478673</v>
       </c>
       <c r="U37" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>197.5</v>
       </c>
       <c r="V37" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>186.58008658008657</v>
       </c>
       <c r="W37" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>283.40026773761713</v>
       </c>
       <c r="X37" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>489.6</v>
       </c>
       <c r="Y37" s="4">
@@ -4393,64 +4474,67 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="10">
-        <f t="shared" ref="G39:O39" si="53">+G3/C3-1</f>
+        <f t="shared" ref="G39:P39" si="52">+G3/C3-1</f>
         <v>1.4833127317676054E-2</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>3.5220125786163514E-2</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>7.2115384615385469E-3</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>1.8270401948842885E-2</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>4.7146401985111552E-2</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>5.2247873633049835E-2</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>5.7279236276849721E-2</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>4.7846889952153138E-2</v>
       </c>
-      <c r="P39" s="10"/>
+      <c r="P39" s="10">
+        <f t="shared" si="52"/>
+        <v>7.5829383886255819E-2</v>
+      </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="10" t="e">
-        <f t="shared" ref="U39:Y39" si="54">+U3/T3-1</f>
+        <f t="shared" ref="U39:Y39" si="53">+U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V39" s="10" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W39" s="10" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X39" s="10" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y39" s="10" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z39" s="10">
@@ -4483,7 +4567,7 @@
         <v>-1.5525114155251152E-2</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" ref="J40" si="55">+J4/F4-1</f>
+        <f t="shared" ref="J40" si="54">+J4/F4-1</f>
         <v>6.2075654704170757E-2</v>
       </c>
       <c r="K40" s="10">
@@ -4506,29 +4590,32 @@
         <f>+O4/K4-1</f>
         <v>2.4612579762989917E-2</v>
       </c>
-      <c r="P40" s="10"/>
+      <c r="P40" s="10">
+        <f>+P4/L4-1</f>
+        <v>2.5500910746812488E-2</v>
+      </c>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="10" t="e">
-        <f t="shared" ref="U40:Y40" si="56">+U4/T4-1</f>
+        <f t="shared" ref="U40:Y40" si="55">+U4/T4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V40" s="10" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W40" s="10" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X40" s="10" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y40" s="10" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z40" s="10">
@@ -4549,72 +4636,75 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="10">
-        <f t="shared" ref="G41:O44" si="57">+G7/C7-1</f>
+        <f t="shared" ref="G41:P44" si="56">+G7/C7-1</f>
         <v>0.14844267726971494</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.20100502512562812</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.18763796909492281</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.26277897768178549</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.14598961338718985</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>4.4456066945606665E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>8.1784386617100413E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>4.0478905359178974E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>5.2366565961732059E-2</v>
       </c>
-      <c r="P41" s="10"/>
+      <c r="P41" s="10">
+        <f t="shared" si="56"/>
+        <v>5.5583375062593809E-2</v>
+      </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="10" t="e">
-        <f t="shared" ref="U41:AA44" si="58">+U7/T7-1</f>
+        <f t="shared" ref="U41:AA44" si="57">+U7/T7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V41" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W41" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X41" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y41" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>0.19819105046017138</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>7.7473182359952375E-2</v>
       </c>
     </row>
@@ -4627,72 +4717,75 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-4.6728971962616828E-2</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-6.9335239456754794E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-8.2210242587601123E-2</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.15789473684210531</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>5.525846702317283E-2</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>2.8417818740399392E-2</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-4.6989720998531603E-2</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-5.663189269746649E-2</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>1.3513513513513598E-2</v>
       </c>
-      <c r="P42" s="10"/>
+      <c r="P42" s="10">
+        <f t="shared" si="56"/>
+        <v>0.13666915608663177</v>
+      </c>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V42" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W42" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X42" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y42" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-1.7436290477102934E-2</v>
       </c>
       <c r="AA42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7.9953198127925562E-3</v>
       </c>
     </row>
@@ -4705,72 +4798,75 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>1.4705882352941124E-2</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>7.3107049608355013E-2</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>8.7356321839080486E-2</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.18507462686567155</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.14715719063545141</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-2.9197080291970767E-2</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>1.0570824524311906E-3</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>6.9269521410579404E-2</v>
       </c>
       <c r="O43" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.10301263362487845</v>
       </c>
-      <c r="P43" s="10"/>
+      <c r="P43" s="10">
+        <f t="shared" si="56"/>
+        <v>0.19423558897243098</v>
+      </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V43" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W43" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X43" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y43" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z43" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>8.4326018808777325E-2</v>
       </c>
       <c r="AA43" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>4.7412546978895742E-2</v>
       </c>
     </row>
@@ -4783,72 +4879,75 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>5.9523809523809534E-2</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.24833333333333329</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>9.1127098321343025E-2</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.26344086021505375</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.2219101123595506</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>1.735647530040052E-2</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>2.7472527472527375E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>3.1914893617022155E-3</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1.1494252873562871E-3</v>
       </c>
-      <c r="P44" s="10"/>
+      <c r="P44" s="10">
+        <f t="shared" si="56"/>
+        <v>0.11286089238845154</v>
+      </c>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V44" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W44" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X44" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y44" s="10" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>0.16140350877192988</v>
       </c>
       <c r="AA44" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>6.042296072507547E-2</v>
       </c>
     </row>
@@ -4861,72 +4960,75 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="10">
-        <f t="shared" ref="G45:I47" si="59">+G13/C13-1</f>
+        <f t="shared" ref="G45:I47" si="58">+G13/C13-1</f>
         <v>7.1452199801521621E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>0.15183752417794971</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>0.10289389067524124</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" ref="J45:J47" si="60">+J13/F13-1</f>
+        <f t="shared" ref="J45:J47" si="59">+J13/F13-1</f>
         <v>0.3356973995271868</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" ref="K45:O47" si="61">+K13/G13-1</f>
+        <f t="shared" ref="K45:P47" si="60">+K13/G13-1</f>
         <v>0.16085211485026241</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-0.30702490904002244</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-6.095944871455039E-3</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.25250737463126849</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-1.6223404255319096E-2</v>
       </c>
-      <c r="P45" s="10"/>
+      <c r="P45" s="10">
+        <f t="shared" si="60"/>
+        <v>0.41033925686591277</v>
+      </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="10" t="e">
-        <f t="shared" ref="U45:Y47" si="62">+U13/T13-1</f>
+        <f t="shared" ref="U45:Y47" si="61">+U13/T13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V45" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W45" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X45" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y45" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z45" s="10">
+        <f t="shared" ref="Z45:AA47" si="62">+Z13/Y13-1</f>
+        <v>0.15658362989323837</v>
+      </c>
+      <c r="AA45" s="10">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W45" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X45" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y45" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z45" s="10">
-        <f t="shared" ref="Z45:AA47" si="63">+Z13/Y13-1</f>
-        <v>0.15658362989323837</v>
-      </c>
-      <c r="AA45" s="10">
-        <f t="shared" si="63"/>
         <v>1.8389982110912362E-2</v>
       </c>
     </row>
@@ -4939,72 +5041,75 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="10">
+        <f t="shared" si="58"/>
+        <v>-1.3605442176870763E-2</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="58"/>
+        <v>3.0501089324618702E-2</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="58"/>
+        <v>2.6051188299817118E-2</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="59"/>
-        <v>-1.3605442176870763E-2</v>
-      </c>
-      <c r="H46" s="10">
-        <f t="shared" si="59"/>
-        <v>3.0501089324618702E-2</v>
-      </c>
-      <c r="I46" s="10">
-        <f t="shared" si="59"/>
-        <v>2.6051188299817118E-2</v>
-      </c>
-      <c r="J46" s="10">
+        <v>0.10140562248995977</v>
+      </c>
+      <c r="K46" s="10">
         <f t="shared" si="60"/>
-        <v>0.10140562248995977</v>
-      </c>
-      <c r="K46" s="10">
-        <f t="shared" si="61"/>
         <v>4.403183023872681E-2</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>7.2410147991543328E-2</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>6.1469933184855163E-2</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>8.6599817684594349E-2</v>
       </c>
       <c r="O46" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.24085365853658547</v>
       </c>
-      <c r="P46" s="10"/>
+      <c r="P46" s="10">
+        <f t="shared" si="60"/>
+        <v>0.34105470675209459</v>
+      </c>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V46" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W46" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X46" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y46" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z46" s="10">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V46" s="10" t="e">
+        <v>4.5824847250509171E-2</v>
+      </c>
+      <c r="AA46" s="10">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W46" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X46" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y46" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z46" s="10">
-        <f t="shared" si="63"/>
-        <v>4.5824847250509171E-2</v>
-      </c>
-      <c r="AA46" s="10">
-        <f t="shared" si="63"/>
         <v>6.669912366114894E-2</v>
       </c>
     </row>
@@ -5017,72 +5122,75 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="10">
+        <f t="shared" si="58"/>
+        <v>-3.5294117647058809E-2</v>
+      </c>
+      <c r="H47" s="10">
+        <f t="shared" si="58"/>
+        <v>-8.6419753086419804E-2</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="58"/>
+        <v>7.9487179487179427E-2</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="59"/>
-        <v>-3.5294117647058809E-2</v>
-      </c>
-      <c r="H47" s="10">
-        <f t="shared" si="59"/>
-        <v>-8.6419753086419804E-2</v>
-      </c>
-      <c r="I47" s="10">
-        <f t="shared" si="59"/>
-        <v>7.9487179487179427E-2</v>
-      </c>
-      <c r="J47" s="10">
+        <v>7.9545454545454586E-2</v>
+      </c>
+      <c r="K47" s="10">
         <f t="shared" si="60"/>
-        <v>7.9545454545454586E-2</v>
-      </c>
-      <c r="K47" s="10">
-        <f t="shared" si="61"/>
         <v>0.29268292682926833</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.2081081081081082</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.178147268408551</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.17894736842105252</v>
       </c>
       <c r="O47" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>6.3679245283018826E-2</v>
       </c>
-      <c r="P47" s="10"/>
+      <c r="P47" s="10">
+        <f t="shared" si="60"/>
+        <v>0.18568232662192385</v>
+      </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V47" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W47" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X47" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y47" s="10" t="e">
+        <f t="shared" si="61"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z47" s="10">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V47" s="10" t="e">
+        <v>7.3924731182795078E-3</v>
+      </c>
+      <c r="AA47" s="10">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W47" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X47" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y47" s="10" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z47" s="10">
-        <f t="shared" si="63"/>
-        <v>7.3924731182795078E-3</v>
-      </c>
-      <c r="AA47" s="10">
-        <f t="shared" si="63"/>
         <v>0.21080720480320214</v>
       </c>
     </row>
@@ -5099,56 +5207,59 @@
         <v>3.4888130451270483E-2</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" ref="H48:J48" si="64">H16/D16-1</f>
+        <f t="shared" ref="H48:J48" si="63">H16/D16-1</f>
         <v>8.9650009358038574E-2</v>
       </c>
       <c r="I48" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>7.3178863143857242E-2</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0.23960931005818797</v>
       </c>
       <c r="K48" s="12">
-        <f t="shared" ref="K48" si="65">K16/G16-1</f>
+        <f t="shared" ref="K48" si="64">K16/G16-1</f>
         <v>0.1273360205203371</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" ref="L48" si="66">L16/H16-1</f>
+        <f t="shared" ref="L48" si="65">L16/H16-1</f>
         <v>2.2329096530401937E-2</v>
       </c>
       <c r="M48" s="12">
-        <f t="shared" ref="M48" si="67">M16/I16-1</f>
+        <f t="shared" ref="M48" si="66">M16/I16-1</f>
         <v>2.982292637465056E-2</v>
       </c>
       <c r="N48" s="12">
-        <f t="shared" ref="N48:O48" si="68">N16/J16-1</f>
+        <f t="shared" ref="N48:P48" si="67">N16/J16-1</f>
         <v>1.8608549874266522E-2</v>
       </c>
       <c r="O48" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>7.1347310255160057E-2</v>
       </c>
-      <c r="P48" s="12"/>
+      <c r="P48" s="12">
+        <f t="shared" si="67"/>
+        <v>0.13289650537634401</v>
+      </c>
       <c r="Q48" s="12"/>
       <c r="R48" s="12"/>
       <c r="S48" s="4"/>
       <c r="T48" s="10"/>
       <c r="U48" s="12">
-        <f t="shared" ref="U48:X48" si="69">U16/T16-1</f>
+        <f t="shared" ref="U48:X48" si="68">U16/T16-1</f>
         <v>7.8713210130047839E-2</v>
       </c>
       <c r="V48" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>-0.22017766497461932</v>
       </c>
       <c r="W48" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0.15183075671277457</v>
       </c>
       <c r="X48" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>6.0139399076952094E-2</v>
       </c>
       <c r="Y48" s="12">
@@ -5169,23 +5280,23 @@
         <v>42</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" ref="C49:G49" si="70">C18/C16</f>
+        <f t="shared" ref="C49:G49" si="69">C18/C16</f>
         <v>0.44804702313234734</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0.50870297585626056</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0.49258209701616934</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0.44638403990024939</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0.51227555881275189</v>
       </c>
       <c r="H49" s="10">
@@ -5193,55 +5304,58 @@
         <v>0.50824458948814843</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" ref="I49:J49" si="71">I18/I16</f>
+        <f t="shared" ref="I49:J49" si="70">I18/I16</f>
         <v>0.51273687480584029</v>
       </c>
       <c r="J49" s="10">
+        <f t="shared" si="70"/>
+        <v>0.49790444258172672</v>
+      </c>
+      <c r="K49" s="10">
+        <f t="shared" ref="K49:N49" si="71">K18/K16</f>
+        <v>0.52088412156671537</v>
+      </c>
+      <c r="L49" s="10">
         <f t="shared" si="71"/>
-        <v>0.49790444258172672</v>
-      </c>
-      <c r="K49" s="10">
-        <f t="shared" ref="K49:N49" si="72">K18/K16</f>
-        <v>0.52088412156671537</v>
-      </c>
-      <c r="L49" s="10">
+        <v>0.51696908602150538</v>
+      </c>
+      <c r="M49" s="10">
+        <f t="shared" si="71"/>
+        <v>0.51809954751131226</v>
+      </c>
+      <c r="N49" s="10">
+        <f t="shared" si="71"/>
+        <v>0.50822909809084926</v>
+      </c>
+      <c r="O49" s="10">
+        <f t="shared" ref="O49:P49" si="72">O18/O16</f>
+        <v>0.51107402912621358</v>
+      </c>
+      <c r="P49" s="10">
         <f t="shared" si="72"/>
-        <v>0.51696908602150538</v>
-      </c>
-      <c r="M49" s="10">
-        <f t="shared" si="72"/>
-        <v>0.51809954751131226</v>
-      </c>
-      <c r="N49" s="10">
-        <f t="shared" si="72"/>
-        <v>0.50822909809084926</v>
-      </c>
-      <c r="O49" s="10">
-        <f t="shared" ref="O49" si="73">O18/O16</f>
-        <v>0.51107402912621358</v>
-      </c>
-      <c r="P49" s="10"/>
+        <v>0.52498887735429334</v>
+      </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
       <c r="S49" s="4"/>
       <c r="T49" s="10">
-        <f t="shared" ref="T49:X49" si="74">T18/T16</f>
+        <f t="shared" ref="T49:X49" si="73">T18/T16</f>
         <v>0.51850330823636781</v>
       </c>
       <c r="U49" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0.52000846023688663</v>
       </c>
       <c r="V49" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0.50024410089503657</v>
       </c>
       <c r="W49" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0.50696995384760291</v>
       </c>
       <c r="X49" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0.47283550264315222</v>
       </c>
       <c r="Y49" s="10">
@@ -5262,23 +5376,23 @@
         <v>43</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" ref="C50:G50" si="75">C25/C16</f>
+        <f t="shared" ref="C50:G50" si="74">C25/C16</f>
         <v>1.1376564277588168E-2</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>3.2753134942915964E-2</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6.8344724120686776E-2</v>
       </c>
       <c r="F50" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-7.813798836242726E-2</v>
       </c>
       <c r="G50" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6.1561011359472333E-2</v>
       </c>
       <c r="H50" s="10">
@@ -5286,55 +5400,58 @@
         <v>5.960151150807283E-2</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" ref="I50:J50" si="76">I25/I16</f>
+        <f t="shared" ref="I50:J50" si="75">I25/I16</f>
         <v>9.2575333954644304E-2</v>
       </c>
       <c r="J50" s="10">
+        <f t="shared" si="75"/>
+        <v>9.5557418273260683E-3</v>
+      </c>
+      <c r="K50" s="10">
+        <f t="shared" ref="K50:N50" si="76">K25/K16</f>
+        <v>9.8976109215017066E-2</v>
+      </c>
+      <c r="L50" s="10">
         <f t="shared" si="76"/>
-        <v>9.5557418273260683E-3</v>
-      </c>
-      <c r="K50" s="10">
-        <f t="shared" ref="K50:N50" si="77">K25/K16</f>
-        <v>9.8976109215017066E-2</v>
-      </c>
-      <c r="L50" s="10">
+        <v>9.1901881720430109E-2</v>
+      </c>
+      <c r="M50" s="10">
+        <f t="shared" si="76"/>
+        <v>0.11101055806938159</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="76"/>
+        <v>2.6991441737985518E-2</v>
+      </c>
+      <c r="O50" s="10">
+        <f t="shared" ref="O50:P50" si="77">O25/O16</f>
+        <v>0.10709951456310679</v>
+      </c>
+      <c r="P50" s="10">
         <f t="shared" si="77"/>
-        <v>9.1901881720430109E-2</v>
-      </c>
-      <c r="M50" s="10">
-        <f t="shared" si="77"/>
-        <v>0.11101055806938159</v>
-      </c>
-      <c r="N50" s="10">
-        <f t="shared" si="77"/>
-        <v>2.6991441737985518E-2</v>
-      </c>
-      <c r="O50" s="10">
-        <f t="shared" ref="O50" si="78">O25/O16</f>
-        <v>0.10709951456310679</v>
-      </c>
-      <c r="P50" s="10"/>
+        <v>8.5125315141628355E-2</v>
+      </c>
       <c r="Q50" s="10"/>
       <c r="R50" s="10"/>
       <c r="S50" s="4"/>
       <c r="T50" s="10">
-        <f t="shared" ref="T50:X50" si="79">T25/T16</f>
+        <f t="shared" ref="T50:X50" si="78">T25/T16</f>
         <v>0.1080082135523614</v>
       </c>
       <c r="U50" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0.11252115059221658</v>
       </c>
       <c r="V50" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>4.0412259289395173E-2</v>
       </c>
       <c r="W50" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>9.3576339832344355E-2</v>
       </c>
       <c r="X50" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>2.9718804140198125E-2</v>
       </c>
       <c r="Y50" s="10">
@@ -5355,23 +5472,23 @@
         <v>45</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" ref="C51:G51" si="80">C34/C16</f>
+        <f t="shared" ref="C51:G51" si="79">C34/C16</f>
         <v>-7.2051573758058398E-3</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>1.5721504772599662E-2</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>4.3340556759459907E-2</v>
       </c>
       <c r="F51" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>4.3640897755610969E-3</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>3.1146940271161598E-2</v>
       </c>
       <c r="H51" s="10">
@@ -5379,55 +5496,58 @@
         <v>3.2634833390587425E-2</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" ref="I51:J51" si="81">I34/I16</f>
+        <f t="shared" ref="I51:J51" si="80">I34/I16</f>
         <v>6.8499534016775401E-2</v>
       </c>
       <c r="J51" s="10">
+        <f t="shared" si="80"/>
+        <v>3.3528918692372171E-3</v>
+      </c>
+      <c r="K51" s="10">
+        <f t="shared" ref="K51:N51" si="81">K34/K16</f>
+        <v>6.9397042093287828E-2</v>
+      </c>
+      <c r="L51" s="10">
         <f t="shared" si="81"/>
-        <v>3.3528918692372171E-3</v>
-      </c>
-      <c r="K51" s="10">
-        <f t="shared" ref="K51:N51" si="82">K34/K16</f>
-        <v>6.9397042093287828E-2</v>
-      </c>
-      <c r="L51" s="10">
+        <v>6.2163978494623656E-2</v>
+      </c>
+      <c r="M51" s="10">
+        <f t="shared" si="81"/>
+        <v>6.953242835595777E-2</v>
+      </c>
+      <c r="N51" s="10">
+        <f t="shared" si="81"/>
+        <v>1.3495720868992759E-2</v>
+      </c>
+      <c r="O51" s="10">
+        <f t="shared" ref="O51:P51" si="82">O34/O16</f>
+        <v>7.3422330097087374E-2</v>
+      </c>
+      <c r="P51" s="10">
         <f t="shared" si="82"/>
-        <v>6.2163978494623656E-2</v>
-      </c>
-      <c r="M51" s="10">
-        <f t="shared" si="82"/>
-        <v>6.953242835595777E-2</v>
-      </c>
-      <c r="N51" s="10">
-        <f t="shared" si="82"/>
-        <v>1.3495720868992759E-2</v>
-      </c>
-      <c r="O51" s="10">
-        <f t="shared" ref="O51" si="83">O34/O16</f>
-        <v>7.3422330097087374E-2</v>
-      </c>
-      <c r="P51" s="10"/>
+        <v>5.2498887735429337E-2</v>
+      </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
       <c r="S51" s="4"/>
       <c r="T51" s="10">
-        <f t="shared" ref="T51:X51" si="84">T34/T16</f>
+        <f t="shared" ref="T51:X51" si="83">T34/T16</f>
         <v>7.7572438968742871E-2</v>
       </c>
       <c r="U51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>8.3544839255499159E-2</v>
       </c>
       <c r="V51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>2.3379441280173583E-2</v>
       </c>
       <c r="W51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>9.9698596590373931E-2</v>
       </c>
       <c r="X51" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>2.7186708720181245E-2</v>
       </c>
       <c r="Y51" s="10">
@@ -5448,23 +5568,23 @@
         <v>44</v>
       </c>
       <c r="C52" s="10">
-        <f t="shared" ref="C52:G52" si="85">C29/C28</f>
+        <f t="shared" ref="C52:G52" si="84">C29/C28</f>
         <v>1.71875</v>
       </c>
       <c r="D52" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>0.21951219512195122</v>
       </c>
       <c r="E52" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>0.16871165644171779</v>
       </c>
       <c r="F52" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>3.3816425120772944E-2</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>0.30204081632653063</v>
       </c>
       <c r="H52" s="10">
@@ -5472,55 +5592,58 @@
         <v>0.30491803278688523</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" ref="I52:J52" si="86">I29/I28</f>
+        <f t="shared" ref="I52:J52" si="85">I29/I28</f>
         <v>0.22166666666666668</v>
       </c>
       <c r="J52" s="10">
+        <f t="shared" si="85"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="K52" s="10">
+        <f t="shared" ref="K52:N52" si="86">K29/K28</f>
+        <v>0.25513698630136988</v>
+      </c>
+      <c r="L52" s="10">
         <f t="shared" si="86"/>
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="K52" s="10">
-        <f t="shared" ref="K52:N52" si="87">K29/K28</f>
-        <v>0.25513698630136988</v>
-      </c>
-      <c r="L52" s="10">
+        <v>0.23312883435582821</v>
+      </c>
+      <c r="M52" s="10">
+        <f t="shared" si="86"/>
+        <v>0.26</v>
+      </c>
+      <c r="N52" s="10">
+        <f t="shared" si="86"/>
+        <v>0.1134020618556701</v>
+      </c>
+      <c r="O52" s="10">
+        <f t="shared" ref="O52:P52" si="87">O29/O28</f>
+        <v>0.24884080370942813</v>
+      </c>
+      <c r="P52" s="10">
         <f t="shared" si="87"/>
-        <v>0.23312883435582821</v>
-      </c>
-      <c r="M52" s="10">
-        <f t="shared" si="87"/>
-        <v>0.26</v>
-      </c>
-      <c r="N52" s="10">
-        <f t="shared" si="87"/>
-        <v>0.1134020618556701</v>
-      </c>
-      <c r="O52" s="10">
-        <f t="shared" ref="O52" si="88">O29/O28</f>
-        <v>0.24884080370942813</v>
-      </c>
-      <c r="P52" s="10"/>
+        <v>0.25094339622641509</v>
+      </c>
       <c r="Q52" s="10"/>
       <c r="R52" s="10"/>
       <c r="S52" s="4"/>
       <c r="T52" s="10">
-        <f t="shared" ref="T52:X52" si="89">T29/T28</f>
+        <f t="shared" ref="T52:X52" si="88">T29/T28</f>
         <v>0.28144720235591081</v>
       </c>
       <c r="U52" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.2501954652071931</v>
       </c>
       <c r="V52" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.20242214532871972</v>
       </c>
       <c r="W52" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.19427954668105774</v>
       </c>
       <c r="X52" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.34536082474226804</v>
       </c>
       <c r="Y52" s="10">
